--- a/BELGRANO 1646/Agosto/Agosto-BLG1646.xlsx
+++ b/BELGRANO 1646/Agosto/Agosto-BLG1646.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BELGRANO 1646\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BELGRANO 1646\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184FF792-8844-4D2D-8B52-8A1F3FA21A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B431F7F4-94EB-43FE-85DF-0F799D2FCE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$128</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$132</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="181">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -496,21 +496,6 @@
     <t>BALBOA, ARIEL</t>
   </si>
   <si>
-    <t>PERÍODO: JULIO</t>
-  </si>
-  <si>
-    <t>Energoup MES DE JULIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mes de JULIO </t>
-  </si>
-  <si>
-    <t>VTO: 14/08</t>
-  </si>
-  <si>
-    <t>Fumigacion 07/07</t>
-  </si>
-  <si>
     <t>Casa ruan - materiales de trabajo - plafones y dicroicas</t>
   </si>
   <si>
@@ -523,9 +508,6 @@
     <t>Debito 27/07</t>
   </si>
   <si>
-    <t xml:space="preserve">Doartero - Mano de obra de impermeabilizacion terraza debajo de pileta </t>
-  </si>
-  <si>
     <t>Contessi - Cuota 2  de arreglo montavehiculos</t>
   </si>
   <si>
@@ -538,9 +520,6 @@
     <t xml:space="preserve">Sr. Diego Britez </t>
   </si>
   <si>
-    <t>Honorarios JULIO</t>
-  </si>
-  <si>
     <t>SEGURO OBLIGATORIO SR DIEGO BRITEZ FEDERACION PATRONAL DEBITO AUTOMATICO 01/07</t>
   </si>
   <si>
@@ -556,15 +535,6 @@
     <t>Leonardo Balcalazza - Recapeo vereda, puntas de canteros</t>
   </si>
   <si>
-    <t>Leonardo Balcalazza - Mano de obra montavehiculos, pintura piso y paredes</t>
-  </si>
-  <si>
-    <t>Leonardo Balcalazza - Pintura techo hall de entrada</t>
-  </si>
-  <si>
-    <t>Pago mis cuentas 10/07</t>
-  </si>
-  <si>
     <t>Vto. 04/07</t>
   </si>
   <si>
@@ -598,10 +568,43 @@
     <t>YA ABONO:</t>
   </si>
   <si>
-    <t>Ingreso mes de JUNIO</t>
-  </si>
-  <si>
     <t>A GASTON LO HABIAMOS PUESTO COMO DEUDOR( FIJARSE EN EL PDF) Y NO LO ERA</t>
+  </si>
+  <si>
+    <t>VTO: 15/09</t>
+  </si>
+  <si>
+    <t>PERÍODO: AGOSTO</t>
+  </si>
+  <si>
+    <t>Honorarios AGOSTO</t>
+  </si>
+  <si>
+    <t>Energoup MES DE AGOSTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mes de AGOSTO </t>
+  </si>
+  <si>
+    <t>Ingreso mes de JULIO</t>
+  </si>
+  <si>
+    <t>Salvatierra Matias - Desobstruccion y limpieza de canaletas guardaganado en pluviales de cochera en 1 piso, 2 piso y coletora de pluvial</t>
+  </si>
+  <si>
+    <t>Salvatierra Matias - Desobstruccion columna en baño 7B</t>
+  </si>
+  <si>
+    <t>Salvatierra Matias -Servicio de diagnostico por imágenes en 6B - Cuota 1/2</t>
+  </si>
+  <si>
+    <t>Fumigacion 19/08</t>
+  </si>
+  <si>
+    <t>Contessi - Provision y cambio de lapices de nivelacion en el montaauto</t>
+  </si>
+  <si>
+    <t>Pago mis cuentas 06/08</t>
   </si>
 </sst>
 </file>
@@ -609,15 +612,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="169" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -1326,11 +1329,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="250">
+  <cellXfs count="252">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
@@ -1340,7 +1343,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -1352,7 +1355,7 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1363,12 +1366,12 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="2" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1420,7 +1423,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="2" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1428,7 +1431,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1444,17 +1447,17 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1467,12 +1470,12 @@
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1480,53 +1483,53 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="9" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="9" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="39" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="10" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="10" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
@@ -1537,41 +1540,38 @@
     <xf numFmtId="10" fontId="2" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="14" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="14" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1580,21 +1580,21 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="10" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="10" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1607,14 +1607,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="6" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1705,51 +1706,51 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1759,7 +1760,7 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="11" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="11" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1774,7 +1775,11 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2140,24 +2145,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P138"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P142"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8"/>
       <c r="B1" s="97" t="s">
         <v>118</v>
@@ -2166,7 +2171,7 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="64"/>
       <c r="B2" s="65" t="s">
         <v>0</v>
@@ -2175,7 +2180,7 @@
       <c r="D2" s="65"/>
       <c r="E2" s="66"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="67"/>
       <c r="B3" s="68" t="s">
         <v>88</v>
@@ -2184,7 +2189,7 @@
       <c r="D3" s="68"/>
       <c r="E3" s="69"/>
     </row>
-    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="67"/>
       <c r="B4" s="68" t="s">
         <v>89</v>
@@ -2193,20 +2198,20 @@
       <c r="D4" s="68"/>
       <c r="E4" s="69"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="C5" s="71" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="D5" s="71"/>
       <c r="E5" s="72"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="67" t="s">
         <v>99</v>
       </c>
@@ -2215,7 +2220,7 @@
       <c r="D6" s="68"/>
       <c r="E6" s="69"/>
     </row>
-    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="70" t="s">
         <v>98</v>
       </c>
@@ -2224,37 +2229,37 @@
       <c r="D7" s="71"/>
       <c r="E7" s="72"/>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14" s="204" t="s">
         <v>134</v>
       </c>
       <c r="C14" s="205"/>
       <c r="D14" s="206"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B15" s="207"/>
       <c r="C15" s="208"/>
       <c r="D15" s="209"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B16" s="207"/>
       <c r="C16" s="208"/>
       <c r="D16" s="209"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B17" s="210"/>
       <c r="C17" s="211"/>
       <c r="D17" s="212"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="61" t="s">
         <v>86</v>
       </c>
@@ -2268,25 +2273,25 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="120" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="129"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="120" t="s">
         <v>126</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="179">
+      <c r="D23" s="178">
         <v>1262522.3</v>
       </c>
       <c r="E23" s="133">
@@ -2298,13 +2303,13 @@
         <v>102138.05407</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="120" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="179">
+      <c r="D24" s="178">
         <v>-274598.59999999998</v>
       </c>
       <c r="E24" s="133">
@@ -2316,13 +2321,13 @@
         <v>-22215.026739999998</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="120" t="s">
         <v>112</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="179">
+      <c r="D25" s="178">
         <v>0.3</v>
       </c>
       <c r="E25" s="133">
@@ -2334,15 +2339,15 @@
         <v>2.427E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="120"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="179"/>
+      <c r="D26" s="178"/>
       <c r="E26" s="133"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="95" t="s">
         <v>3</v>
       </c>
@@ -2369,13 +2374,13 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="94" t="s">
         <v>109</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="180">
+      <c r="D28" s="179">
         <v>0</v>
       </c>
       <c r="E28" s="133">
@@ -2388,11 +2393,11 @@
       </c>
       <c r="H28" s="149"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="94"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="179">
+      <c r="D29" s="178">
         <v>0</v>
       </c>
       <c r="E29" s="133">
@@ -2405,25 +2410,25 @@
       </c>
       <c r="H29" s="149"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="94"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="179"/>
+      <c r="D30" s="178"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="H30" s="149"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="94"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="179"/>
+      <c r="D31" s="178"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="H31" s="149"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="95" t="s">
         <v>117</v>
       </c>
@@ -2450,13 +2455,13 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="94" t="s">
         <v>109</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="180"/>
+      <c r="D33" s="179"/>
       <c r="E33" s="133">
         <f>D33*91.91%</f>
         <v>0</v>
@@ -2467,13 +2472,13 @@
       </c>
       <c r="H33" s="149"/>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>130</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="179"/>
+      <c r="D34" s="178"/>
       <c r="E34" s="133">
         <f t="shared" ref="E34:E35" si="3">D34*91.91%</f>
         <v>0</v>
@@ -2484,13 +2489,13 @@
       </c>
       <c r="H34" s="149"/>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="94" t="s">
         <v>2</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="179"/>
+      <c r="D35" s="178"/>
       <c r="E35" s="133">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2501,7 +2506,7 @@
       </c>
       <c r="H35" s="149"/>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="95" t="s">
         <v>110</v>
       </c>
@@ -2521,34 +2526,34 @@
       </c>
       <c r="H36" s="149"/>
     </row>
-    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="128"/>
       <c r="B37" s="98"/>
       <c r="C37" s="98"/>
-      <c r="D37" s="179"/>
+      <c r="D37" s="178"/>
       <c r="E37" s="119"/>
       <c r="F37" s="119"/>
       <c r="H37" s="149"/>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="128"/>
       <c r="B38" s="98"/>
       <c r="C38" s="98"/>
-      <c r="D38" s="179"/>
+      <c r="D38" s="178"/>
       <c r="E38" s="119"/>
       <c r="F38" s="119"/>
       <c r="H38" s="149"/>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="98"/>
       <c r="B39" s="98"/>
       <c r="C39" s="110"/>
-      <c r="D39" s="179"/>
+      <c r="D39" s="178"/>
       <c r="E39" s="119"/>
       <c r="F39" s="119"/>
       <c r="H39" s="149"/>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="95" t="s">
         <v>117</v>
       </c>
@@ -2565,7 +2570,7 @@
       </c>
       <c r="H40" s="149"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="94" t="s">
         <v>140</v>
       </c>
@@ -2584,7 +2589,7 @@
       </c>
       <c r="H41" s="149"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="94" t="s">
         <v>139</v>
       </c>
@@ -2603,11 +2608,11 @@
       </c>
       <c r="H42" s="149"/>
     </row>
-    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="94"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="182"/>
+      <c r="D43" s="181"/>
       <c r="E43" s="133">
         <f>D43*91.91%</f>
         <v>0</v>
@@ -2618,7 +2623,7 @@
       </c>
       <c r="H43" s="149"/>
     </row>
-    <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="95" t="s">
         <v>127</v>
       </c>
@@ -2628,11 +2633,11 @@
         <f>SUM(D41:D43)</f>
         <v>40567.21</v>
       </c>
-      <c r="E44" s="158">
+      <c r="E44" s="157">
         <f>SUM(E41:E43)</f>
         <v>37285.322710999993</v>
       </c>
-      <c r="F44" s="168">
+      <c r="F44" s="167">
         <f>SUM(F41:F43)</f>
         <v>3281.8872890000002</v>
       </c>
@@ -2642,20 +2647,20 @@
       </c>
       <c r="H44" s="149"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="94" t="s">
         <v>4</v>
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="182"/>
+      <c r="D45" s="181"/>
       <c r="E45" s="113"/>
       <c r="F45" s="100"/>
       <c r="H45" s="149"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="94" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="98"/>
@@ -2672,37 +2677,37 @@
       </c>
       <c r="H46" s="149"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="94" t="s">
         <v>5</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C47" s="7"/>
-      <c r="D47" s="112">
-        <f>157828.92+9348.69+84138.18</f>
-        <v>251315.79</v>
+      <c r="D47" s="191">
+        <f>106691.95+6312.61+56813.5</f>
+        <v>169818.06</v>
       </c>
       <c r="E47" s="133">
         <f>D47*91.91%</f>
-        <v>230984.34258899998</v>
+        <v>156079.77894599998</v>
       </c>
       <c r="F47" s="133">
         <f>D47*8.09%</f>
-        <v>20331.447411000001</v>
+        <v>13738.281053999999</v>
       </c>
       <c r="H47" s="149"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="94" t="s">
         <v>135</v>
       </c>
       <c r="B48" s="98" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="C48" s="7"/>
-      <c r="D48" s="112">
+      <c r="D48" s="191">
         <v>828107.55</v>
       </c>
       <c r="E48" s="133">
@@ -2715,7 +2720,7 @@
       </c>
       <c r="H48" s="149"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="95" t="s">
         <v>6</v>
       </c>
@@ -2723,43 +2728,43 @@
       <c r="C49" s="96"/>
       <c r="D49" s="107">
         <f>SUM(D46:D48)</f>
-        <v>1084443.3400000001</v>
+        <v>1002945.6100000001</v>
       </c>
       <c r="E49" s="107">
         <f t="shared" ref="E49:F49" si="6">SUM(E46:E48)</f>
-        <v>996711.87379400001</v>
+        <v>921807.31015100004</v>
       </c>
       <c r="F49" s="107">
         <f t="shared" si="6"/>
-        <v>87731.466206000012</v>
+        <v>81138.299849000003</v>
       </c>
       <c r="G49" s="108">
         <f>E49+F49</f>
-        <v>1084443.3400000001</v>
+        <v>1002945.6100000001</v>
       </c>
       <c r="H49" s="149" t="str">
         <f>IF(D49=G49, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="182"/>
+      <c r="D50" s="181"/>
       <c r="E50" s="114"/>
       <c r="F50" s="7"/>
       <c r="H50" s="149"/>
     </row>
-    <row r="51" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="187" t="s">
-        <v>154</v>
-      </c>
-      <c r="B51" s="175"/>
-      <c r="C51" s="176"/>
-      <c r="D51" s="182">
+    <row r="51" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="186" t="s">
+        <v>148</v>
+      </c>
+      <c r="B51" s="174"/>
+      <c r="C51" s="175"/>
+      <c r="D51" s="181">
         <v>960000</v>
       </c>
       <c r="E51" s="148">
@@ -2771,1398 +2776,1492 @@
         <f>D51</f>
         <v>960000</v>
       </c>
-      <c r="H51" s="160">
+      <c r="H51" s="159">
         <f>E51+F51</f>
         <v>960000</v>
       </c>
-      <c r="I51" s="177">
-        <f t="shared" ref="I51:I70" si="7">H51-D51</f>
-        <v>0</v>
-      </c>
-      <c r="J51" s="177">
-        <f t="shared" ref="J51:J70" si="8">G51-D51</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="187" t="s">
-        <v>138</v>
-      </c>
-      <c r="B52" s="175"/>
-      <c r="C52" s="176"/>
-      <c r="D52" s="112">
-        <v>372000</v>
+      <c r="I51" s="176">
+        <f t="shared" ref="I51:I74" si="7">H51-D51</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="176">
+        <f t="shared" ref="J51:J75" si="8">G51-D51</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="186" t="s">
+        <v>179</v>
+      </c>
+      <c r="B52" s="174"/>
+      <c r="C52" s="175"/>
+      <c r="D52" s="249">
+        <v>160000</v>
       </c>
       <c r="E52" s="148">
         <f>D52</f>
+        <v>160000</v>
+      </c>
+      <c r="F52" s="7"/>
+      <c r="G52" s="108"/>
+      <c r="H52" s="159"/>
+      <c r="I52" s="176"/>
+      <c r="J52" s="176"/>
+    </row>
+    <row r="53" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="186" t="s">
+        <v>138</v>
+      </c>
+      <c r="B53" s="174"/>
+      <c r="C53" s="175"/>
+      <c r="D53" s="191">
         <v>372000</v>
       </c>
-      <c r="F52" s="7"/>
-      <c r="G52" s="108">
-        <f>D52</f>
+      <c r="E53" s="148">
+        <f>D53</f>
         <v>372000</v>
       </c>
-      <c r="H52" s="160">
-        <f>E52+F52</f>
+      <c r="F53" s="7"/>
+      <c r="G53" s="108">
+        <f>D53</f>
         <v>372000</v>
       </c>
-      <c r="I52" s="177">
-        <f>H52-D52</f>
-        <v>0</v>
-      </c>
-      <c r="J52" s="177"/>
-    </row>
-    <row r="53" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="199" t="s">
-        <v>155</v>
-      </c>
-      <c r="B53" s="200"/>
-      <c r="C53" s="201"/>
-      <c r="D53" s="112">
+      <c r="H53" s="159">
+        <f>E53+F53</f>
+        <v>372000</v>
+      </c>
+      <c r="I53" s="176">
+        <f>H53-D53</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="176"/>
+    </row>
+    <row r="54" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="199" t="s">
+        <v>149</v>
+      </c>
+      <c r="B54" s="200"/>
+      <c r="C54" s="201"/>
+      <c r="D54" s="112">
         <v>165500</v>
       </c>
-      <c r="E53" s="148">
-        <f t="shared" ref="E53:E59" si="9">D53*91.91%</f>
+      <c r="E54" s="148">
+        <f t="shared" ref="E54:E60" si="9">D54*91.91%</f>
         <v>152111.04999999999</v>
       </c>
-      <c r="F53" s="133">
-        <f t="shared" ref="F53:F59" si="10">D53*8.09%</f>
+      <c r="F54" s="133">
+        <f t="shared" ref="F54:F60" si="10">D54*8.09%</f>
         <v>13388.95</v>
       </c>
-      <c r="G53" s="108">
-        <f t="shared" ref="G53:G70" si="11">D53</f>
+      <c r="G54" s="108">
+        <f t="shared" ref="G54:G75" si="11">D54</f>
         <v>165500</v>
       </c>
-      <c r="H53" s="160">
-        <f t="shared" ref="H53:H70" si="12">E53+F53</f>
+      <c r="H54" s="159">
+        <f t="shared" ref="H54:H75" si="12">E54+F54</f>
         <v>165500</v>
       </c>
-      <c r="I53" s="177">
+      <c r="I54" s="176">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J53" s="177">
+      <c r="J54" s="176">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="120" t="s">
+    <row r="55" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="B54" s="162"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="112">
+      <c r="B55" s="161"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="112">
         <v>148124.67000000001</v>
       </c>
-      <c r="E54" s="148">
+      <c r="E55" s="148">
         <f t="shared" si="9"/>
         <v>136141.38419700001</v>
       </c>
-      <c r="F54" s="133">
+      <c r="F55" s="133">
         <f t="shared" si="10"/>
         <v>11983.285803000001</v>
       </c>
-      <c r="G54" s="108">
+      <c r="G55" s="108">
         <f t="shared" si="11"/>
         <v>148124.67000000001</v>
       </c>
-      <c r="H54" s="160">
+      <c r="H55" s="159">
         <f t="shared" si="12"/>
         <v>148124.67000000001</v>
       </c>
-      <c r="I54" s="177"/>
-      <c r="J54" s="177"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="94" t="s">
-        <v>145</v>
-      </c>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="112">
+      <c r="I55" s="176"/>
+      <c r="J55" s="176"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="94" t="s">
+        <v>172</v>
+      </c>
+      <c r="B56" s="7"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="191">
         <v>148200</v>
       </c>
-      <c r="E55" s="148">
+      <c r="E56" s="148">
         <f t="shared" si="9"/>
         <v>136210.62</v>
       </c>
-      <c r="F55" s="133">
+      <c r="F56" s="133">
         <f t="shared" si="10"/>
         <v>11989.38</v>
       </c>
-      <c r="G55" s="108">
+      <c r="G56" s="108">
         <f t="shared" si="11"/>
         <v>148200</v>
       </c>
-      <c r="H55" s="160">
+      <c r="H56" s="159">
         <f t="shared" si="12"/>
         <v>148200</v>
       </c>
-      <c r="I55" s="177">
+      <c r="I56" s="176">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J55" s="177">
+      <c r="J56" s="176">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="94" t="s">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="B56" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="C56" s="7"/>
-      <c r="D56" s="112">
+      <c r="B57" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C57" s="7"/>
+      <c r="D57" s="112">
         <v>129320</v>
       </c>
-      <c r="E56" s="148">
-        <f>D56*91.91%</f>
+      <c r="E57" s="148">
+        <f>D57*91.91%</f>
         <v>118858.01199999999</v>
       </c>
-      <c r="F56" s="133">
+      <c r="F57" s="133">
         <f t="shared" si="10"/>
         <v>10461.987999999999</v>
       </c>
-      <c r="G56" s="108">
+      <c r="G57" s="108">
         <f t="shared" si="11"/>
         <v>129320</v>
       </c>
-      <c r="H56" s="160">
-        <f>E56+F56</f>
+      <c r="H57" s="159">
+        <f>E57+F57</f>
         <v>129319.99999999999</v>
       </c>
-      <c r="I56" s="177">
+      <c r="I57" s="176">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J56" s="177">
+      <c r="J57" s="176">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="94" t="s">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="B57" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="C57" s="7"/>
-      <c r="D57" s="112">
+      <c r="B58" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C58" s="7"/>
+      <c r="D58" s="112">
         <v>614674.98</v>
       </c>
-      <c r="E57" s="148">
+      <c r="E58" s="148">
         <f t="shared" si="9"/>
         <v>564947.77411799994</v>
       </c>
-      <c r="F57" s="133">
+      <c r="F58" s="133">
         <f t="shared" si="10"/>
         <v>49727.205881999995</v>
       </c>
-      <c r="G57" s="108">
+      <c r="G58" s="108">
         <f t="shared" si="11"/>
         <v>614674.98</v>
       </c>
-      <c r="H57" s="160">
+      <c r="H58" s="159">
         <f t="shared" si="12"/>
         <v>614674.98</v>
       </c>
-      <c r="I57" s="177">
+      <c r="I58" s="176">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J57" s="177">
+      <c r="J58" s="176">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="94" t="s">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="B58" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="112">
+      <c r="B59" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C59" s="7"/>
+      <c r="D59" s="112">
         <v>641235.69999999995</v>
       </c>
-      <c r="E58" s="148">
+      <c r="E59" s="148">
         <f t="shared" si="9"/>
         <v>589359.7318699999</v>
       </c>
-      <c r="F58" s="133">
+      <c r="F59" s="133">
         <f t="shared" si="10"/>
         <v>51875.968129999994</v>
       </c>
-      <c r="G58" s="108">
+      <c r="G59" s="108">
         <f t="shared" si="11"/>
         <v>641235.69999999995</v>
       </c>
-      <c r="H58" s="160">
+      <c r="H59" s="159">
         <f t="shared" si="12"/>
         <v>641235.69999999995</v>
       </c>
-      <c r="I58" s="177">
+      <c r="I59" s="176">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J58" s="177">
+      <c r="J59" s="176">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="128" t="s">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="B59" s="98" t="s">
-        <v>152</v>
-      </c>
-      <c r="C59" s="98"/>
-      <c r="D59" s="112">
-        <v>1101493.94</v>
-      </c>
-      <c r="E59" s="148">
+      <c r="B60" s="98" t="s">
+        <v>147</v>
+      </c>
+      <c r="C60" s="98"/>
+      <c r="D60" s="191">
+        <v>2180444.39</v>
+      </c>
+      <c r="E60" s="148">
         <f t="shared" si="9"/>
-        <v>1012383.0802539999</v>
-      </c>
-      <c r="F59" s="133">
+        <v>2004046.438849</v>
+      </c>
+      <c r="F60" s="133">
         <f t="shared" si="10"/>
-        <v>89110.859746000002</v>
-      </c>
-      <c r="G59" s="108">
-        <f t="shared" si="11"/>
-        <v>1101493.94</v>
-      </c>
-      <c r="H59" s="160">
-        <f t="shared" si="12"/>
-        <v>1101493.94</v>
-      </c>
-      <c r="I59" s="177">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="177">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="196" t="s">
-        <v>148</v>
-      </c>
-      <c r="B60" s="197"/>
-      <c r="C60" s="198"/>
-      <c r="D60" s="112">
-        <v>65500</v>
-      </c>
-      <c r="E60" s="148">
-        <f t="shared" ref="E60:E65" si="13">D60</f>
-        <v>65500</v>
-      </c>
-      <c r="F60" s="133"/>
+        <v>176397.95115100002</v>
+      </c>
       <c r="G60" s="108">
         <f t="shared" si="11"/>
-        <v>65500</v>
-      </c>
-      <c r="H60" s="160">
+        <v>2180444.39</v>
+      </c>
+      <c r="H60" s="159">
         <f t="shared" si="12"/>
-        <v>65500</v>
-      </c>
-      <c r="I60" s="177">
+        <v>2180444.39</v>
+      </c>
+      <c r="I60" s="176">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J60" s="177">
+      <c r="J60" s="176">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="188" t="s">
-        <v>150</v>
-      </c>
-      <c r="B61" s="189"/>
-      <c r="C61" s="186"/>
-      <c r="D61" s="112">
-        <v>90000</v>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" s="196" t="s">
+        <v>178</v>
+      </c>
+      <c r="B61" s="197"/>
+      <c r="C61" s="198"/>
+      <c r="D61" s="191">
+        <v>67000</v>
       </c>
       <c r="E61" s="148">
-        <f t="shared" si="13"/>
-        <v>90000</v>
+        <f t="shared" ref="E61:E67" si="13">D61</f>
+        <v>67000</v>
       </c>
       <c r="F61" s="133"/>
       <c r="G61" s="108">
         <f t="shared" si="11"/>
+        <v>67000</v>
+      </c>
+      <c r="H61" s="159">
+        <f t="shared" si="12"/>
+        <v>67000</v>
+      </c>
+      <c r="I61" s="176">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="176">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="187" t="s">
+        <v>145</v>
+      </c>
+      <c r="B62" s="188"/>
+      <c r="C62" s="185"/>
+      <c r="D62" s="112">
         <v>90000</v>
-      </c>
-      <c r="H61" s="160">
-        <f t="shared" si="12"/>
-        <v>90000</v>
-      </c>
-      <c r="I61" s="177">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J61" s="177">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B62" s="113"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="112">
-        <v>29200</v>
       </c>
       <c r="E62" s="148">
         <f t="shared" si="13"/>
-        <v>29200</v>
+        <v>90000</v>
       </c>
       <c r="F62" s="133"/>
       <c r="G62" s="108">
         <f t="shared" si="11"/>
+        <v>90000</v>
+      </c>
+      <c r="H62" s="159">
+        <f t="shared" si="12"/>
+        <v>90000</v>
+      </c>
+      <c r="I62" s="176">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J62" s="176">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B63" s="113"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="112">
         <v>29200</v>
       </c>
-      <c r="H62" s="160">
+      <c r="E63" s="148">
+        <f t="shared" si="13"/>
+        <v>29200</v>
+      </c>
+      <c r="F63" s="133"/>
+      <c r="G63" s="108">
+        <f t="shared" si="11"/>
+        <v>29200</v>
+      </c>
+      <c r="H63" s="159">
         <f t="shared" si="12"/>
         <v>29200</v>
       </c>
-      <c r="I62" s="177">
+      <c r="I63" s="176">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J62" s="177"/>
-    </row>
-    <row r="63" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="196" t="s">
-        <v>163</v>
-      </c>
-      <c r="B63" s="197"/>
-      <c r="C63" s="198"/>
-      <c r="D63" s="112">
-        <f>380000+350000</f>
-        <v>730000</v>
-      </c>
-      <c r="E63" s="148">
-        <f t="shared" ref="E63:E69" si="14">D63*91.91%</f>
-        <v>670942.99999999988</v>
-      </c>
-      <c r="F63" s="133">
-        <f t="shared" ref="F63:F69" si="15">D63*8.09%</f>
-        <v>59057</v>
-      </c>
-      <c r="G63" s="108">
-        <f t="shared" si="11"/>
-        <v>730000</v>
-      </c>
-      <c r="H63" s="160">
-        <f t="shared" si="12"/>
-        <v>729999.99999999988</v>
-      </c>
-      <c r="I63" s="177">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J63" s="177"/>
-    </row>
-    <row r="64" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J63" s="176"/>
+    </row>
+    <row r="64" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="196" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B64" s="197"/>
       <c r="C64" s="198"/>
       <c r="D64" s="112">
-        <v>120000</v>
+        <f>380000+350000</f>
+        <v>730000</v>
       </c>
       <c r="E64" s="148">
-        <f t="shared" si="14"/>
-        <v>110291.99999999999</v>
+        <f t="shared" ref="E64:E73" si="14">D64*91.91%</f>
+        <v>670942.99999999988</v>
       </c>
       <c r="F64" s="133">
-        <f t="shared" si="15"/>
-        <v>9708</v>
-      </c>
-      <c r="G64" s="108"/>
-      <c r="H64" s="160"/>
-      <c r="I64" s="177"/>
-      <c r="J64" s="177"/>
-    </row>
-    <row r="65" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="F64:F72" si="15">D64*8.09%</f>
+        <v>59057</v>
+      </c>
+      <c r="G64" s="108">
+        <f t="shared" si="11"/>
+        <v>730000</v>
+      </c>
+      <c r="H64" s="159">
+        <f t="shared" si="12"/>
+        <v>729999.99999999988</v>
+      </c>
+      <c r="I64" s="176">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J64" s="176"/>
+    </row>
+    <row r="65" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="196" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="B65" s="197"/>
       <c r="C65" s="198"/>
-      <c r="D65" s="112">
-        <v>480000</v>
+      <c r="D65" s="191">
+        <v>35500</v>
       </c>
       <c r="E65" s="148">
         <f t="shared" si="13"/>
-        <v>480000</v>
-      </c>
-      <c r="F65" s="7"/>
+        <v>35500</v>
+      </c>
+      <c r="F65" s="133"/>
       <c r="G65" s="108"/>
-      <c r="H65" s="160"/>
-      <c r="I65" s="177"/>
-      <c r="J65" s="177"/>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A66" s="98" t="s">
+      <c r="H65" s="159"/>
+      <c r="I65" s="176"/>
+      <c r="J65" s="176"/>
+    </row>
+    <row r="66" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="196" t="s">
+        <v>177</v>
+      </c>
+      <c r="B66" s="197"/>
+      <c r="C66" s="198"/>
+      <c r="D66" s="191">
+        <v>159500</v>
+      </c>
+      <c r="E66" s="148">
+        <f t="shared" si="13"/>
+        <v>159500</v>
+      </c>
+      <c r="F66" s="133"/>
+      <c r="G66" s="108"/>
+      <c r="H66" s="159"/>
+      <c r="I66" s="176"/>
+      <c r="J66" s="176"/>
+    </row>
+    <row r="67" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="196" t="s">
+        <v>175</v>
+      </c>
+      <c r="B67" s="197"/>
+      <c r="C67" s="198"/>
+      <c r="D67" s="191">
+        <v>170000</v>
+      </c>
+      <c r="E67" s="148">
+        <f t="shared" si="13"/>
+        <v>170000</v>
+      </c>
+      <c r="F67" s="7"/>
+      <c r="G67" s="108"/>
+      <c r="H67" s="159"/>
+      <c r="I67" s="176"/>
+      <c r="J67" s="176"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A68" s="98" t="s">
         <v>142</v>
       </c>
-      <c r="B66" s="98" t="s">
-        <v>162</v>
-      </c>
-      <c r="C66" s="98"/>
-      <c r="D66" s="112">
+      <c r="B68" s="98" t="s">
+        <v>155</v>
+      </c>
+      <c r="C68" s="98"/>
+      <c r="D68" s="112">
         <v>232510.18</v>
       </c>
-      <c r="E66" s="148">
+      <c r="E68" s="148">
         <f t="shared" si="14"/>
         <v>213700.10643799999</v>
       </c>
-      <c r="F66" s="133">
+      <c r="F68" s="133">
         <f t="shared" si="15"/>
         <v>18810.073561999998</v>
       </c>
-      <c r="G66" s="108">
+      <c r="G68" s="108">
         <f t="shared" si="11"/>
         <v>232510.18</v>
       </c>
-      <c r="H66" s="160">
+      <c r="H68" s="159">
         <f t="shared" si="12"/>
         <v>232510.18</v>
       </c>
-      <c r="I66" s="177">
+      <c r="I68" s="176">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J66" s="177">
+      <c r="J68" s="176">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="M66" s="191" t="s">
+      <c r="M68" s="190" t="s">
         <v>137</v>
       </c>
-      <c r="N66" s="7"/>
-      <c r="O66" s="7"/>
-      <c r="P66" s="192">
+      <c r="N68" s="7"/>
+      <c r="O68" s="7"/>
+      <c r="P68" s="191">
         <v>357622.29</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A67" s="98" t="s">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A69" s="98" t="s">
         <v>137</v>
       </c>
-      <c r="B67" s="98" t="s">
-        <v>162</v>
-      </c>
-      <c r="C67" s="98"/>
-      <c r="D67" s="112">
-        <v>357622.29</v>
-      </c>
-      <c r="E67" s="148">
-        <f t="shared" si="14"/>
-        <v>328690.64673899993</v>
-      </c>
-      <c r="F67" s="133">
-        <f t="shared" si="15"/>
-        <v>28931.643260999997</v>
-      </c>
-      <c r="G67" s="108">
-        <f t="shared" si="11"/>
-        <v>357622.29</v>
-      </c>
-      <c r="H67" s="160">
-        <f t="shared" si="12"/>
-        <v>357622.28999999992</v>
-      </c>
-      <c r="I67" s="177">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J67" s="177">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="M67" s="191" t="s">
-        <v>137</v>
-      </c>
-      <c r="N67" s="7"/>
-      <c r="O67" s="7"/>
-      <c r="P67" s="192">
-        <v>358487.12</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A68" s="98" t="s">
-        <v>137</v>
-      </c>
-      <c r="B68" s="98" t="s">
-        <v>162</v>
-      </c>
-      <c r="C68" s="98"/>
-      <c r="D68" s="112">
-        <v>358487.12</v>
-      </c>
-      <c r="E68" s="148">
-        <f t="shared" si="14"/>
-        <v>329485.51199199999</v>
-      </c>
-      <c r="F68" s="133">
-        <f t="shared" si="15"/>
-        <v>29001.608007999999</v>
-      </c>
-      <c r="G68" s="108">
-        <f t="shared" si="11"/>
-        <v>358487.12</v>
-      </c>
-      <c r="H68" s="160">
-        <f t="shared" si="12"/>
-        <v>358487.12</v>
-      </c>
-      <c r="I68" s="177">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J68" s="177">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C69" s="7"/>
-      <c r="D69" s="112">
-        <v>83283.39</v>
+      <c r="B69" s="98" t="s">
+        <v>155</v>
+      </c>
+      <c r="C69" s="98"/>
+      <c r="D69" s="191">
+        <v>141112.26</v>
       </c>
       <c r="E69" s="148">
         <f t="shared" si="14"/>
-        <v>76545.763748999991</v>
+        <v>129696.278166</v>
       </c>
       <c r="F69" s="133">
         <f t="shared" si="15"/>
-        <v>6737.6262509999997</v>
+        <v>11415.981834</v>
       </c>
       <c r="G69" s="108">
         <f t="shared" si="11"/>
+        <v>141112.26</v>
+      </c>
+      <c r="H69" s="159">
+        <f t="shared" si="12"/>
+        <v>141112.26</v>
+      </c>
+      <c r="I69" s="176">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J69" s="176">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M69" s="190" t="s">
+        <v>137</v>
+      </c>
+      <c r="N69" s="7"/>
+      <c r="O69" s="7"/>
+      <c r="P69" s="191">
+        <v>358487.12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A70" s="98" t="s">
+        <v>137</v>
+      </c>
+      <c r="B70" s="98" t="s">
+        <v>155</v>
+      </c>
+      <c r="C70" s="98"/>
+      <c r="D70" s="191">
+        <v>199992.75</v>
+      </c>
+      <c r="E70" s="148">
+        <f t="shared" si="14"/>
+        <v>183813.33652499999</v>
+      </c>
+      <c r="F70" s="133">
+        <f t="shared" si="15"/>
+        <v>16179.413474999999</v>
+      </c>
+      <c r="G70" s="108">
+        <f t="shared" si="11"/>
+        <v>199992.75</v>
+      </c>
+      <c r="H70" s="159">
+        <f t="shared" si="12"/>
+        <v>199992.75</v>
+      </c>
+      <c r="I70" s="176">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J70" s="176">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C71" s="7"/>
+      <c r="D71" s="112">
         <v>83283.39</v>
       </c>
-      <c r="H69" s="160">
+      <c r="E71" s="148">
+        <f t="shared" si="14"/>
+        <v>76545.763748999991</v>
+      </c>
+      <c r="F71" s="133">
+        <f t="shared" si="15"/>
+        <v>6737.6262509999997</v>
+      </c>
+      <c r="G71" s="108">
+        <f t="shared" si="11"/>
+        <v>83283.39</v>
+      </c>
+      <c r="H71" s="159">
         <f t="shared" si="12"/>
         <v>83283.389999999985</v>
       </c>
-      <c r="I69" s="177">
+      <c r="I71" s="176">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J69" s="177">
+      <c r="J71" s="176">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="98" t="s">
-        <v>153</v>
-      </c>
-      <c r="B70" s="113"/>
-      <c r="C70" s="161"/>
-      <c r="D70" s="112">
-        <v>300000</v>
-      </c>
-      <c r="E70" s="148">
-        <f t="shared" ref="E70" si="16">D70</f>
-        <v>300000</v>
-      </c>
-      <c r="F70" s="133"/>
-      <c r="G70" s="108">
+    <row r="72" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="190"/>
+      <c r="B72" s="113"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="191">
+        <v>260000</v>
+      </c>
+      <c r="E72" s="148">
+        <f t="shared" ref="E72:E75" si="16">D72</f>
+        <v>260000</v>
+      </c>
+      <c r="F72" s="133"/>
+      <c r="G72" s="108">
         <f t="shared" si="11"/>
-        <v>300000</v>
-      </c>
-      <c r="H70" s="160">
+        <v>260000</v>
+      </c>
+      <c r="H72" s="159">
         <f t="shared" si="12"/>
-        <v>300000</v>
-      </c>
-      <c r="I70" s="177">
+        <v>260000</v>
+      </c>
+      <c r="I72" s="176">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J70" s="177">
+      <c r="J72" s="176">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A71" s="154"/>
-      <c r="B71" s="155"/>
-      <c r="C71" s="155"/>
-      <c r="D71" s="165"/>
-      <c r="E71" s="148"/>
-      <c r="F71" s="133"/>
-      <c r="G71" s="108"/>
-      <c r="H71" s="160"/>
-      <c r="I71" t="str">
-        <f>IF(G71=H71, "", "Error")</f>
+    <row r="73" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="190"/>
+      <c r="B73" s="113"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="191">
+        <v>256310.6</v>
+      </c>
+      <c r="E73" s="148">
+        <f t="shared" si="16"/>
+        <v>256310.6</v>
+      </c>
+      <c r="F73" s="133"/>
+      <c r="G73" s="108"/>
+      <c r="H73" s="159"/>
+      <c r="I73" s="176"/>
+      <c r="J73" s="176"/>
+    </row>
+    <row r="74" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="190"/>
+      <c r="B74" s="113"/>
+      <c r="C74" s="160"/>
+      <c r="D74" s="191">
+        <v>124007</v>
+      </c>
+      <c r="E74" s="148">
+        <f t="shared" si="16"/>
+        <v>124007</v>
+      </c>
+      <c r="F74" s="133"/>
+      <c r="G74" s="108">
+        <f t="shared" si="11"/>
+        <v>124007</v>
+      </c>
+      <c r="H74" s="159">
+        <f t="shared" si="12"/>
+        <v>124007</v>
+      </c>
+      <c r="I74" s="176">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J74" s="176">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A75" s="251"/>
+      <c r="B75" s="154"/>
+      <c r="C75" s="154"/>
+      <c r="D75" s="250">
+        <v>123999.96</v>
+      </c>
+      <c r="E75" s="148">
+        <f t="shared" si="16"/>
+        <v>123999.96</v>
+      </c>
+      <c r="F75" s="133"/>
+      <c r="G75" s="108">
+        <f t="shared" si="11"/>
+        <v>123999.96</v>
+      </c>
+      <c r="H75" s="159">
+        <f t="shared" si="12"/>
+        <v>123999.96</v>
+      </c>
+      <c r="I75" t="str">
+        <f>IF(G75=H75, "", "Error")</f>
         <v/>
       </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A72" s="95" t="s">
+      <c r="J75" s="176">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A76" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="B72" s="96"/>
-      <c r="C72" s="96"/>
-      <c r="D72" s="107">
-        <f>SUM(D51:D71)</f>
-        <v>7127152.2699999986</v>
-      </c>
-      <c r="E72" s="107">
-        <f>SUM(E51:E71)</f>
-        <v>6736368.6813569991</v>
-      </c>
-      <c r="F72" s="107">
-        <f>SUM(F51:F71)</f>
-        <v>390783.58864299994</v>
-      </c>
-      <c r="G72" s="108">
-        <f>E72+F72</f>
-        <v>7127152.2699999986</v>
-      </c>
-      <c r="H72" s="149" t="str">
-        <f>IF(D72=G72, "", "Error")</f>
+      <c r="B76" s="96"/>
+      <c r="C76" s="96"/>
+      <c r="D76" s="107">
+        <f>SUM(D51:D75)</f>
+        <v>8221915.879999999</v>
+      </c>
+      <c r="E76" s="107">
+        <f>SUM(E51:E75)</f>
+        <v>7783891.0559119983</v>
+      </c>
+      <c r="F76" s="107">
+        <f>SUM(F51:F75)</f>
+        <v>438024.82408799999</v>
+      </c>
+      <c r="G76" s="108">
+        <f>E76+F76</f>
+        <v>8221915.879999998</v>
+      </c>
+      <c r="H76" s="149" t="str">
+        <f>IF(D76=G76, "", "Error")</f>
         <v/>
       </c>
-      <c r="I72" s="177">
-        <f>D72-G72</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="7"/>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="182"/>
-      <c r="E73" s="114"/>
-      <c r="F73" s="7"/>
-      <c r="H73" s="149"/>
-    </row>
-    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="182"/>
-      <c r="E74" s="113"/>
-      <c r="F74" s="7"/>
-      <c r="H74" s="149"/>
-    </row>
-    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="7"/>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="182"/>
-      <c r="E75" s="113"/>
-      <c r="F75" s="7"/>
-      <c r="H75" s="149"/>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A76" s="94" t="s">
-        <v>151</v>
-      </c>
-      <c r="B76" s="98"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="112">
-        <f>127080+80450</f>
-        <v>207530</v>
-      </c>
-      <c r="E76" s="148">
-        <f>D76*91.91%</f>
-        <v>190740.82299999997</v>
-      </c>
-      <c r="F76" s="133">
-        <f>D76*8.09%</f>
-        <v>16789.177</v>
-      </c>
-      <c r="G76" s="159"/>
-      <c r="H76" s="149"/>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I76" s="176">
+        <f>D76-G76</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
-      <c r="D77" s="112"/>
-      <c r="E77" s="163">
-        <f>D77</f>
-        <v>0</v>
-      </c>
+      <c r="D77" s="181"/>
+      <c r="E77" s="114"/>
       <c r="F77" s="7"/>
       <c r="H77" s="149"/>
-      <c r="I77" s="108"/>
-    </row>
-    <row r="78" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="95" t="s">
-        <v>16</v>
-      </c>
-      <c r="B78" s="95"/>
-      <c r="C78" s="95"/>
-      <c r="D78" s="107">
-        <f>SUM(D76:D77)</f>
-        <v>207530</v>
-      </c>
-      <c r="E78" s="107">
-        <f>SUM(E76:E77)</f>
-        <v>190740.82299999997</v>
-      </c>
-      <c r="F78" s="107">
-        <f>SUM(F76:F77)</f>
-        <v>16789.177</v>
-      </c>
-      <c r="G78" s="108">
-        <f>E78+F78</f>
-        <v>207529.99999999997</v>
-      </c>
-      <c r="H78" s="149" t="str">
-        <f>IF(D78=G78, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J78" s="108"/>
-    </row>
-    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="7"/>
+      <c r="B78" s="7"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="181"/>
+      <c r="E78" s="113"/>
+      <c r="F78" s="7"/>
+      <c r="H78" s="149"/>
+    </row>
+    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
-      <c r="D79" s="182"/>
-      <c r="E79" s="114"/>
+      <c r="D79" s="181"/>
+      <c r="E79" s="113"/>
       <c r="F79" s="7"/>
       <c r="H79" s="149"/>
     </row>
-    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="7"/>
-      <c r="B80" s="7"/>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A80" s="94" t="s">
+        <v>146</v>
+      </c>
+      <c r="B80" s="98"/>
       <c r="C80" s="7"/>
-      <c r="D80" s="182"/>
-      <c r="E80" s="113"/>
-      <c r="F80" s="7"/>
+      <c r="D80" s="191">
+        <v>124980</v>
+      </c>
+      <c r="E80" s="148">
+        <f>D80*91.91%</f>
+        <v>114869.11799999999</v>
+      </c>
+      <c r="F80" s="133">
+        <f>D80*8.09%</f>
+        <v>10110.882</v>
+      </c>
+      <c r="G80" s="158"/>
       <c r="H80" s="149"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A81" s="94" t="s">
-        <v>13</v>
-      </c>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
-      <c r="D81" s="182"/>
-      <c r="E81" s="113"/>
+      <c r="D81" s="112"/>
+      <c r="E81" s="162">
+        <f>D81</f>
+        <v>0</v>
+      </c>
       <c r="F81" s="7"/>
       <c r="H81" s="149"/>
-    </row>
-    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="94" t="s">
-        <v>14</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="112">
-        <v>246000</v>
-      </c>
-      <c r="E82" s="148">
-        <f>D82*91.91%</f>
-        <v>226098.59999999998</v>
-      </c>
-      <c r="F82" s="133">
-        <f>D82*8.09%</f>
-        <v>19901.400000000001</v>
-      </c>
-      <c r="G82" t="s">
-        <v>141</v>
-      </c>
-      <c r="H82" s="149"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="94" t="s">
-        <v>107</v>
-      </c>
+      <c r="I81" s="108"/>
+    </row>
+    <row r="82" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="95" t="s">
+        <v>16</v>
+      </c>
+      <c r="B82" s="95"/>
+      <c r="C82" s="95"/>
+      <c r="D82" s="107">
+        <f>SUM(D80:D81)</f>
+        <v>124980</v>
+      </c>
+      <c r="E82" s="107">
+        <f>SUM(E80:E81)</f>
+        <v>114869.11799999999</v>
+      </c>
+      <c r="F82" s="107">
+        <f>SUM(F80:F81)</f>
+        <v>10110.882</v>
+      </c>
+      <c r="G82" s="108">
+        <f>E82+F82</f>
+        <v>124979.99999999999</v>
+      </c>
+      <c r="H82" s="149" t="str">
+        <f>IF(D82=G82, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J82" s="108"/>
+    </row>
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
-      <c r="D83" s="112">
-        <v>30000</v>
-      </c>
-      <c r="E83" s="148">
-        <f>D83*91.91%</f>
-        <v>27572.999999999996</v>
-      </c>
-      <c r="F83" s="133">
-        <f>D83*8.09%</f>
-        <v>2427</v>
-      </c>
+      <c r="D83" s="181"/>
+      <c r="E83" s="114"/>
+      <c r="F83" s="7"/>
       <c r="H83" s="149"/>
-      <c r="J83" s="112"/>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
-      <c r="D84" s="182"/>
-      <c r="E84" s="115"/>
+      <c r="D84" s="181"/>
+      <c r="E84" s="113"/>
       <c r="F84" s="7"/>
       <c r="H84" s="149"/>
-      <c r="J84" s="108"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" s="95" t="s">
-        <v>100</v>
-      </c>
-      <c r="B85" s="95"/>
-      <c r="C85" s="95"/>
-      <c r="D85" s="107">
-        <f>SUM(D82:D84)</f>
-        <v>276000</v>
-      </c>
-      <c r="E85" s="107">
-        <f>SUM(E82:E84)</f>
-        <v>253671.59999999998</v>
-      </c>
-      <c r="F85" s="107">
-        <f>SUM(F82:F84)</f>
-        <v>22328.400000000001</v>
-      </c>
-      <c r="G85" s="108">
-        <f>E85+F85</f>
-        <v>276000</v>
-      </c>
-      <c r="H85" s="149" t="str">
-        <f>IF(D85=G85, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J85" s="108"/>
-    </row>
-    <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="7"/>
-      <c r="B86" s="7"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" s="94" t="s">
+        <v>13</v>
+      </c>
+      <c r="B85" s="7"/>
+      <c r="C85" s="7"/>
+      <c r="D85" s="181"/>
+      <c r="E85" s="113"/>
+      <c r="F85" s="7"/>
+      <c r="H85" s="149"/>
+    </row>
+    <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="94" t="s">
+        <v>14</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>116</v>
+      </c>
       <c r="C86" s="7"/>
-      <c r="D86" s="112"/>
-      <c r="E86" s="116"/>
-      <c r="F86" s="7"/>
+      <c r="D86" s="112">
+        <v>246000</v>
+      </c>
+      <c r="E86" s="148">
+        <f>D86*91.91%</f>
+        <v>226098.59999999998</v>
+      </c>
+      <c r="F86" s="133">
+        <f>D86*8.09%</f>
+        <v>19901.400000000001</v>
+      </c>
+      <c r="G86" t="s">
+        <v>141</v>
+      </c>
       <c r="H86" s="149"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="94" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
       <c r="D87" s="112">
-        <v>126577.59</v>
+        <v>30000</v>
       </c>
       <c r="E87" s="148">
         <f>D87*91.91%</f>
-        <v>116337.46296899999</v>
+        <v>27572.999999999996</v>
       </c>
       <c r="F87" s="133">
         <f>D87*8.09%</f>
-        <v>10240.127031</v>
+        <v>2427</v>
       </c>
       <c r="H87" s="149"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="94" t="s">
-        <v>102</v>
-      </c>
+      <c r="J87" s="112"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88" s="7"/>
       <c r="B88" s="7"/>
-      <c r="C88" s="121"/>
-      <c r="D88" s="112">
-        <v>44400</v>
-      </c>
-      <c r="E88" s="148">
-        <f>D88*91.91%</f>
-        <v>40808.039999999994</v>
-      </c>
-      <c r="F88" s="133">
-        <f>D88*8.09%</f>
-        <v>3591.96</v>
-      </c>
+      <c r="C88" s="7"/>
+      <c r="D88" s="181"/>
+      <c r="E88" s="115"/>
+      <c r="F88" s="7"/>
       <c r="H88" s="149"/>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J88" s="108"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="95" t="s">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="B89" s="95"/>
       <c r="C89" s="95"/>
-      <c r="D89" s="157">
-        <f>SUM(D87:D88)</f>
-        <v>170977.59</v>
-      </c>
-      <c r="E89" s="146">
-        <f t="shared" ref="E89:F89" si="17">SUM(E87:E88)</f>
-        <v>157145.50296899996</v>
-      </c>
-      <c r="F89" s="146">
-        <f t="shared" si="17"/>
-        <v>13832.087030999999</v>
+      <c r="D89" s="107">
+        <f>SUM(D86:D88)</f>
+        <v>276000</v>
+      </c>
+      <c r="E89" s="107">
+        <f>SUM(E86:E88)</f>
+        <v>253671.59999999998</v>
+      </c>
+      <c r="F89" s="107">
+        <f>SUM(F86:F88)</f>
+        <v>22328.400000000001</v>
       </c>
       <c r="G89" s="108">
         <f>E89+F89</f>
-        <v>170977.58999999997</v>
+        <v>276000</v>
       </c>
       <c r="H89" s="149" t="str">
         <f>IF(D89=G89, "", "Error")</f>
         <v/>
       </c>
-    </row>
-    <row r="90" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J89" s="108"/>
+    </row>
+    <row r="90" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
-      <c r="D90" s="183"/>
-      <c r="E90" s="12"/>
+      <c r="D90" s="112"/>
+      <c r="E90" s="116"/>
       <c r="F90" s="7"/>
       <c r="H90" s="149"/>
     </row>
-    <row r="91" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="99" t="s">
-        <v>133</v>
-      </c>
-      <c r="B91" s="99"/>
-      <c r="C91" s="99"/>
-      <c r="D91" s="184"/>
-      <c r="E91" s="117">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A91" s="94" t="s">
+        <v>101</v>
+      </c>
+      <c r="B91" s="7"/>
+      <c r="C91" s="7"/>
+      <c r="D91" s="112">
+        <v>126577.59</v>
+      </c>
+      <c r="E91" s="148">
         <f>D91*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F91" s="135">
+        <v>116337.46296899999</v>
+      </c>
+      <c r="F91" s="133">
         <f>D91*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G91" s="108">
-        <f>E91+F91</f>
-        <v>0</v>
-      </c>
-      <c r="H91" s="149" t="str">
-        <f>IF(D91=G91, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="1"/>
-      <c r="D92" s="181"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="10"/>
-      <c r="G92" s="156"/>
+        <v>10240.127031</v>
+      </c>
+      <c r="H91" s="149"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="B92" s="7"/>
+      <c r="C92" s="121"/>
+      <c r="D92" s="112">
+        <v>44400</v>
+      </c>
+      <c r="E92" s="148">
+        <f>D92*91.91%</f>
+        <v>40808.039999999994</v>
+      </c>
+      <c r="F92" s="133">
+        <f>D92*8.09%</f>
+        <v>3591.96</v>
+      </c>
       <c r="H92" s="149"/>
     </row>
-    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B93" s="60"/>
-      <c r="C93" s="5"/>
-      <c r="D93" s="185">
-        <f>SUM(D91+D89+D85+D78+D72+D49+D32+D27+D44)</f>
-        <v>9894594.4100000001</v>
-      </c>
-      <c r="E93" s="147">
-        <f>SUM(E91+E89+E85+E78+E72+E49+E32+E27+E44)</f>
-        <v>9279924.7522309981</v>
-      </c>
-      <c r="F93" s="147">
-        <f>SUM(F91+F89+F85+F78+F72+F49+F32+F27+F44)</f>
-        <v>614669.65776899992</v>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A93" s="95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" s="95"/>
+      <c r="C93" s="95"/>
+      <c r="D93" s="156">
+        <f>SUM(D91:D92)</f>
+        <v>170977.59</v>
+      </c>
+      <c r="E93" s="146">
+        <f t="shared" ref="E93:F93" si="17">SUM(E91:E92)</f>
+        <v>157145.50296899996</v>
+      </c>
+      <c r="F93" s="146">
+        <f t="shared" si="17"/>
+        <v>13832.087030999999</v>
       </c>
       <c r="G93" s="108">
         <f>E93+F93</f>
-        <v>9894594.4099999983</v>
+        <v>170977.58999999997</v>
       </c>
       <c r="H93" s="149" t="str">
         <f>IF(D93=G93, "", "Error")</f>
         <v/>
       </c>
-      <c r="I93" s="177">
-        <f>D93-G93</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D94" s="181"/>
-      <c r="E94" s="108"/>
-    </row>
-    <row r="95" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="141" t="s">
+    </row>
+    <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="7"/>
+      <c r="B94" s="7"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="182"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="7"/>
+      <c r="H94" s="149"/>
+    </row>
+    <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="99" t="s">
+        <v>133</v>
+      </c>
+      <c r="B95" s="99"/>
+      <c r="C95" s="99"/>
+      <c r="D95" s="183"/>
+      <c r="E95" s="117">
+        <f>D95*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F95" s="135">
+        <f>D95*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G95" s="108">
+        <f>E95+F95</f>
+        <v>0</v>
+      </c>
+      <c r="H95" s="149" t="str">
+        <f>IF(D95=G95, "", "Error")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="1"/>
+      <c r="D96" s="180"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="10"/>
+      <c r="G96" s="155"/>
+      <c r="H96" s="149"/>
+    </row>
+    <row r="97" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B97" s="60"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="184">
+        <f>SUM(D95+D93+D89+D82+D76+D49+D32+D27+D44)</f>
+        <v>10825310.289999999</v>
+      </c>
+      <c r="E97" s="147">
+        <f>SUM(E95+E93+E89+E82+E76+E49+E32+E27+E44)</f>
+        <v>10176670.858142998</v>
+      </c>
+      <c r="F97" s="147">
+        <f>SUM(F95+F93+F89+F82+F76+F49+F32+F27+F44)</f>
+        <v>648639.43185699999</v>
+      </c>
+      <c r="G97" s="108">
+        <f>E97+F97</f>
+        <v>10825310.289999997</v>
+      </c>
+      <c r="H97" s="149" t="str">
+        <f>IF(D97=G97, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="I97" s="176">
+        <f>D97-G97</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D98" s="180"/>
+      <c r="E98" s="108"/>
+    </row>
+    <row r="99" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="141" t="s">
         <v>120</v>
       </c>
-      <c r="B95" s="140"/>
-      <c r="C95" s="140"/>
-      <c r="E95" s="108"/>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A96" s="1"/>
-      <c r="C96" s="138"/>
-      <c r="E96" s="108"/>
-    </row>
-    <row r="97" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="1"/>
-      <c r="C97" s="138"/>
-      <c r="E97" s="108"/>
-    </row>
-    <row r="98" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="142" t="s">
+      <c r="B99" s="140"/>
+      <c r="C99" s="140"/>
+      <c r="E99" s="108"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A100" s="1"/>
+      <c r="C100" s="138"/>
+      <c r="E100" s="108"/>
+    </row>
+    <row r="101" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="1"/>
+      <c r="C101" s="138"/>
+      <c r="E101" s="108"/>
+    </row>
+    <row r="102" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="142" t="s">
         <v>29</v>
       </c>
-      <c r="B98" s="143"/>
-      <c r="C98" s="139">
-        <f>SUM(C96:C97)</f>
-        <v>0</v>
-      </c>
-      <c r="E98" s="108"/>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E99" s="108"/>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E100" s="136"/>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="222" t="s">
+      <c r="B102" s="143"/>
+      <c r="C102" s="139">
+        <f>SUM(C100:C101)</f>
+        <v>0</v>
+      </c>
+      <c r="E102" s="108"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E103" s="108"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E104" s="136"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A105" s="222" t="s">
         <v>113</v>
       </c>
-      <c r="B101" s="223"/>
-      <c r="C101" s="223"/>
-      <c r="D101" s="223"/>
-      <c r="E101" s="170" t="s">
+      <c r="B105" s="223"/>
+      <c r="C105" s="223"/>
+      <c r="D105" s="223"/>
+      <c r="E105" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F101" s="171" t="s">
+      <c r="F105" s="170" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="219"/>
-      <c r="B102" s="220"/>
-      <c r="C102" s="221"/>
-      <c r="D102" s="165"/>
-      <c r="E102" s="148"/>
-      <c r="F102" s="133"/>
-    </row>
-    <row r="103" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="216"/>
-      <c r="B103" s="217"/>
-      <c r="C103" s="172"/>
-      <c r="D103" s="112"/>
-      <c r="E103" s="148">
-        <f t="shared" ref="E103:E104" si="18">D103*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F103" s="133">
-        <f t="shared" ref="F103:F104" si="19">D103*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="216"/>
-      <c r="B104" s="217"/>
-      <c r="C104" s="172"/>
-      <c r="D104" s="112"/>
-      <c r="E104" s="148">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="219"/>
+      <c r="B106" s="220"/>
+      <c r="C106" s="221"/>
+      <c r="D106" s="164"/>
+      <c r="E106" s="148"/>
+      <c r="F106" s="133"/>
+    </row>
+    <row r="107" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="216"/>
+      <c r="B107" s="217"/>
+      <c r="C107" s="171"/>
+      <c r="D107" s="112"/>
+      <c r="E107" s="148">
+        <f t="shared" ref="E107:E108" si="18">D107*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F107" s="133">
+        <f t="shared" ref="F107:F108" si="19">D107*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="216"/>
+      <c r="B108" s="217"/>
+      <c r="C108" s="171"/>
+      <c r="D108" s="112"/>
+      <c r="E108" s="148">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="F104" s="133">
+      <c r="F108" s="133">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="216"/>
-      <c r="B105" s="217"/>
-      <c r="C105" s="218"/>
-      <c r="D105" s="112"/>
-      <c r="E105" s="148">
-        <f>D105*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F105" s="133">
-        <f>D105*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="213" t="s">
+    <row r="109" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="216"/>
+      <c r="B109" s="217"/>
+      <c r="C109" s="218"/>
+      <c r="D109" s="112"/>
+      <c r="E109" s="148">
+        <f>D109*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F109" s="133">
+        <f>D109*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A110" s="213" t="s">
         <v>29</v>
       </c>
-      <c r="B106" s="214"/>
-      <c r="C106" s="215"/>
-      <c r="D106" s="169">
-        <f>SUM(D102:D105)</f>
-        <v>0</v>
-      </c>
-      <c r="E106" s="169">
-        <f>SUM(E102:E105)</f>
-        <v>0</v>
-      </c>
-      <c r="F106" s="169">
-        <f>SUM(F102:F105)</f>
-        <v>0</v>
-      </c>
-      <c r="H106" s="108">
-        <f>E106+F106</f>
-        <v>0</v>
-      </c>
-      <c r="I106" s="149" t="str">
-        <f>IF(D106=H106, "", "Error")</f>
+      <c r="B110" s="214"/>
+      <c r="C110" s="215"/>
+      <c r="D110" s="168">
+        <f>SUM(D106:D109)</f>
+        <v>0</v>
+      </c>
+      <c r="E110" s="168">
+        <f>SUM(E106:E109)</f>
+        <v>0</v>
+      </c>
+      <c r="F110" s="168">
+        <f>SUM(F106:F109)</f>
+        <v>0</v>
+      </c>
+      <c r="H110" s="108">
+        <f>E110+F110</f>
+        <v>0</v>
+      </c>
+      <c r="I110" s="149" t="str">
+        <f>IF(D110=H110, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E108" s="108"/>
-    </row>
-    <row r="109" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="102" t="s">
+    <row r="112" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E112" s="108"/>
+    </row>
+    <row r="113" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="102" t="s">
         <v>104</v>
       </c>
-      <c r="B109" s="103">
-        <f>D93</f>
-        <v>9894594.4100000001</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="104" t="s">
+      <c r="B113" s="103">
+        <f>D97</f>
+        <v>10825310.289999999</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="104" t="s">
         <v>106</v>
       </c>
-      <c r="B110" s="105">
-        <f>D93-D91</f>
-        <v>9894594.4100000001</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D111" s="203"/>
-      <c r="E111" s="203"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="74" t="s">
-        <v>90</v>
-      </c>
-      <c r="B112" s="75"/>
-      <c r="C112" s="76"/>
-      <c r="D112" s="203"/>
-      <c r="E112" s="203"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="B113" s="11">
-        <v>-630321.16476135515</v>
-      </c>
-      <c r="C113" s="78"/>
-      <c r="D113" s="203"/>
-      <c r="E113" s="203"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="79" t="s">
-        <v>92</v>
-      </c>
-      <c r="B114" s="92">
-        <f>PRORRATEO!G52</f>
-        <v>6975889.7925080024</v>
-      </c>
-      <c r="C114" s="78" t="s">
-        <v>93</v>
-      </c>
-      <c r="D114" s="203"/>
-      <c r="E114" s="203"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="79" t="s">
-        <v>115</v>
-      </c>
-      <c r="B115" s="174">
-        <f>-B110</f>
-        <v>-9894594.4100000001</v>
-      </c>
-      <c r="C115" s="76"/>
+      <c r="B114" s="105">
+        <f>D97-D95</f>
+        <v>10825310.289999999</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D115" s="203"/>
       <c r="E115" s="203"/>
-      <c r="G115" s="112"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="79" t="s">
-        <v>114</v>
-      </c>
-      <c r="B116" s="174">
-        <f>-D106</f>
-        <v>0</v>
-      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" s="74" t="s">
+        <v>90</v>
+      </c>
+      <c r="B116" s="75"/>
       <c r="C116" s="76"/>
       <c r="D116" s="203"/>
       <c r="E116" s="203"/>
-      <c r="G116" s="124"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="79" t="s">
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="B117" s="11">
+        <v>-630321.16476135515</v>
+      </c>
+      <c r="C117" s="78"/>
+      <c r="D117" s="203"/>
+      <c r="E117" s="203"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" s="79" t="s">
+        <v>92</v>
+      </c>
+      <c r="B118" s="92">
+        <f>PRORRATEO!G52</f>
+        <v>6975889.7925080024</v>
+      </c>
+      <c r="C118" s="78" t="s">
+        <v>93</v>
+      </c>
+      <c r="D118" s="203"/>
+      <c r="E118" s="203"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" s="79" t="s">
+        <v>115</v>
+      </c>
+      <c r="B119" s="173">
+        <f>-B114</f>
+        <v>-10825310.289999999</v>
+      </c>
+      <c r="C119" s="76"/>
+      <c r="D119" s="203"/>
+      <c r="E119" s="203"/>
+      <c r="G119" s="112"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" s="79" t="s">
+        <v>114</v>
+      </c>
+      <c r="B120" s="173">
+        <f>-D110</f>
+        <v>0</v>
+      </c>
+      <c r="C120" s="76"/>
+      <c r="D120" s="203"/>
+      <c r="E120" s="203"/>
+      <c r="G120" s="124"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="B117" s="174">
-        <f>-B124</f>
+      <c r="B121" s="173">
+        <f>-B128</f>
         <v>-50000</v>
       </c>
-      <c r="C117" s="80"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="79" t="s">
+      <c r="C121" s="80"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="B118" s="93">
-        <f>-C98</f>
-        <v>0</v>
-      </c>
-      <c r="C118" s="80"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="79"/>
-      <c r="B119" s="75"/>
-      <c r="C119" s="80"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="77" t="s">
+      <c r="B122" s="93">
+        <f>-C102</f>
+        <v>0</v>
+      </c>
+      <c r="C122" s="80"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" s="79"/>
+      <c r="B123" s="75"/>
+      <c r="C123" s="80"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="B120" s="81">
-        <f>SUM(B113:B119)</f>
-        <v>-3599025.7822533529</v>
-      </c>
-      <c r="C120" s="153"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="80"/>
-      <c r="C121" s="76"/>
-      <c r="D121" s="83"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C122" s="76"/>
-      <c r="D122" s="108"/>
-      <c r="E122" s="177"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="74" t="s">
+      <c r="B124" s="81">
+        <f>SUM(B117:B123)</f>
+        <v>-4529741.6622533519</v>
+      </c>
+      <c r="C124" s="153"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" s="80"/>
+      <c r="C125" s="76"/>
+      <c r="D125" s="83"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C126" s="76"/>
+      <c r="D126" s="108"/>
+      <c r="E126" s="176"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="B123" s="11">
+      <c r="B127" s="11">
         <v>-365694.54000000004</v>
       </c>
-      <c r="C123" s="82"/>
-      <c r="D123" s="177"/>
-      <c r="E123" s="177"/>
-      <c r="F123" s="177"/>
-    </row>
-    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="77" t="s">
-        <v>178</v>
-      </c>
-      <c r="B124" s="93">
+      <c r="C127" s="82"/>
+      <c r="D127" s="176"/>
+      <c r="E127" s="176"/>
+      <c r="F127" s="176"/>
+    </row>
+    <row r="128" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="77" t="s">
+        <v>174</v>
+      </c>
+      <c r="B128" s="93">
         <v>50000</v>
       </c>
-      <c r="C124" s="82"/>
-      <c r="D124" s="177"/>
-      <c r="E124" s="190"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="77" t="s">
-        <v>156</v>
-      </c>
-      <c r="B125" s="174">
+      <c r="C128" s="82"/>
+      <c r="D128" s="176"/>
+      <c r="E128" s="189"/>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A129" s="77" t="s">
+        <v>150</v>
+      </c>
+      <c r="B129" s="173">
         <v>-37000</v>
       </c>
-      <c r="C125" s="82"/>
-      <c r="E125" s="108"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126" s="77"/>
-      <c r="B126" s="174"/>
-      <c r="C126" s="82"/>
-      <c r="E126" s="108"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127" s="100" t="s">
+      <c r="C129" s="82"/>
+      <c r="E129" s="108"/>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A130" s="77"/>
+      <c r="B130" s="173"/>
+      <c r="C130" s="82"/>
+      <c r="E130" s="108"/>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A131" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="B127" s="101">
-        <f>SUM(B123:B126)</f>
+      <c r="B131" s="101">
+        <f>SUM(B127:B130)</f>
         <v>-352694.54000000004</v>
       </c>
-      <c r="C127" s="82"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C128" s="83"/>
-      <c r="D128" s="177"/>
-    </row>
-    <row r="129" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B129" s="80"/>
-      <c r="C129" s="76"/>
-    </row>
-    <row r="131" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="N131" s="12"/>
-    </row>
-    <row r="134" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B134" s="202"/>
-      <c r="C134" s="202"/>
-      <c r="D134" s="202"/>
-      <c r="E134" s="202"/>
-    </row>
-    <row r="135" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B135" s="202"/>
-      <c r="C135" s="202"/>
-      <c r="D135" s="202"/>
-      <c r="E135" s="202"/>
-    </row>
-    <row r="136" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B136" s="202"/>
-      <c r="C136" s="202"/>
-      <c r="D136" s="202"/>
-      <c r="E136" s="202"/>
-    </row>
-    <row r="137" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B137" s="202"/>
-      <c r="C137" s="202"/>
-      <c r="D137" s="202"/>
-      <c r="E137" s="202"/>
-    </row>
-    <row r="138" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C131" s="82"/>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C132" s="83"/>
+      <c r="D132" s="176"/>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B133" s="80"/>
+      <c r="C133" s="76"/>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N135" s="12"/>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B138" s="202"/>
       <c r="C138" s="202"/>
       <c r="D138" s="202"/>
       <c r="E138" s="202"/>
     </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B139" s="202"/>
+      <c r="C139" s="202"/>
+      <c r="D139" s="202"/>
+      <c r="E139" s="202"/>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B140" s="202"/>
+      <c r="C140" s="202"/>
+      <c r="D140" s="202"/>
+      <c r="E140" s="202"/>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B141" s="202"/>
+      <c r="C141" s="202"/>
+      <c r="D141" s="202"/>
+      <c r="E141" s="202"/>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B142" s="202"/>
+      <c r="C142" s="202"/>
+      <c r="D142" s="202"/>
+      <c r="E142" s="202"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="B134:E138"/>
-    <mergeCell ref="D111:E116"/>
+  <mergeCells count="15">
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="B138:E142"/>
+    <mergeCell ref="D115:E120"/>
     <mergeCell ref="B14:D17"/>
+    <mergeCell ref="A110:C110"/>
+    <mergeCell ref="A109:C109"/>
     <mergeCell ref="A106:C106"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="A102:C102"/>
-    <mergeCell ref="A101:D101"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A104:B104"/>
-    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="A105:D105"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A67:C67"/>
     <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A66:C66"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4173,26 +4272,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" customWidth="1"/>
     <col min="6" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4208,18 +4307,18 @@
       <c r="K1" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="L1" s="231">
-        <f>RESUMEN!D93</f>
-        <v>9894594.4100000001</v>
-      </c>
-      <c r="M1" s="232"/>
+      <c r="L1" s="227">
+        <f>RESUMEN!D97</f>
+        <v>10825310.289999999</v>
+      </c>
+      <c r="M1" s="228"/>
       <c r="N1" s="151"/>
       <c r="O1" s="134">
         <f>L1*8.09%</f>
-        <v>800472.68776899995</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+        <v>875767.60246099997</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4241,13 +4340,13 @@
       <c r="N2" s="152"/>
       <c r="O2" s="134">
         <f>O1-K7-553-50-86-8</f>
-        <v>185106.03000000003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>260400.94469200005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="str">
         <f>RESUMEN!C5</f>
-        <v>VTO: 14/08</v>
+        <v>VTO: 15/09</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -4263,13 +4362,13 @@
       </c>
       <c r="L3" s="8"/>
       <c r="M3" s="127">
-        <f>RESUMEN!D106</f>
+        <f>RESUMEN!D110</f>
         <v>0</v>
       </c>
       <c r="N3" s="150"/>
       <c r="O3" s="73"/>
     </row>
-    <row r="4" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -4292,17 +4391,17 @@
       </c>
       <c r="N4" s="123"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="224" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="226" t="s">
+      <c r="B5" s="238" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="224" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="228" t="s">
+      <c r="D5" s="236" t="s">
         <v>22</v>
       </c>
       <c r="E5" s="224" t="s">
@@ -4314,45 +4413,45 @@
       <c r="G5" s="224" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="235" t="s">
+      <c r="H5" s="231" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="228" t="s">
+      <c r="I5" s="236" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="233" t="s">
+      <c r="J5" s="229" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="233" t="s">
+      <c r="K5" s="229" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="238" t="s">
+      <c r="L5" s="234" t="s">
         <v>123</v>
       </c>
-      <c r="M5" s="233" t="s">
+      <c r="M5" s="229" t="s">
         <v>67</v>
       </c>
-      <c r="N5" s="233" t="s">
+      <c r="N5" s="229" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="225"/>
-      <c r="B6" s="227"/>
+      <c r="B6" s="239"/>
       <c r="C6" s="225"/>
-      <c r="D6" s="229"/>
+      <c r="D6" s="240"/>
       <c r="E6" s="225"/>
       <c r="F6" s="225"/>
       <c r="G6" s="225"/>
-      <c r="H6" s="236"/>
-      <c r="I6" s="240"/>
-      <c r="J6" s="234"/>
-      <c r="K6" s="237"/>
-      <c r="L6" s="239"/>
-      <c r="M6" s="237"/>
-      <c r="N6" s="234"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H6" s="232"/>
+      <c r="I6" s="237"/>
+      <c r="J6" s="230"/>
+      <c r="K6" s="233"/>
+      <c r="L6" s="235"/>
+      <c r="M6" s="233"/>
+      <c r="N6" s="230"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>33</v>
       </c>
@@ -4369,7 +4468,7 @@
       <c r="F7" s="88">
         <v>412157.680108</v>
       </c>
-      <c r="G7" s="194">
+      <c r="G7" s="193">
         <f>F7</f>
         <v>412157.680108</v>
       </c>
@@ -4396,7 +4495,7 @@
         <v>651549.83723513992</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>35</v>
       </c>
@@ -4413,7 +4512,7 @@
       <c r="F8" s="88">
         <v>173244.21501451588</v>
       </c>
-      <c r="G8" s="194">
+      <c r="G8" s="193">
         <v>175000</v>
       </c>
       <c r="H8" s="130">
@@ -4431,7 +4530,7 @@
         <f>M$2*E8 /100</f>
         <v>182803.90700000001</v>
       </c>
-      <c r="L8" s="164">
+      <c r="L8" s="163">
         <f>J$3*E8%+J$4</f>
         <v>0</v>
       </c>
@@ -4444,7 +4543,7 @@
         <v>191911.00933538683</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
@@ -4461,7 +4560,7 @@
       <c r="F9" s="88">
         <v>326579.3682842633</v>
       </c>
-      <c r="G9" s="195">
+      <c r="G9" s="194">
         <f>366606-G34</f>
         <v>325999.62</v>
       </c>
@@ -4480,7 +4579,7 @@
         <f t="shared" ref="K9:K51" si="3">M$2*E9 /100</f>
         <v>348237.30700000003</v>
       </c>
-      <c r="L9" s="164">
+      <c r="L9" s="163">
         <f t="shared" ref="L9:L50" si="4">J$3*E9%+J$4</f>
         <v>0</v>
       </c>
@@ -4493,7 +4592,7 @@
         <v>369746.07860131911</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>38</v>
       </c>
@@ -4510,7 +4609,7 @@
       <c r="F10" s="88">
         <v>257752.68620596873</v>
       </c>
-      <c r="G10" s="194">
+      <c r="G10" s="193">
         <v>213558</v>
       </c>
       <c r="H10" s="130">
@@ -4528,7 +4627,7 @@
         <f t="shared" si="3"/>
         <v>234915.42799999996</v>
       </c>
-      <c r="L10" s="164">
+      <c r="L10" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4541,7 +4640,7 @@
         <v>295856.72105832677</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>38</v>
       </c>
@@ -4558,7 +4657,7 @@
       <c r="F11" s="88">
         <v>269508.94160000002</v>
       </c>
-      <c r="G11" s="194">
+      <c r="G11" s="193">
         <f>F11</f>
         <v>269508.94160000002</v>
       </c>
@@ -4577,7 +4676,7 @@
         <f t="shared" si="3"/>
         <v>283718.28100000002</v>
       </c>
-      <c r="L11" s="164">
+      <c r="L11" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4591,7 +4690,7 @@
       </c>
       <c r="P11" s="108"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>41</v>
       </c>
@@ -4608,7 +4707,7 @@
       <c r="F12" s="88">
         <v>223559.48</v>
       </c>
-      <c r="G12" s="195">
+      <c r="G12" s="194">
         <f>F12</f>
         <v>223559.48</v>
       </c>
@@ -4627,7 +4726,7 @@
         <f t="shared" si="3"/>
         <v>234915.42799999996</v>
       </c>
-      <c r="L12" s="164">
+      <c r="L12" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4640,7 +4739,7 @@
         <v>249010.35367999994</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>41</v>
       </c>
@@ -4657,7 +4756,7 @@
       <c r="F13" s="88">
         <v>308384.31311924173</v>
       </c>
-      <c r="G13" s="195">
+      <c r="G13" s="194">
         <f>352750-G50</f>
         <v>308383.77</v>
       </c>
@@ -4676,7 +4775,7 @@
         <f t="shared" si="3"/>
         <v>283718.28100000002</v>
       </c>
-      <c r="L13" s="164">
+      <c r="L13" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4689,7 +4788,7 @@
         <v>300741.95356639626</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>43</v>
       </c>
@@ -4706,7 +4805,7 @@
       <c r="F14" s="88">
         <v>223150.98080000002</v>
       </c>
-      <c r="G14" s="194">
+      <c r="G14" s="193">
         <f>214000</f>
         <v>214000</v>
       </c>
@@ -4725,7 +4824,7 @@
         <f t="shared" si="3"/>
         <v>234915.42799999996</v>
       </c>
-      <c r="L14" s="164">
+      <c r="L14" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4738,7 +4837,7 @@
         <v>258710.39332799998</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>43</v>
       </c>
@@ -4755,7 +4854,7 @@
       <c r="F15" s="88">
         <v>257925.38604653394</v>
       </c>
-      <c r="G15" s="195">
+      <c r="G15" s="194">
         <f>295524-G35</f>
         <v>257925.5</v>
       </c>
@@ -4774,7 +4873,7 @@
         <f t="shared" si="3"/>
         <v>283718.28100000002</v>
       </c>
-      <c r="L15" s="164">
+      <c r="L15" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4787,7 +4886,7 @@
         <v>300741.25706932601</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
@@ -4804,7 +4903,7 @@
       <c r="F16" s="88">
         <v>213560.22460066073</v>
       </c>
-      <c r="G16" s="249">
+      <c r="G16" s="195">
         <f>250407-G49</f>
         <v>213560.47</v>
       </c>
@@ -4823,7 +4922,7 @@
         <f t="shared" si="3"/>
         <v>234915.42799999996</v>
       </c>
-      <c r="L16" s="164">
+      <c r="L16" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4836,10 +4935,10 @@
         <v>249010.09355670033</v>
       </c>
       <c r="P16" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>46</v>
       </c>
@@ -4856,7 +4955,7 @@
       <c r="F17" s="88">
         <v>257925.83371111474</v>
       </c>
-      <c r="G17" s="194">
+      <c r="G17" s="193">
         <f>332372-G47-G48</f>
         <v>257926.97</v>
       </c>
@@ -4875,7 +4974,7 @@
         <f t="shared" si="3"/>
         <v>283718.28100000002</v>
       </c>
-      <c r="L17" s="164">
+      <c r="L17" s="163">
         <v>10000</v>
       </c>
       <c r="M17" s="6">
@@ -4887,7 +4986,7 @@
         <v>311340.17339378165</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>48</v>
       </c>
@@ -4904,7 +5003,7 @@
       <c r="F18" s="88">
         <v>223827.22398325134</v>
       </c>
-      <c r="G18" s="194">
+      <c r="G18" s="193">
         <f>270000-G51</f>
         <v>227137.71</v>
       </c>
@@ -4923,7 +5022,7 @@
         <f t="shared" si="3"/>
         <v>234915.42799999996</v>
       </c>
-      <c r="L18" s="164">
+      <c r="L18" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4936,7 +5035,7 @@
         <v>245501.23850224639</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>48</v>
       </c>
@@ -4953,7 +5052,7 @@
       <c r="F19" s="88">
         <v>257926.19276516797</v>
       </c>
-      <c r="G19" s="195">
+      <c r="G19" s="194">
         <f>298532-G41</f>
         <v>257925.62</v>
       </c>
@@ -4972,7 +5071,7 @@
         <f t="shared" si="3"/>
         <v>283718.28100000002</v>
       </c>
-      <c r="L19" s="164">
+      <c r="L19" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4985,7 +5084,7 @@
         <v>300741.98499107809</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
@@ -5002,7 +5101,7 @@
       <c r="F20" s="88">
         <v>224805.06990707474</v>
       </c>
-      <c r="G20" s="194">
+      <c r="G20" s="193">
         <f>250406-G38</f>
         <v>213559.47</v>
       </c>
@@ -5021,7 +5120,7 @@
         <f t="shared" si="3"/>
         <v>234915.42799999996</v>
       </c>
-      <c r="L20" s="164">
+      <c r="L20" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5034,7 +5133,7 @@
         <v>260930.68958149917</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
@@ -5051,7 +5150,7 @@
       <c r="F21" s="88">
         <v>257925.59509179581</v>
       </c>
-      <c r="G21" s="194">
+      <c r="G21" s="193">
         <f>298532-G45</f>
         <v>257925.62</v>
       </c>
@@ -5070,7 +5169,7 @@
         <f t="shared" si="3"/>
         <v>283718.28100000002</v>
       </c>
-      <c r="L21" s="164">
+      <c r="L21" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5083,7 +5182,7 @@
         <v>300741.35145730362</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>54</v>
       </c>
@@ -5091,7 +5190,7 @@
       <c r="C22" s="7">
         <v>38</v>
       </c>
-      <c r="D22" s="166" t="s">
+      <c r="D22" s="165" t="s">
         <v>128</v>
       </c>
       <c r="E22" s="7">
@@ -5100,7 +5199,7 @@
       <c r="F22" s="88">
         <v>223150.98080000002</v>
       </c>
-      <c r="G22" s="194">
+      <c r="G22" s="193">
         <f>F22</f>
         <v>223150.98080000002</v>
       </c>
@@ -5119,7 +5218,7 @@
         <f t="shared" si="3"/>
         <v>234915.42799999996</v>
       </c>
-      <c r="L22" s="164">
+      <c r="L22" s="163">
         <v>20000</v>
       </c>
       <c r="M22" s="6">
@@ -5131,7 +5230,7 @@
         <v>270210.35367999994</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>54</v>
       </c>
@@ -5148,7 +5247,7 @@
       <c r="F23" s="88">
         <v>240712.43648409515</v>
       </c>
-      <c r="G23" s="195">
+      <c r="G23" s="194">
         <f>280000-G46</f>
         <v>242401.5</v>
       </c>
@@ -5167,7 +5266,7 @@
         <f t="shared" si="3"/>
         <v>283718.28100000002</v>
       </c>
-      <c r="L23" s="164">
+      <c r="L23" s="163">
         <v>10000</v>
       </c>
       <c r="M23" s="6">
@@ -5179,7 +5278,7 @@
         <v>309550.97053314082</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>56</v>
       </c>
@@ -5196,7 +5295,7 @@
       <c r="F24" s="88">
         <v>206644.78747107476</v>
       </c>
-      <c r="G24" s="194">
+      <c r="G24" s="193">
         <f>245000-G37</f>
         <v>208153.47</v>
       </c>
@@ -5204,7 +5303,7 @@
         <f t="shared" si="0"/>
         <v>-1508.6825289252447</v>
       </c>
-      <c r="I24" s="178">
+      <c r="I24" s="177">
         <v>7</v>
       </c>
       <c r="J24" s="88">
@@ -5215,7 +5314,7 @@
         <f t="shared" si="3"/>
         <v>234915.42799999996</v>
       </c>
-      <c r="L24" s="164">
+      <c r="L24" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5228,7 +5327,7 @@
         <v>247411.1501993392</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>56</v>
       </c>
@@ -5245,7 +5344,7 @@
       <c r="F25" s="88">
         <v>267925.70999999996</v>
       </c>
-      <c r="G25" s="194">
+      <c r="G25" s="193">
         <f>F25</f>
         <v>267925.70999999996</v>
       </c>
@@ -5264,7 +5363,7 @@
         <f t="shared" si="3"/>
         <v>283718.28100000002</v>
       </c>
-      <c r="L25" s="164">
+      <c r="L25" s="163">
         <f>10000+K25*0.1</f>
         <v>38371.828099999999</v>
       </c>
@@ -5277,7 +5376,7 @@
         <v>341415.51564599999</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>59</v>
       </c>
@@ -5294,7 +5393,7 @@
       <c r="F26" s="88">
         <v>3958.5408160369843</v>
       </c>
-      <c r="G26" s="195">
+      <c r="G26" s="194">
         <f>119563+3959-G30-G31-G36</f>
         <v>3958.7699999999895</v>
       </c>
@@ -5313,7 +5412,7 @@
         <f t="shared" si="3"/>
         <v>496300.2</v>
       </c>
-      <c r="L26" s="164">
+      <c r="L26" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5326,7 +5425,7 @@
         <v>526077.96906499926</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>61</v>
       </c>
@@ -5343,7 +5442,7 @@
       <c r="F27" s="88">
         <v>442910.4355352656</v>
       </c>
-      <c r="G27" s="194">
+      <c r="G27" s="193">
         <f>526378-G39-G40</f>
         <v>439149.48000000004</v>
       </c>
@@ -5362,7 +5461,7 @@
         <f t="shared" si="3"/>
         <v>487201.36299999995</v>
       </c>
-      <c r="L27" s="164">
+      <c r="L27" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5375,7 +5474,7 @@
         <v>520420.05764738144</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>63</v>
       </c>
@@ -5392,7 +5491,7 @@
       <c r="F28" s="88">
         <v>466343.09357654094</v>
       </c>
-      <c r="G28" s="194">
+      <c r="G28" s="193">
         <f>523000-G32-G33</f>
         <v>443291.18</v>
       </c>
@@ -5411,7 +5510,7 @@
         <f t="shared" si="3"/>
         <v>487201.36299999995</v>
       </c>
-      <c r="L28" s="164">
+      <c r="L28" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5424,7 +5523,7 @@
         <v>540868.47317113332</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>65</v>
       </c>
@@ -5441,7 +5540,7 @@
       <c r="F29" s="88">
         <v>771000.92145669996</v>
       </c>
-      <c r="G29" s="195">
+      <c r="G29" s="194">
         <f>564000-G42-G43-G44</f>
         <v>442932.83</v>
       </c>
@@ -5460,7 +5559,7 @@
         <f t="shared" si="3"/>
         <v>487201.36299999995</v>
       </c>
-      <c r="L29" s="164">
+      <c r="L29" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5473,7 +5572,7 @@
         <v>864185.62172410195</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="125" t="s">
         <v>96</v>
       </c>
@@ -5490,7 +5589,7 @@
       <c r="F30" s="88">
         <v>40606.380000000005</v>
       </c>
-      <c r="G30" s="194">
+      <c r="G30" s="193">
         <f t="shared" ref="G30:G34" si="6">F30</f>
         <v>40606.380000000005</v>
       </c>
@@ -5507,7 +5606,7 @@
         <f t="shared" si="3"/>
         <v>44667.018000000011</v>
       </c>
-      <c r="L30" s="164">
+      <c r="L30" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5520,7 +5619,7 @@
         <v>47347.03908000001</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="125" t="s">
         <v>96</v>
       </c>
@@ -5537,7 +5636,7 @@
       <c r="F31" s="88">
         <v>41358.350000000006</v>
       </c>
-      <c r="G31" s="194">
+      <c r="G31" s="193">
         <f t="shared" si="6"/>
         <v>41358.350000000006</v>
       </c>
@@ -5554,7 +5653,7 @@
         <f t="shared" si="3"/>
         <v>45494.184999999998</v>
       </c>
-      <c r="L31" s="164">
+      <c r="L31" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5567,7 +5666,7 @@
         <v>48223.8361</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="125" t="s">
         <v>96</v>
       </c>
@@ -5584,7 +5683,7 @@
       <c r="F32" s="88">
         <v>33838.65</v>
       </c>
-      <c r="G32" s="194">
+      <c r="G32" s="193">
         <f>F32</f>
         <v>33838.65</v>
       </c>
@@ -5601,7 +5700,7 @@
         <f t="shared" si="3"/>
         <v>37222.514999999999</v>
       </c>
-      <c r="L32" s="164">
+      <c r="L32" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5614,7 +5713,7 @@
         <v>39455.865899999997</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="125" t="s">
         <v>96</v>
       </c>
@@ -5631,7 +5730,7 @@
       <c r="F33" s="88">
         <v>45870.17</v>
       </c>
-      <c r="G33" s="194">
+      <c r="G33" s="193">
         <f t="shared" si="6"/>
         <v>45870.17</v>
       </c>
@@ -5648,7 +5747,7 @@
         <f t="shared" si="3"/>
         <v>50457.187000000005</v>
       </c>
-      <c r="L33" s="164">
+      <c r="L33" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5661,7 +5760,7 @@
         <v>53484.618220000004</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="125" t="s">
         <v>96</v>
       </c>
@@ -5678,7 +5777,7 @@
       <c r="F34" s="88">
         <v>40606.380000000005</v>
       </c>
-      <c r="G34" s="194">
+      <c r="G34" s="193">
         <f t="shared" si="6"/>
         <v>40606.380000000005</v>
       </c>
@@ -5695,7 +5794,7 @@
         <f t="shared" si="3"/>
         <v>44667.018000000011</v>
       </c>
-      <c r="L34" s="164">
+      <c r="L34" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5708,7 +5807,7 @@
         <v>47347.03908000001</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="125" t="s">
         <v>96</v>
       </c>
@@ -5725,7 +5824,7 @@
       <c r="F35" s="11">
         <v>37598.5</v>
       </c>
-      <c r="G35" s="195">
+      <c r="G35" s="194">
         <f>F35</f>
         <v>37598.5</v>
       </c>
@@ -5742,7 +5841,7 @@
         <f t="shared" si="3"/>
         <v>41358.35</v>
       </c>
-      <c r="L35" s="164">
+      <c r="L35" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5755,7 +5854,7 @@
         <v>43839.850999999995</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="125" t="s">
         <v>96</v>
       </c>
@@ -5772,7 +5871,7 @@
       <c r="F36" s="88">
         <v>37598.5</v>
       </c>
-      <c r="G36" s="194">
+      <c r="G36" s="193">
         <f t="shared" ref="G36:G41" si="7">F36</f>
         <v>37598.5</v>
       </c>
@@ -5789,7 +5888,7 @@
         <f t="shared" si="3"/>
         <v>41358.35</v>
       </c>
-      <c r="L36" s="164">
+      <c r="L36" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5802,7 +5901,7 @@
         <v>43839.850999999995</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="125" t="s">
         <v>96</v>
       </c>
@@ -5819,7 +5918,7 @@
       <c r="F37" s="88">
         <v>36846.53</v>
       </c>
-      <c r="G37" s="194">
+      <c r="G37" s="193">
         <f t="shared" si="7"/>
         <v>36846.53</v>
       </c>
@@ -5836,7 +5935,7 @@
         <f t="shared" si="3"/>
         <v>40531.182999999997</v>
       </c>
-      <c r="L37" s="164">
+      <c r="L37" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5849,7 +5948,7 @@
         <v>42963.053979999997</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="125" t="s">
         <v>96</v>
       </c>
@@ -5866,7 +5965,7 @@
       <c r="F38" s="88">
         <v>36846.53</v>
       </c>
-      <c r="G38" s="194">
+      <c r="G38" s="193">
         <f t="shared" si="7"/>
         <v>36846.53</v>
       </c>
@@ -5883,7 +5982,7 @@
         <f t="shared" si="3"/>
         <v>40531.182999999997</v>
       </c>
-      <c r="L38" s="164">
+      <c r="L38" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5896,7 +5995,7 @@
         <v>42963.053979999997</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="125" t="s">
         <v>96</v>
       </c>
@@ -5913,7 +6012,7 @@
       <c r="F39" s="88">
         <v>44366.23</v>
       </c>
-      <c r="G39" s="194">
+      <c r="G39" s="193">
         <f t="shared" si="7"/>
         <v>44366.23</v>
       </c>
@@ -5930,7 +6029,7 @@
         <f t="shared" si="3"/>
         <v>48802.852999999996</v>
       </c>
-      <c r="L39" s="164">
+      <c r="L39" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5943,7 +6042,7 @@
         <v>51731.024179999993</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="125" t="s">
         <v>96</v>
       </c>
@@ -5960,7 +6059,7 @@
       <c r="F40" s="88">
         <v>42862.29</v>
       </c>
-      <c r="G40" s="194">
+      <c r="G40" s="193">
         <f t="shared" si="7"/>
         <v>42862.29</v>
       </c>
@@ -5977,7 +6076,7 @@
         <f t="shared" si="3"/>
         <v>47148.518999999993</v>
       </c>
-      <c r="L40" s="164">
+      <c r="L40" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5990,7 +6089,7 @@
         <v>49977.430139999989</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="125" t="s">
         <v>96</v>
       </c>
@@ -6007,7 +6106,7 @@
       <c r="F41" s="88">
         <v>40606.380000000005</v>
       </c>
-      <c r="G41" s="194">
+      <c r="G41" s="193">
         <f t="shared" si="7"/>
         <v>40606.380000000005</v>
       </c>
@@ -6024,7 +6123,7 @@
         <f t="shared" si="3"/>
         <v>44667.018000000011</v>
       </c>
-      <c r="L41" s="164">
+      <c r="L41" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6037,7 +6136,7 @@
         <v>47347.03908000001</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="125" t="s">
         <v>96</v>
       </c>
@@ -6054,7 +6153,7 @@
       <c r="F42" s="88">
         <v>41358.350000000006</v>
       </c>
-      <c r="G42" s="194">
+      <c r="G42" s="193">
         <f>F42</f>
         <v>41358.350000000006</v>
       </c>
@@ -6071,7 +6170,7 @@
         <f t="shared" si="3"/>
         <v>45494.184999999998</v>
       </c>
-      <c r="L42" s="164">
+      <c r="L42" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6084,7 +6183,7 @@
         <v>48223.8361</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="125" t="s">
         <v>96</v>
       </c>
@@ -6101,7 +6200,7 @@
       <c r="F43" s="88">
         <v>33838.65</v>
       </c>
-      <c r="G43" s="194">
+      <c r="G43" s="193">
         <f t="shared" ref="G43:G44" si="8">F43</f>
         <v>33838.65</v>
       </c>
@@ -6118,7 +6217,7 @@
         <f t="shared" si="3"/>
         <v>37222.514999999999</v>
       </c>
-      <c r="L43" s="164">
+      <c r="L43" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6132,10 +6231,10 @@
       </c>
       <c r="P43" s="108">
         <f>L1-K52</f>
-        <v>1677432.855231001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+        <v>2608148.735231</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="125" t="s">
         <v>96</v>
       </c>
@@ -6152,7 +6251,7 @@
       <c r="F44" s="88">
         <v>45870.17</v>
       </c>
-      <c r="G44" s="194">
+      <c r="G44" s="193">
         <f t="shared" si="8"/>
         <v>45870.17</v>
       </c>
@@ -6169,7 +6268,7 @@
         <f t="shared" si="3"/>
         <v>50457.187000000005</v>
       </c>
-      <c r="L44" s="164">
+      <c r="L44" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6182,7 +6281,7 @@
         <v>53484.618220000004</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="125" t="s">
         <v>96</v>
       </c>
@@ -6199,7 +6298,7 @@
       <c r="F45" s="88">
         <v>40606.380000000005</v>
       </c>
-      <c r="G45" s="194">
+      <c r="G45" s="193">
         <f t="shared" ref="G45:G51" si="9">F45</f>
         <v>40606.380000000005</v>
       </c>
@@ -6216,7 +6315,7 @@
         <f t="shared" si="3"/>
         <v>44667.018000000011</v>
       </c>
-      <c r="L45" s="164">
+      <c r="L45" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6229,7 +6328,7 @@
         <v>47347.03908000001</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="125" t="s">
         <v>96</v>
       </c>
@@ -6246,7 +6345,7 @@
       <c r="F46" s="88">
         <v>37598.5</v>
       </c>
-      <c r="G46" s="194">
+      <c r="G46" s="193">
         <f>F46</f>
         <v>37598.5</v>
       </c>
@@ -6263,7 +6362,7 @@
         <f t="shared" si="3"/>
         <v>41358.35</v>
       </c>
-      <c r="L46" s="164">
+      <c r="L46" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6279,7 +6378,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="125" t="s">
         <v>96</v>
       </c>
@@ -6296,7 +6395,7 @@
       <c r="F47" s="88">
         <v>37598.5</v>
       </c>
-      <c r="G47" s="194">
+      <c r="G47" s="193">
         <f t="shared" si="9"/>
         <v>37598.5</v>
       </c>
@@ -6313,7 +6412,7 @@
         <f t="shared" si="3"/>
         <v>41358.35</v>
       </c>
-      <c r="L47" s="164">
+      <c r="L47" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6331,7 +6430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="125" t="s">
         <v>96</v>
       </c>
@@ -6348,7 +6447,7 @@
       <c r="F48" s="88">
         <v>36846.53</v>
       </c>
-      <c r="G48" s="194">
+      <c r="G48" s="193">
         <f t="shared" si="9"/>
         <v>36846.53</v>
       </c>
@@ -6365,7 +6464,7 @@
         <f t="shared" si="3"/>
         <v>40531.182999999997</v>
       </c>
-      <c r="L48" s="164">
+      <c r="L48" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6378,7 +6477,7 @@
         <v>42963.053979999997</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="125" t="s">
         <v>96</v>
       </c>
@@ -6396,7 +6495,7 @@
       <c r="F49" s="88">
         <v>36846.53</v>
       </c>
-      <c r="G49" s="194">
+      <c r="G49" s="193">
         <f>F49</f>
         <v>36846.53</v>
       </c>
@@ -6413,7 +6512,7 @@
         <f t="shared" si="3"/>
         <v>40531.182999999997</v>
       </c>
-      <c r="L49" s="164">
+      <c r="L49" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6426,7 +6525,7 @@
         <v>42963.053979999997</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="125" t="s">
         <v>96</v>
       </c>
@@ -6443,7 +6542,7 @@
       <c r="F50" s="88">
         <v>44366.23</v>
       </c>
-      <c r="G50" s="195">
+      <c r="G50" s="194">
         <f>F50</f>
         <v>44366.23</v>
       </c>
@@ -6460,7 +6559,7 @@
         <f t="shared" si="3"/>
         <v>48802.852999999996</v>
       </c>
-      <c r="L50" s="164">
+      <c r="L50" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6473,7 +6572,7 @@
         <v>51731.024179999993</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="125" t="s">
         <v>96</v>
       </c>
@@ -6490,7 +6589,7 @@
       <c r="F51" s="88">
         <v>42862.29</v>
       </c>
-      <c r="G51" s="194">
+      <c r="G51" s="193">
         <f t="shared" si="9"/>
         <v>42862.29</v>
       </c>
@@ -6507,7 +6606,7 @@
         <f t="shared" si="3"/>
         <v>47148.518999999993</v>
       </c>
-      <c r="L51" s="164">
+      <c r="L51" s="163">
         <f t="shared" ref="L51" si="10">J$3*E51%+J$4</f>
         <v>0</v>
       </c>
@@ -6520,7 +6619,7 @@
         <v>49977.430139999989</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="89"/>
       <c r="B52" s="89"/>
       <c r="C52" s="89"/>
@@ -6547,7 +6646,7 @@
         <f>SUM(K7:K51)</f>
         <v>8217161.5547689991</v>
       </c>
-      <c r="L52" s="173">
+      <c r="L52" s="172">
         <f>SUM(L7:L51)</f>
         <v>78371.828099999999</v>
       </c>
@@ -6561,156 +6660,161 @@
       </c>
       <c r="P52" s="134"/>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="K53" s="137">
         <f>K52-L1</f>
-        <v>-1677432.855231001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="230"/>
-      <c r="D54" s="230"/>
-      <c r="E54" s="230"/>
-      <c r="F54" s="230"/>
-      <c r="G54" s="230"/>
-      <c r="H54" s="230"/>
-      <c r="I54" s="230"/>
-      <c r="J54" s="230"/>
-      <c r="K54" s="230"/>
-      <c r="L54" s="230"/>
-      <c r="M54" s="230"/>
-      <c r="N54" s="230"/>
-    </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="230"/>
-      <c r="D55" s="230"/>
-      <c r="E55" s="230"/>
-      <c r="F55" s="230"/>
-      <c r="G55" s="230"/>
-      <c r="H55" s="230"/>
-      <c r="I55" s="230"/>
-      <c r="J55" s="230"/>
-      <c r="K55" s="230"/>
-      <c r="L55" s="230"/>
-      <c r="M55" s="230"/>
-      <c r="N55" s="230"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C56" s="167"/>
-      <c r="D56" s="167"/>
-      <c r="E56" s="167"/>
-      <c r="F56" s="167"/>
-      <c r="G56" s="167"/>
-      <c r="H56" s="167"/>
-      <c r="I56" s="167"/>
-      <c r="J56" s="167"/>
-      <c r="K56" s="167"/>
-      <c r="L56" s="167"/>
-      <c r="M56" s="167"/>
-      <c r="N56" s="167"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C57" s="230" t="s">
+        <v>-2608148.735231</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C54" s="226"/>
+      <c r="D54" s="226"/>
+      <c r="E54" s="226"/>
+      <c r="F54" s="226"/>
+      <c r="G54" s="226"/>
+      <c r="H54" s="226"/>
+      <c r="I54" s="226"/>
+      <c r="J54" s="226"/>
+      <c r="K54" s="226"/>
+      <c r="L54" s="226"/>
+      <c r="M54" s="226"/>
+      <c r="N54" s="226"/>
+    </row>
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C55" s="226"/>
+      <c r="D55" s="226"/>
+      <c r="E55" s="226"/>
+      <c r="F55" s="226"/>
+      <c r="G55" s="226"/>
+      <c r="H55" s="226"/>
+      <c r="I55" s="226"/>
+      <c r="J55" s="226"/>
+      <c r="K55" s="226"/>
+      <c r="L55" s="226"/>
+      <c r="M55" s="226"/>
+      <c r="N55" s="226"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C56" s="166"/>
+      <c r="D56" s="166"/>
+      <c r="E56" s="166"/>
+      <c r="F56" s="166"/>
+      <c r="G56" s="166"/>
+      <c r="H56" s="166"/>
+      <c r="I56" s="166"/>
+      <c r="J56" s="166"/>
+      <c r="K56" s="166"/>
+      <c r="L56" s="166"/>
+      <c r="M56" s="166"/>
+      <c r="N56" s="166"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C57" s="226" t="s">
         <v>129</v>
       </c>
-      <c r="D57" s="230"/>
-      <c r="E57" s="230"/>
-      <c r="F57" s="230"/>
-      <c r="G57" s="230"/>
-      <c r="H57" s="230"/>
-      <c r="I57" s="230"/>
-      <c r="J57" s="230"/>
-      <c r="K57" s="230"/>
-      <c r="L57" s="230"/>
-      <c r="M57" s="230"/>
-      <c r="N57" s="230"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C58" s="230"/>
-      <c r="D58" s="230"/>
-      <c r="E58" s="230"/>
-      <c r="F58" s="230"/>
-      <c r="G58" s="230"/>
-      <c r="H58" s="230"/>
-      <c r="I58" s="230"/>
-      <c r="J58" s="230"/>
-      <c r="K58" s="230"/>
-      <c r="L58" s="230"/>
-      <c r="M58" s="230"/>
-      <c r="N58" s="230"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C59" s="230"/>
-      <c r="D59" s="230"/>
-      <c r="E59" s="230"/>
-      <c r="F59" s="230"/>
-      <c r="G59" s="230"/>
-      <c r="H59" s="230"/>
-      <c r="I59" s="230"/>
-      <c r="J59" s="230"/>
-      <c r="K59" s="230"/>
-      <c r="L59" s="230"/>
-      <c r="M59" s="230"/>
-      <c r="N59" s="230"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C60" s="230"/>
-      <c r="D60" s="230"/>
-      <c r="E60" s="230"/>
-      <c r="F60" s="230"/>
-      <c r="G60" s="230"/>
-      <c r="H60" s="230"/>
-      <c r="I60" s="230"/>
-      <c r="J60" s="230"/>
-      <c r="K60" s="230"/>
-      <c r="L60" s="230"/>
-      <c r="M60" s="230"/>
-      <c r="N60" s="230"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C61" s="230"/>
-      <c r="D61" s="230"/>
-      <c r="E61" s="230"/>
-      <c r="F61" s="230"/>
-      <c r="G61" s="230"/>
-      <c r="H61" s="230"/>
-      <c r="I61" s="230"/>
-      <c r="J61" s="230"/>
-      <c r="K61" s="230"/>
-      <c r="L61" s="230"/>
-      <c r="M61" s="230"/>
-      <c r="N61" s="230"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C62" s="230"/>
-      <c r="D62" s="230"/>
-      <c r="E62" s="230"/>
-      <c r="F62" s="230"/>
-      <c r="G62" s="230"/>
-      <c r="H62" s="230"/>
-      <c r="I62" s="230"/>
-      <c r="J62" s="230"/>
-      <c r="K62" s="230"/>
-      <c r="L62" s="230"/>
-      <c r="M62" s="230"/>
-      <c r="N62" s="230"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C63" s="230"/>
-      <c r="D63" s="230"/>
-      <c r="E63" s="230"/>
-      <c r="F63" s="230"/>
-      <c r="G63" s="230"/>
-      <c r="H63" s="230"/>
-      <c r="I63" s="230"/>
-      <c r="J63" s="230"/>
-      <c r="K63" s="230"/>
-      <c r="L63" s="230"/>
-      <c r="M63" s="230"/>
-      <c r="N63" s="230"/>
+      <c r="D57" s="226"/>
+      <c r="E57" s="226"/>
+      <c r="F57" s="226"/>
+      <c r="G57" s="226"/>
+      <c r="H57" s="226"/>
+      <c r="I57" s="226"/>
+      <c r="J57" s="226"/>
+      <c r="K57" s="226"/>
+      <c r="L57" s="226"/>
+      <c r="M57" s="226"/>
+      <c r="N57" s="226"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C58" s="226"/>
+      <c r="D58" s="226"/>
+      <c r="E58" s="226"/>
+      <c r="F58" s="226"/>
+      <c r="G58" s="226"/>
+      <c r="H58" s="226"/>
+      <c r="I58" s="226"/>
+      <c r="J58" s="226"/>
+      <c r="K58" s="226"/>
+      <c r="L58" s="226"/>
+      <c r="M58" s="226"/>
+      <c r="N58" s="226"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C59" s="226"/>
+      <c r="D59" s="226"/>
+      <c r="E59" s="226"/>
+      <c r="F59" s="226"/>
+      <c r="G59" s="226"/>
+      <c r="H59" s="226"/>
+      <c r="I59" s="226"/>
+      <c r="J59" s="226"/>
+      <c r="K59" s="226"/>
+      <c r="L59" s="226"/>
+      <c r="M59" s="226"/>
+      <c r="N59" s="226"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C60" s="226"/>
+      <c r="D60" s="226"/>
+      <c r="E60" s="226"/>
+      <c r="F60" s="226"/>
+      <c r="G60" s="226"/>
+      <c r="H60" s="226"/>
+      <c r="I60" s="226"/>
+      <c r="J60" s="226"/>
+      <c r="K60" s="226"/>
+      <c r="L60" s="226"/>
+      <c r="M60" s="226"/>
+      <c r="N60" s="226"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C61" s="226"/>
+      <c r="D61" s="226"/>
+      <c r="E61" s="226"/>
+      <c r="F61" s="226"/>
+      <c r="G61" s="226"/>
+      <c r="H61" s="226"/>
+      <c r="I61" s="226"/>
+      <c r="J61" s="226"/>
+      <c r="K61" s="226"/>
+      <c r="L61" s="226"/>
+      <c r="M61" s="226"/>
+      <c r="N61" s="226"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C62" s="226"/>
+      <c r="D62" s="226"/>
+      <c r="E62" s="226"/>
+      <c r="F62" s="226"/>
+      <c r="G62" s="226"/>
+      <c r="H62" s="226"/>
+      <c r="I62" s="226"/>
+      <c r="J62" s="226"/>
+      <c r="K62" s="226"/>
+      <c r="L62" s="226"/>
+      <c r="M62" s="226"/>
+      <c r="N62" s="226"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C63" s="226"/>
+      <c r="D63" s="226"/>
+      <c r="E63" s="226"/>
+      <c r="F63" s="226"/>
+      <c r="G63" s="226"/>
+      <c r="H63" s="226"/>
+      <c r="I63" s="226"/>
+      <c r="J63" s="226"/>
+      <c r="K63" s="226"/>
+      <c r="L63" s="226"/>
+      <c r="M63" s="226"/>
+      <c r="N63" s="226"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
@@ -6723,11 +6827,6 @@
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="I5:I6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -6737,88 +6836,88 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{596D2FF5-218B-41A1-9BCB-F43114942886}">
   <dimension ref="C4:H25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="193">
+        <v>160</v>
+      </c>
+      <c r="D5" s="192">
         <v>-447223.45918396302</v>
       </c>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
-        <v>171</v>
-      </c>
-      <c r="D6" s="193">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="D6" s="192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D7" s="193">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="D7" s="192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
-        <v>173</v>
-      </c>
-      <c r="D8" s="193">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="D8" s="192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C10" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>170</v>
-      </c>
-      <c r="D11" s="193">
+        <v>160</v>
+      </c>
+      <c r="D11" s="192">
         <v>451182</v>
       </c>
     </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
-        <v>171</v>
-      </c>
-      <c r="D12" s="193">
+        <v>161</v>
+      </c>
+      <c r="D12" s="192">
         <v>40606.380000000005</v>
       </c>
     </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
-        <v>172</v>
-      </c>
-      <c r="D13" s="193">
+        <v>162</v>
+      </c>
+      <c r="D13" s="192">
         <v>41358.350000000006</v>
       </c>
     </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>173</v>
-      </c>
-      <c r="D14" s="193">
+        <v>163</v>
+      </c>
+      <c r="D14" s="192">
         <v>37598.5</v>
       </c>
     </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C16" s="3" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6826,65 +6925,65 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>170</v>
-      </c>
-      <c r="D17" s="193">
+        <v>160</v>
+      </c>
+      <c r="D17" s="192">
         <f>D11+D5</f>
         <v>3958.5408160369843</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
-        <v>171</v>
-      </c>
-      <c r="D18" s="193">
+        <v>161</v>
+      </c>
+      <c r="D18" s="192">
         <v>40606.380000000005</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
-        <v>172</v>
-      </c>
-      <c r="D19" s="193">
+        <v>162</v>
+      </c>
+      <c r="D19" s="192">
         <v>41358.350000000006</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
-        <v>173</v>
-      </c>
-      <c r="D20" s="193">
+        <v>163</v>
+      </c>
+      <c r="D20" s="192">
         <v>37598.5</v>
       </c>
     </row>
-    <row r="21" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C21" t="s">
-        <v>177</v>
-      </c>
-      <c r="D21" s="193">
+        <v>167</v>
+      </c>
+      <c r="D21" s="192">
         <v>-25000</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C22" s="241" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D22" s="244">
         <f>SUM(D17:D21)</f>
         <v>98521.770816036995</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C23" s="242"/>
       <c r="D23" s="245"/>
     </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C24" s="242"/>
       <c r="D24" s="245"/>
     </row>
-    <row r="25" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C25" s="243"/>
       <c r="D25" s="246"/>
     </row>
@@ -6901,16 +7000,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="8.44140625" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" customWidth="1"/>
+    <col min="13" max="13" width="11.44140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="48"/>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
@@ -6930,11 +7029,11 @@
       <c r="M1" s="49"/>
       <c r="N1" s="52" t="str">
         <f>RESUMEN!C5</f>
-        <v>VTO: 14/08</v>
+        <v>VTO: 15/09</v>
       </c>
       <c r="O1" s="52"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="49"/>
       <c r="B2" s="51"/>
       <c r="C2" s="51"/>
@@ -6953,7 +7052,7 @@
       <c r="N2" s="49"/>
       <c r="O2" s="49"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="49"/>
       <c r="B3" s="51"/>
       <c r="C3" s="51"/>
@@ -6976,7 +7075,7 @@
       </c>
       <c r="O3" s="54"/>
     </row>
-    <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="49"/>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
@@ -6997,7 +7096,7 @@
       <c r="N4" s="49"/>
       <c r="O4" s="49"/>
     </row>
-    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="247" t="s">
         <v>73</v>
       </c>
@@ -7042,7 +7141,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="248"/>
       <c r="B6" s="248"/>
       <c r="C6" s="56" t="s">
@@ -7077,7 +7176,7 @@
       <c r="N6" s="248"/>
       <c r="O6" s="248"/>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15">
         <v>1</v>
       </c>
@@ -7123,7 +7222,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15">
         <v>2</v>
       </c>
@@ -7169,7 +7268,7 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="15">
         <v>3</v>
       </c>
@@ -7215,7 +7314,7 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15">
         <v>4</v>
       </c>
@@ -7261,7 +7360,7 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15">
         <v>5</v>
       </c>
@@ -7307,7 +7406,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15">
         <v>6</v>
       </c>
@@ -7353,7 +7452,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15">
         <v>7</v>
       </c>
@@ -7399,7 +7498,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15">
         <v>8</v>
       </c>
@@ -7445,7 +7544,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15">
         <v>9</v>
       </c>
@@ -7491,7 +7590,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15">
         <v>10</v>
       </c>
@@ -7537,7 +7636,7 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="15">
         <v>11</v>
       </c>
@@ -7583,7 +7682,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15">
         <v>12</v>
       </c>
@@ -7629,7 +7728,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="15">
         <v>13</v>
       </c>
@@ -7675,7 +7774,7 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15">
         <v>14</v>
       </c>
@@ -7721,7 +7820,7 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="15">
         <v>15</v>
       </c>
@@ -7767,7 +7866,7 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15">
         <v>16</v>
       </c>
@@ -7813,7 +7912,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="15">
         <v>17</v>
       </c>
@@ -7859,7 +7958,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15">
         <v>18</v>
       </c>
@@ -7905,7 +8004,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="15">
         <v>19</v>
       </c>
@@ -7951,7 +8050,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15">
         <v>20</v>
       </c>
@@ -7997,7 +8096,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="15">
         <v>21</v>
       </c>
@@ -8043,7 +8142,7 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15">
         <v>22</v>
       </c>
@@ -8089,7 +8188,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="15"/>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
@@ -8106,7 +8205,7 @@
       <c r="N29" s="6"/>
       <c r="O29" s="6"/>
     </row>
-    <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="13"/>
       <c r="B30" s="14"/>
       <c r="C30" s="57">
@@ -8147,7 +8246,7 @@
         <v>264873.42966686888</v>
       </c>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E33" s="33"/>
       <c r="F33" s="33"/>
     </row>

--- a/BELGRANO 1646/Agosto/Agosto-BLG1646.xlsx
+++ b/BELGRANO 1646/Agosto/Agosto-BLG1646.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BELGRANO 1646\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BELGRANO 1646\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B431F7F4-94EB-43FE-85DF-0F799D2FCE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EA71FE-E90E-4848-A622-C7445FDFFEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$132</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$127</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="179">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -481,66 +481,24 @@
     <t>Contessi - Mantenimiento de ascensores</t>
   </si>
   <si>
-    <t>Reemplazo Sr. Diego -  Monica Gorosito</t>
-  </si>
-  <si>
-    <t>Seguro de vida Sra. Monica</t>
-  </si>
-  <si>
     <t>Subidos en jun de 2025</t>
   </si>
   <si>
-    <t>Kromacolor</t>
-  </si>
-  <si>
     <t>BALBOA, ARIEL</t>
   </si>
   <si>
-    <t>Casa ruan - materiales de trabajo - plafones y dicroicas</t>
-  </si>
-  <si>
-    <t>Servisur - reemplazo de plafones y dicroicas</t>
-  </si>
-  <si>
     <t>Articulos de limpieza - Montoya Alejandra</t>
   </si>
   <si>
-    <t>Debito 27/07</t>
-  </si>
-  <si>
-    <t>Contessi - Cuota 2  de arreglo montavehiculos</t>
-  </si>
-  <si>
-    <t>Riesgo Uno - Reemplazo de detector, verificacion de cableado, pulsadores y panel - Mano de obra y materiales</t>
-  </si>
-  <si>
     <t>Limpieza de SUM - Sra. Monica</t>
   </si>
   <si>
     <t xml:space="preserve">Sr. Diego Britez </t>
   </si>
   <si>
-    <t>SEGURO OBLIGATORIO SR DIEGO BRITEZ FEDERACION PATRONAL DEBITO AUTOMATICO 01/07</t>
-  </si>
-  <si>
-    <t>Debito 14/07</t>
-  </si>
-  <si>
-    <t>Numero 1859135 Debito automatico 01/07</t>
-  </si>
-  <si>
     <t xml:space="preserve">Compra de materiales </t>
   </si>
   <si>
-    <t>Leonardo Balcalazza - Recapeo vereda, puntas de canteros</t>
-  </si>
-  <si>
-    <t>Vto. 04/07</t>
-  </si>
-  <si>
-    <t>Vto. 31/07</t>
-  </si>
-  <si>
     <t>EL MES ANTERIOR ATILIO QUEDO CON UN SALDO A FAVOR DE:</t>
   </si>
   <si>
@@ -568,9 +526,6 @@
     <t>YA ABONO:</t>
   </si>
   <si>
-    <t>A GASTON LO HABIAMOS PUESTO COMO DEUDOR( FIJARSE EN EL PDF) Y NO LO ERA</t>
-  </si>
-  <si>
     <t>VTO: 15/09</t>
   </si>
   <si>
@@ -583,9 +538,6 @@
     <t>Energoup MES DE AGOSTO</t>
   </si>
   <si>
-    <t xml:space="preserve">Mes de AGOSTO </t>
-  </si>
-  <si>
     <t>Ingreso mes de JULIO</t>
   </si>
   <si>
@@ -604,7 +556,49 @@
     <t>Contessi - Provision y cambio de lapices de nivelacion en el montaauto</t>
   </si>
   <si>
-    <t>Pago mis cuentas 06/08</t>
+    <t>Pago mis cuentas 07/08</t>
+  </si>
+  <si>
+    <t>Debito 12/08</t>
+  </si>
+  <si>
+    <t>SEGURO OBLIGATORIO SR DIEGO BRITEZ FEDERACION PATRONAL DEBITO AUTOMATICO 01/08</t>
+  </si>
+  <si>
+    <t>Numero 1859135 Debito automatico 01/08</t>
+  </si>
+  <si>
+    <t>Pintureria prestigio - Compra de pintura lockson larga duracion - 12/08</t>
+  </si>
+  <si>
+    <t>Pintureria prestigio - Compra de pintura lockson larga duracion - 08/08</t>
+  </si>
+  <si>
+    <t>Efectivo</t>
+  </si>
+  <si>
+    <t>Debito 29/08</t>
+  </si>
+  <si>
+    <t>Combustible - Recarga dia 18/08 - Efectivo</t>
+  </si>
+  <si>
+    <t>Servicio de recarga de combustible 18/08 - Efectivo</t>
+  </si>
+  <si>
+    <t>No llego factura</t>
+  </si>
+  <si>
+    <t>Pinsur - Colmeiro Oscar - Sellado de mamposteria e inyectado con terminacion de pintura de los frentes de balcones lado izquiero - Transferencia y efectivo</t>
+  </si>
+  <si>
+    <t>Pinsur - Colmeiro Oscar - Vaciado de agua en parantes, ajuste de tornillos y sellados - Transferencia y efectivo</t>
+  </si>
+  <si>
+    <t>GASTOS PARTICULARES</t>
+  </si>
+  <si>
+    <t>No hubo boleta</t>
   </si>
 </sst>
 </file>
@@ -612,15 +606,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="169" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -1329,11 +1323,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="252">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
@@ -1343,7 +1337,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -1355,7 +1349,7 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1366,12 +1360,12 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="2" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1423,7 +1417,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1431,7 +1425,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1447,17 +1441,17 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1470,12 +1464,12 @@
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1483,95 +1477,88 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="9" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="9" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="14" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="8" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="39" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="10" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="10" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="6" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="6" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="14" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="14" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1580,60 +1567,55 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="15" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="15" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="10" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="10" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="6" fillId="11" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="20" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="6" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1709,10 +1691,10 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1760,7 +1742,7 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="11" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="2" fillId="11" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1775,11 +1757,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2145,24 +2123,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P142"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P137"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8"/>
       <c r="B1" s="97" t="s">
         <v>118</v>
@@ -2171,7 +2149,7 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="64"/>
       <c r="B2" s="65" t="s">
         <v>0</v>
@@ -2180,7 +2158,7 @@
       <c r="D2" s="65"/>
       <c r="E2" s="66"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="67"/>
       <c r="B3" s="68" t="s">
         <v>88</v>
@@ -2189,7 +2167,7 @@
       <c r="D3" s="68"/>
       <c r="E3" s="69"/>
     </row>
-    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="67"/>
       <c r="B4" s="68" t="s">
         <v>89</v>
@@ -2198,20 +2176,20 @@
       <c r="D4" s="68"/>
       <c r="E4" s="69"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C5" s="71" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D5" s="71"/>
       <c r="E5" s="72"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="67" t="s">
         <v>99</v>
       </c>
@@ -2220,7 +2198,7 @@
       <c r="D6" s="68"/>
       <c r="E6" s="69"/>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="70" t="s">
         <v>98</v>
       </c>
@@ -2229,69 +2207,69 @@
       <c r="D7" s="71"/>
       <c r="E7" s="72"/>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="204" t="s">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="202" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="205"/>
-      <c r="D14" s="206"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="207"/>
-      <c r="C15" s="208"/>
-      <c r="D15" s="209"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="207"/>
-      <c r="C16" s="208"/>
-      <c r="D16" s="209"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="210"/>
-      <c r="C17" s="211"/>
-      <c r="D17" s="212"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C14" s="203"/>
+      <c r="D14" s="204"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="205"/>
+      <c r="C15" s="206"/>
+      <c r="D15" s="207"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="205"/>
+      <c r="C16" s="206"/>
+      <c r="D16" s="207"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="208"/>
+      <c r="C17" s="209"/>
+      <c r="D17" s="210"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="61" t="s">
         <v>86</v>
       </c>
       <c r="B21" s="62"/>
       <c r="C21" s="63"/>
       <c r="D21" s="59"/>
-      <c r="E21" s="145" t="s">
+      <c r="E21" s="193" t="s">
         <v>121</v>
       </c>
-      <c r="F21" s="144" t="s">
+      <c r="F21" s="194" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="120" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="129"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E22" s="192"/>
+      <c r="F22" s="192"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="120" t="s">
         <v>126</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="178">
+      <c r="D23" s="189">
         <v>1262522.3</v>
       </c>
       <c r="E23" s="133">
@@ -2303,13 +2281,13 @@
         <v>102138.05407</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="120" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="178">
+      <c r="D24" s="189">
         <v>-274598.59999999998</v>
       </c>
       <c r="E24" s="133">
@@ -2321,13 +2299,13 @@
         <v>-22215.026739999998</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="120" t="s">
         <v>112</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="178">
+      <c r="D25" s="189">
         <v>0.3</v>
       </c>
       <c r="E25" s="133">
@@ -2339,15 +2317,15 @@
         <v>2.427E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="120"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="178"/>
+      <c r="D26" s="175"/>
       <c r="E26" s="133"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="95" t="s">
         <v>3</v>
       </c>
@@ -2369,18 +2347,18 @@
         <f>E27+F27</f>
         <v>987924</v>
       </c>
-      <c r="H27" s="149" t="str">
+      <c r="H27" s="146" t="str">
         <f>IF(D27=G27, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="94" t="s">
         <v>109</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="179">
+      <c r="D28" s="176">
         <v>0</v>
       </c>
       <c r="E28" s="133">
@@ -2391,13 +2369,13 @@
         <f>D28*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H28" s="149"/>
-    </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H28" s="146"/>
+    </row>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="94"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="178">
+      <c r="D29" s="175">
         <v>0</v>
       </c>
       <c r="E29" s="133">
@@ -2408,27 +2386,27 @@
         <f>D29*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H29" s="149"/>
-    </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H29" s="146"/>
+    </row>
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="94"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="178"/>
+      <c r="D30" s="175"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
-      <c r="H30" s="149"/>
-    </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H30" s="146"/>
+    </row>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="94"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="178"/>
+      <c r="D31" s="175"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
-      <c r="H31" s="149"/>
-    </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H31" s="146"/>
+    </row>
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="95" t="s">
         <v>117</v>
       </c>
@@ -2450,18 +2428,18 @@
         <f>E32+F32</f>
         <v>0</v>
       </c>
-      <c r="H32" s="149" t="str">
+      <c r="H32" s="146" t="str">
         <f>IF(D32=G32, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="94" t="s">
         <v>109</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="179"/>
+      <c r="D33" s="176"/>
       <c r="E33" s="133">
         <f>D33*91.91%</f>
         <v>0</v>
@@ -2470,15 +2448,15 @@
         <f>D33*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H33" s="149"/>
-    </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H33" s="146"/>
+    </row>
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>130</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="178"/>
+      <c r="D34" s="175"/>
       <c r="E34" s="133">
         <f t="shared" ref="E34:E35" si="3">D34*91.91%</f>
         <v>0</v>
@@ -2487,15 +2465,15 @@
         <f t="shared" ref="F34:F35" si="4">D34*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H34" s="149"/>
-    </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H34" s="146"/>
+    </row>
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="94" t="s">
         <v>2</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="178"/>
+      <c r="D35" s="175"/>
       <c r="E35" s="133">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2504,9 +2482,9 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H35" s="149"/>
-    </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H35" s="146"/>
+    </row>
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="95" t="s">
         <v>110</v>
       </c>
@@ -2524,36 +2502,36 @@
         <f>E36*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H36" s="149"/>
-    </row>
-    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H36" s="146"/>
+    </row>
+    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="128"/>
       <c r="B37" s="98"/>
       <c r="C37" s="98"/>
-      <c r="D37" s="178"/>
+      <c r="D37" s="175"/>
       <c r="E37" s="119"/>
       <c r="F37" s="119"/>
-      <c r="H37" s="149"/>
-    </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H37" s="146"/>
+    </row>
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="128"/>
       <c r="B38" s="98"/>
       <c r="C38" s="98"/>
-      <c r="D38" s="178"/>
+      <c r="D38" s="175"/>
       <c r="E38" s="119"/>
       <c r="F38" s="119"/>
-      <c r="H38" s="149"/>
-    </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H38" s="146"/>
+    </row>
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="98"/>
       <c r="B39" s="98"/>
       <c r="C39" s="110"/>
-      <c r="D39" s="178"/>
+      <c r="D39" s="175"/>
       <c r="E39" s="119"/>
       <c r="F39" s="119"/>
-      <c r="H39" s="149"/>
-    </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H39" s="146"/>
+    </row>
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="95" t="s">
         <v>117</v>
       </c>
@@ -2568,51 +2546,43 @@
         <f>(D37)*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H40" s="149"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="94" t="s">
-        <v>140</v>
-      </c>
+      <c r="H40" s="146"/>
+    </row>
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="94"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="112">
-        <v>3567.21</v>
-      </c>
+      <c r="D41" s="112"/>
       <c r="E41" s="133">
         <f>D41*91.91%</f>
-        <v>3278.6227109999995</v>
+        <v>0</v>
       </c>
       <c r="F41" s="133">
         <f>D41*8.09%</f>
-        <v>288.587289</v>
-      </c>
-      <c r="H41" s="149"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="94" t="s">
-        <v>139</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H41" s="146"/>
+    </row>
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="94"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="112">
-        <v>37000</v>
-      </c>
+      <c r="D42" s="112"/>
       <c r="E42" s="133">
         <f>D42*91.91%</f>
-        <v>34006.699999999997</v>
+        <v>0</v>
       </c>
       <c r="F42" s="133">
         <f>D42*8.09%</f>
-        <v>2993.3</v>
-      </c>
-      <c r="H42" s="149"/>
-    </row>
-    <row r="43" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="H42" s="146"/>
+    </row>
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="94"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="181"/>
+      <c r="D43" s="178"/>
       <c r="E43" s="133">
         <f>D43*91.91%</f>
         <v>0</v>
@@ -2621,9 +2591,9 @@
         <f>D43*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H43" s="149"/>
-    </row>
-    <row r="44" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H43" s="146"/>
+    </row>
+    <row r="44" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="95" t="s">
         <v>127</v>
       </c>
@@ -2631,40 +2601,40 @@
       <c r="C44" s="95"/>
       <c r="D44" s="107">
         <f>SUM(D41:D43)</f>
-        <v>40567.21</v>
-      </c>
-      <c r="E44" s="157">
+        <v>0</v>
+      </c>
+      <c r="E44" s="154">
         <f>SUM(E41:E43)</f>
-        <v>37285.322710999993</v>
-      </c>
-      <c r="F44" s="167">
+        <v>0</v>
+      </c>
+      <c r="F44" s="164">
         <f>SUM(F41:F43)</f>
-        <v>3281.8872890000002</v>
+        <v>0</v>
       </c>
       <c r="G44" s="108">
         <f>E44+F44</f>
-        <v>40567.209999999992</v>
-      </c>
-      <c r="H44" s="149"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="146"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="94" t="s">
         <v>4</v>
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="181"/>
+      <c r="D45" s="178"/>
       <c r="E45" s="113"/>
       <c r="F45" s="100"/>
-      <c r="H45" s="149"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H45" s="146"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="94" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="98"/>
-      <c r="D46" s="112">
+      <c r="D46" s="185">
         <v>5020</v>
       </c>
       <c r="E46" s="133">
@@ -2675,17 +2645,17 @@
         <f>D46*8.09%</f>
         <v>406.11799999999999</v>
       </c>
-      <c r="H46" s="149"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H46" s="146"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="94" t="s">
         <v>5</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C47" s="7"/>
-      <c r="D47" s="191">
+      <c r="D47" s="185">
         <f>106691.95+6312.61+56813.5</f>
         <v>169818.06</v>
       </c>
@@ -2697,30 +2667,30 @@
         <f>D47*8.09%</f>
         <v>13738.281053999999</v>
       </c>
-      <c r="H47" s="149"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H47" s="146"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="94" t="s">
         <v>135</v>
       </c>
       <c r="B48" s="98" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="C48" s="7"/>
-      <c r="D48" s="191">
-        <v>828107.55</v>
+      <c r="D48" s="185">
+        <v>559190.81000000006</v>
       </c>
       <c r="E48" s="133">
         <f>D48*91.91%</f>
-        <v>761113.64920500002</v>
+        <v>513952.27347100002</v>
       </c>
       <c r="F48" s="133">
         <f>D48*8.09%</f>
-        <v>66993.900795000009</v>
-      </c>
-      <c r="H48" s="149"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+        <v>45238.536529000005</v>
+      </c>
+      <c r="H48" s="146"/>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="95" t="s">
         <v>6</v>
       </c>
@@ -2728,1540 +2698,1398 @@
       <c r="C49" s="96"/>
       <c r="D49" s="107">
         <f>SUM(D46:D48)</f>
-        <v>1002945.6100000001</v>
+        <v>734028.87000000011</v>
       </c>
       <c r="E49" s="107">
         <f t="shared" ref="E49:F49" si="6">SUM(E46:E48)</f>
-        <v>921807.31015100004</v>
+        <v>674645.93441700004</v>
       </c>
       <c r="F49" s="107">
         <f t="shared" si="6"/>
-        <v>81138.299849000003</v>
+        <v>59382.935583000006</v>
       </c>
       <c r="G49" s="108">
         <f>E49+F49</f>
-        <v>1002945.6100000001</v>
-      </c>
-      <c r="H49" s="149" t="str">
+        <v>734028.87</v>
+      </c>
+      <c r="H49" s="146" t="str">
         <f>IF(D49=G49, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="181"/>
+      <c r="D50" s="178"/>
       <c r="E50" s="114"/>
       <c r="F50" s="7"/>
-      <c r="H50" s="149"/>
-    </row>
-    <row r="51" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="186" t="s">
-        <v>148</v>
-      </c>
-      <c r="B51" s="174"/>
-      <c r="C51" s="175"/>
-      <c r="D51" s="181">
-        <v>960000</v>
-      </c>
-      <c r="E51" s="148">
+      <c r="H50" s="146"/>
+    </row>
+    <row r="51" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="182" t="s">
+        <v>163</v>
+      </c>
+      <c r="B51" s="171"/>
+      <c r="C51" s="172"/>
+      <c r="D51" s="187">
+        <v>160000</v>
+      </c>
+      <c r="E51" s="145">
         <f>D51</f>
-        <v>960000</v>
+        <v>160000</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="108">
         <f>D51</f>
-        <v>960000</v>
-      </c>
-      <c r="H51" s="159">
+        <v>160000</v>
+      </c>
+      <c r="H51" s="156">
         <f>E51+F51</f>
-        <v>960000</v>
-      </c>
-      <c r="I51" s="176">
-        <f t="shared" ref="I51:I74" si="7">H51-D51</f>
-        <v>0</v>
-      </c>
-      <c r="J51" s="176">
-        <f t="shared" ref="J51:J75" si="8">G51-D51</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="186" t="s">
-        <v>179</v>
-      </c>
-      <c r="B52" s="174"/>
-      <c r="C52" s="175"/>
-      <c r="D52" s="249">
         <v>160000</v>
       </c>
-      <c r="E52" s="148">
+      <c r="I51" s="173"/>
+      <c r="J51" s="173"/>
+    </row>
+    <row r="52" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="182" t="s">
+        <v>138</v>
+      </c>
+      <c r="B52" s="171"/>
+      <c r="C52" s="172"/>
+      <c r="D52" s="185">
+        <v>372000</v>
+      </c>
+      <c r="E52" s="145">
         <f>D52</f>
-        <v>160000</v>
+        <v>372000</v>
       </c>
       <c r="F52" s="7"/>
-      <c r="G52" s="108"/>
-      <c r="H52" s="159"/>
-      <c r="I52" s="176"/>
-      <c r="J52" s="176"/>
-    </row>
-    <row r="53" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="186" t="s">
-        <v>138</v>
-      </c>
-      <c r="B53" s="174"/>
-      <c r="C53" s="175"/>
-      <c r="D53" s="191">
+      <c r="G52" s="108">
+        <f>D52</f>
         <v>372000</v>
       </c>
-      <c r="E53" s="148">
-        <f>D53</f>
+      <c r="H52" s="156">
+        <f>E52+F52</f>
         <v>372000</v>
       </c>
-      <c r="F53" s="7"/>
+      <c r="I52" s="173">
+        <f>H52-D52</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="173"/>
+    </row>
+    <row r="53" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="120" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="158"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="112"/>
+      <c r="E53" s="145">
+        <f t="shared" ref="E53:E57" si="7">D53*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F53" s="133">
+        <f t="shared" ref="F53:F57" si="8">D53*8.09%</f>
+        <v>0</v>
+      </c>
       <c r="G53" s="108">
-        <f>D53</f>
-        <v>372000</v>
-      </c>
-      <c r="H53" s="159">
-        <f>E53+F53</f>
-        <v>372000</v>
-      </c>
-      <c r="I53" s="176">
-        <f>H53-D53</f>
-        <v>0</v>
-      </c>
-      <c r="J53" s="176"/>
-    </row>
-    <row r="54" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="199" t="s">
-        <v>149</v>
-      </c>
-      <c r="B54" s="200"/>
-      <c r="C54" s="201"/>
-      <c r="D54" s="112">
-        <v>165500</v>
-      </c>
-      <c r="E54" s="148">
-        <f t="shared" ref="E54:E60" si="9">D54*91.91%</f>
-        <v>152111.04999999999</v>
+        <f t="shared" ref="G53:G70" si="9">D53</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="156">
+        <f t="shared" ref="H53:H70" si="10">E53+F53</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="173"/>
+      <c r="J53" s="173"/>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A54" s="94" t="s">
+        <v>157</v>
+      </c>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="185">
+        <v>148200</v>
+      </c>
+      <c r="E54" s="145">
+        <f t="shared" si="7"/>
+        <v>136210.62</v>
       </c>
       <c r="F54" s="133">
-        <f t="shared" ref="F54:F60" si="10">D54*8.09%</f>
-        <v>13388.95</v>
+        <f t="shared" si="8"/>
+        <v>11989.38</v>
       </c>
       <c r="G54" s="108">
-        <f t="shared" ref="G54:G75" si="11">D54</f>
-        <v>165500</v>
-      </c>
-      <c r="H54" s="159">
-        <f t="shared" ref="H54:H75" si="12">E54+F54</f>
-        <v>165500</v>
-      </c>
-      <c r="I54" s="176">
+        <f t="shared" si="9"/>
+        <v>148200</v>
+      </c>
+      <c r="H54" s="156">
+        <f t="shared" si="10"/>
+        <v>148200</v>
+      </c>
+      <c r="I54" s="173">
+        <f t="shared" ref="I54:I69" si="11">H54-D54</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="173">
+        <f t="shared" ref="J54:J70" si="12">G54-D54</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A55" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C55" s="7"/>
+      <c r="D55" s="185">
+        <v>129320</v>
+      </c>
+      <c r="E55" s="145">
+        <f>D55*91.91%</f>
+        <v>118858.01199999999</v>
+      </c>
+      <c r="F55" s="133">
+        <f t="shared" si="8"/>
+        <v>10461.987999999999</v>
+      </c>
+      <c r="G55" s="108">
+        <f t="shared" si="9"/>
+        <v>129320</v>
+      </c>
+      <c r="H55" s="156">
+        <f>E55+F55</f>
+        <v>129319.99999999999</v>
+      </c>
+      <c r="I55" s="173">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="173">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A56" s="94" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C56" s="7"/>
+      <c r="D56" s="112">
+        <v>0</v>
+      </c>
+      <c r="E56" s="145">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J54" s="176">
+      <c r="F56" s="133">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="120" t="s">
-        <v>8</v>
-      </c>
-      <c r="B55" s="161"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="112">
-        <v>148124.67000000001</v>
-      </c>
-      <c r="E55" s="148">
+      <c r="G56" s="108">
         <f t="shared" si="9"/>
-        <v>136141.38419700001</v>
-      </c>
-      <c r="F55" s="133">
+        <v>0</v>
+      </c>
+      <c r="H56" s="156">
         <f t="shared" si="10"/>
-        <v>11983.285803000001</v>
-      </c>
-      <c r="G55" s="108">
+        <v>0</v>
+      </c>
+      <c r="I56" s="173">
         <f t="shared" si="11"/>
-        <v>148124.67000000001</v>
-      </c>
-      <c r="H55" s="159">
+        <v>0</v>
+      </c>
+      <c r="J56" s="173">
         <f t="shared" si="12"/>
-        <v>148124.67000000001</v>
-      </c>
-      <c r="I55" s="176"/>
-      <c r="J55" s="176"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="94" t="s">
-        <v>172</v>
-      </c>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="191">
-        <v>148200</v>
-      </c>
-      <c r="E56" s="148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A57" s="128" t="s">
+        <v>10</v>
+      </c>
+      <c r="B57" s="98" t="s">
+        <v>171</v>
+      </c>
+      <c r="C57" s="98"/>
+      <c r="D57" s="185">
+        <v>1173289.52</v>
+      </c>
+      <c r="E57" s="145">
+        <f t="shared" si="7"/>
+        <v>1078370.3978319999</v>
+      </c>
+      <c r="F57" s="133">
+        <f t="shared" si="8"/>
+        <v>94919.122168000002</v>
+      </c>
+      <c r="G57" s="108">
         <f t="shared" si="9"/>
-        <v>136210.62</v>
-      </c>
-      <c r="F56" s="133">
+        <v>1173289.52</v>
+      </c>
+      <c r="H57" s="156">
         <f t="shared" si="10"/>
-        <v>11989.38</v>
-      </c>
-      <c r="G56" s="108">
+        <v>1173289.52</v>
+      </c>
+      <c r="I57" s="173">
         <f t="shared" si="11"/>
-        <v>148200</v>
-      </c>
-      <c r="H56" s="159">
+        <v>0</v>
+      </c>
+      <c r="J57" s="173">
         <f t="shared" si="12"/>
-        <v>148200</v>
-      </c>
-      <c r="I56" s="176">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J56" s="176">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="94" t="s">
-        <v>9</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C57" s="7"/>
-      <c r="D57" s="112">
-        <v>129320</v>
-      </c>
-      <c r="E57" s="148">
-        <f>D57*91.91%</f>
-        <v>118858.01199999999</v>
-      </c>
-      <c r="F57" s="133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A58" s="197" t="s">
+        <v>162</v>
+      </c>
+      <c r="B58" s="198"/>
+      <c r="C58" s="199"/>
+      <c r="D58" s="185">
+        <v>67000</v>
+      </c>
+      <c r="E58" s="145">
+        <f t="shared" ref="E58:E63" si="13">D58</f>
+        <v>67000</v>
+      </c>
+      <c r="F58" s="133"/>
+      <c r="G58" s="108">
+        <f t="shared" si="9"/>
+        <v>67000</v>
+      </c>
+      <c r="H58" s="156">
         <f t="shared" si="10"/>
-        <v>10461.987999999999</v>
-      </c>
-      <c r="G57" s="108">
+        <v>67000</v>
+      </c>
+      <c r="I58" s="173">
         <f t="shared" si="11"/>
-        <v>129320</v>
-      </c>
-      <c r="H57" s="159">
-        <f>E57+F57</f>
-        <v>129319.99999999999</v>
-      </c>
-      <c r="I57" s="176">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J57" s="176">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="94" t="s">
-        <v>11</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="112">
-        <v>614674.98</v>
-      </c>
-      <c r="E58" s="148">
+        <v>0</v>
+      </c>
+      <c r="J58" s="173">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="197" t="s">
+        <v>175</v>
+      </c>
+      <c r="B59" s="198"/>
+      <c r="C59" s="199"/>
+      <c r="D59" s="185">
+        <v>1400000</v>
+      </c>
+      <c r="E59" s="145">
+        <f t="shared" ref="E59:E66" si="14">D59*91.91%</f>
+        <v>1286740</v>
+      </c>
+      <c r="F59" s="133">
+        <f t="shared" ref="F59:F66" si="15">D59*8.09%</f>
+        <v>113260</v>
+      </c>
+      <c r="G59" s="108">
         <f t="shared" si="9"/>
-        <v>564947.77411799994</v>
-      </c>
-      <c r="F58" s="133">
+        <v>1400000</v>
+      </c>
+      <c r="H59" s="156">
         <f t="shared" si="10"/>
-        <v>49727.205881999995</v>
-      </c>
-      <c r="G58" s="108">
+        <v>1400000</v>
+      </c>
+      <c r="I59" s="173">
         <f t="shared" si="11"/>
-        <v>614674.98</v>
-      </c>
-      <c r="H58" s="159">
-        <f t="shared" si="12"/>
-        <v>614674.98</v>
-      </c>
-      <c r="I58" s="176">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="176">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="94" t="s">
-        <v>11</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C59" s="7"/>
-      <c r="D59" s="112">
-        <v>641235.69999999995</v>
-      </c>
-      <c r="E59" s="148">
+        <v>0</v>
+      </c>
+      <c r="J59" s="173"/>
+    </row>
+    <row r="60" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="197" t="s">
+        <v>176</v>
+      </c>
+      <c r="B60" s="198"/>
+      <c r="C60" s="199"/>
+      <c r="D60" s="185">
+        <v>1000000</v>
+      </c>
+      <c r="E60" s="145">
+        <f t="shared" si="14"/>
+        <v>919099.99999999988</v>
+      </c>
+      <c r="F60" s="133">
+        <f t="shared" si="15"/>
+        <v>80900</v>
+      </c>
+      <c r="G60" s="108">
         <f t="shared" si="9"/>
-        <v>589359.7318699999</v>
-      </c>
-      <c r="F59" s="133">
-        <f t="shared" si="10"/>
-        <v>51875.968129999994</v>
-      </c>
-      <c r="G59" s="108">
-        <f t="shared" si="11"/>
-        <v>641235.69999999995</v>
-      </c>
-      <c r="H59" s="159">
-        <f t="shared" si="12"/>
-        <v>641235.69999999995</v>
-      </c>
-      <c r="I59" s="176">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="176">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="128" t="s">
-        <v>10</v>
-      </c>
-      <c r="B60" s="98" t="s">
-        <v>147</v>
-      </c>
-      <c r="C60" s="98"/>
-      <c r="D60" s="191">
-        <v>2180444.39</v>
-      </c>
-      <c r="E60" s="148">
-        <f t="shared" si="9"/>
-        <v>2004046.438849</v>
-      </c>
-      <c r="F60" s="133">
-        <f t="shared" si="10"/>
-        <v>176397.95115100002</v>
-      </c>
-      <c r="G60" s="108">
-        <f t="shared" si="11"/>
-        <v>2180444.39</v>
-      </c>
-      <c r="H60" s="159">
-        <f t="shared" si="12"/>
-        <v>2180444.39</v>
-      </c>
-      <c r="I60" s="176">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J60" s="176">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="196" t="s">
-        <v>178</v>
-      </c>
-      <c r="B61" s="197"/>
-      <c r="C61" s="198"/>
-      <c r="D61" s="191">
-        <v>67000</v>
-      </c>
-      <c r="E61" s="148">
-        <f t="shared" ref="E61:E67" si="13">D61</f>
-        <v>67000</v>
+        <v>1000000</v>
+      </c>
+      <c r="H60" s="156"/>
+      <c r="I60" s="173"/>
+      <c r="J60" s="173"/>
+    </row>
+    <row r="61" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="197" t="s">
+        <v>160</v>
+      </c>
+      <c r="B61" s="198"/>
+      <c r="C61" s="199"/>
+      <c r="D61" s="185">
+        <v>35500</v>
+      </c>
+      <c r="E61" s="145">
+        <f t="shared" si="13"/>
+        <v>35500</v>
       </c>
       <c r="F61" s="133"/>
       <c r="G61" s="108">
-        <f t="shared" si="11"/>
-        <v>67000</v>
-      </c>
-      <c r="H61" s="159">
-        <f t="shared" si="12"/>
-        <v>67000</v>
-      </c>
-      <c r="I61" s="176">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J61" s="176">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="187" t="s">
-        <v>145</v>
-      </c>
-      <c r="B62" s="188"/>
-      <c r="C62" s="185"/>
-      <c r="D62" s="112">
-        <v>90000</v>
-      </c>
-      <c r="E62" s="148">
+        <f t="shared" si="9"/>
+        <v>35500</v>
+      </c>
+      <c r="H61" s="156">
+        <f t="shared" si="10"/>
+        <v>35500</v>
+      </c>
+      <c r="I61" s="173"/>
+      <c r="J61" s="173"/>
+    </row>
+    <row r="62" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="197" t="s">
+        <v>161</v>
+      </c>
+      <c r="B62" s="198"/>
+      <c r="C62" s="199"/>
+      <c r="D62" s="185">
+        <v>159500</v>
+      </c>
+      <c r="E62" s="145">
         <f t="shared" si="13"/>
-        <v>90000</v>
+        <v>159500</v>
       </c>
       <c r="F62" s="133"/>
       <c r="G62" s="108">
-        <f t="shared" si="11"/>
-        <v>90000</v>
-      </c>
-      <c r="H62" s="159">
-        <f t="shared" si="12"/>
-        <v>90000</v>
-      </c>
-      <c r="I62" s="176">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J62" s="176">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B63" s="113"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="112">
-        <v>29200</v>
-      </c>
-      <c r="E63" s="148">
-        <f t="shared" si="13"/>
-        <v>29200</v>
-      </c>
-      <c r="F63" s="133"/>
-      <c r="G63" s="108">
-        <f t="shared" si="11"/>
-        <v>29200</v>
-      </c>
-      <c r="H63" s="159">
-        <f t="shared" si="12"/>
-        <v>29200</v>
-      </c>
-      <c r="I63" s="176">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J63" s="176"/>
-    </row>
-    <row r="64" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="196" t="s">
-        <v>156</v>
-      </c>
-      <c r="B64" s="197"/>
-      <c r="C64" s="198"/>
-      <c r="D64" s="112">
-        <f>380000+350000</f>
-        <v>730000</v>
-      </c>
-      <c r="E64" s="148">
-        <f t="shared" ref="E64:E73" si="14">D64*91.91%</f>
-        <v>670942.99999999988</v>
-      </c>
-      <c r="F64" s="133">
-        <f t="shared" ref="F64:F72" si="15">D64*8.09%</f>
-        <v>59057</v>
-      </c>
-      <c r="G64" s="108">
-        <f t="shared" si="11"/>
-        <v>730000</v>
-      </c>
-      <c r="H64" s="159">
-        <f t="shared" si="12"/>
-        <v>729999.99999999988</v>
-      </c>
-      <c r="I64" s="176">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J64" s="176"/>
-    </row>
-    <row r="65" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="196" t="s">
-        <v>176</v>
-      </c>
-      <c r="B65" s="197"/>
-      <c r="C65" s="198"/>
-      <c r="D65" s="191">
-        <v>35500</v>
-      </c>
-      <c r="E65" s="148">
-        <f t="shared" si="13"/>
-        <v>35500</v>
-      </c>
-      <c r="F65" s="133"/>
-      <c r="G65" s="108"/>
-      <c r="H65" s="159"/>
-      <c r="I65" s="176"/>
-      <c r="J65" s="176"/>
-    </row>
-    <row r="66" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="196" t="s">
-        <v>177</v>
-      </c>
-      <c r="B66" s="197"/>
-      <c r="C66" s="198"/>
-      <c r="D66" s="191">
+        <f t="shared" si="9"/>
         <v>159500</v>
       </c>
-      <c r="E66" s="148">
-        <f t="shared" si="13"/>
+      <c r="H62" s="156">
+        <f t="shared" si="10"/>
         <v>159500</v>
       </c>
-      <c r="F66" s="133"/>
-      <c r="G66" s="108"/>
-      <c r="H66" s="159"/>
-      <c r="I66" s="176"/>
-      <c r="J66" s="176"/>
-    </row>
-    <row r="67" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="196" t="s">
-        <v>175</v>
-      </c>
-      <c r="B67" s="197"/>
-      <c r="C67" s="198"/>
-      <c r="D67" s="191">
+      <c r="I62" s="173"/>
+      <c r="J62" s="173"/>
+    </row>
+    <row r="63" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="197" t="s">
+        <v>159</v>
+      </c>
+      <c r="B63" s="198"/>
+      <c r="C63" s="199"/>
+      <c r="D63" s="185">
         <v>170000</v>
       </c>
-      <c r="E67" s="148">
+      <c r="E63" s="145">
         <f t="shared" si="13"/>
         <v>170000</v>
       </c>
-      <c r="F67" s="7"/>
-      <c r="G67" s="108"/>
-      <c r="H67" s="159"/>
-      <c r="I67" s="176"/>
-      <c r="J67" s="176"/>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A68" s="98" t="s">
-        <v>142</v>
-      </c>
-      <c r="B68" s="98" t="s">
-        <v>155</v>
-      </c>
-      <c r="C68" s="98"/>
-      <c r="D68" s="112">
-        <v>232510.18</v>
-      </c>
-      <c r="E68" s="148">
-        <f t="shared" si="14"/>
-        <v>213700.10643799999</v>
-      </c>
-      <c r="F68" s="133">
-        <f t="shared" si="15"/>
-        <v>18810.073561999998</v>
-      </c>
-      <c r="G68" s="108">
-        <f t="shared" si="11"/>
-        <v>232510.18</v>
-      </c>
-      <c r="H68" s="159">
-        <f t="shared" si="12"/>
-        <v>232510.18</v>
-      </c>
-      <c r="I68" s="176">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J68" s="176">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="M68" s="190" t="s">
+      <c r="F63" s="7"/>
+      <c r="G63" s="108">
+        <f t="shared" si="9"/>
+        <v>170000</v>
+      </c>
+      <c r="H63" s="156">
+        <f t="shared" si="10"/>
+        <v>170000</v>
+      </c>
+      <c r="I63" s="173"/>
+      <c r="J63" s="173"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" s="98" t="s">
         <v>137</v>
       </c>
-      <c r="N68" s="7"/>
-      <c r="O68" s="7"/>
-      <c r="P68" s="191">
-        <v>357622.29</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A69" s="98" t="s">
-        <v>137</v>
-      </c>
-      <c r="B69" s="98" t="s">
-        <v>155</v>
-      </c>
-      <c r="C69" s="98"/>
-      <c r="D69" s="191">
+      <c r="B64" s="98" t="s">
+        <v>144</v>
+      </c>
+      <c r="C64" s="98"/>
+      <c r="D64" s="185">
         <v>141112.26</v>
       </c>
-      <c r="E69" s="148">
+      <c r="E64" s="145">
         <f t="shared" si="14"/>
         <v>129696.278166</v>
       </c>
-      <c r="F69" s="133">
+      <c r="F64" s="133">
         <f t="shared" si="15"/>
         <v>11415.981834</v>
       </c>
-      <c r="G69" s="108">
+      <c r="G64" s="108">
+        <f t="shared" si="9"/>
+        <v>141112.26</v>
+      </c>
+      <c r="H64" s="156">
+        <f t="shared" si="10"/>
+        <v>141112.26</v>
+      </c>
+      <c r="I64" s="173">
         <f t="shared" si="11"/>
-        <v>141112.26</v>
-      </c>
-      <c r="H69" s="159">
+        <v>0</v>
+      </c>
+      <c r="J64" s="173">
         <f t="shared" si="12"/>
-        <v>141112.26</v>
-      </c>
-      <c r="I69" s="176">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J69" s="176">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="M69" s="190" t="s">
+        <v>0</v>
+      </c>
+      <c r="M64" s="184" t="s">
         <v>137</v>
       </c>
-      <c r="N69" s="7"/>
-      <c r="O69" s="7"/>
-      <c r="P69" s="191">
+      <c r="N64" s="7"/>
+      <c r="O64" s="7"/>
+      <c r="P64" s="185">
         <v>358487.12</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A70" s="98" t="s">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="98" t="s">
         <v>137</v>
       </c>
-      <c r="B70" s="98" t="s">
-        <v>155</v>
-      </c>
-      <c r="C70" s="98"/>
-      <c r="D70" s="191">
+      <c r="B65" s="98" t="s">
+        <v>144</v>
+      </c>
+      <c r="C65" s="98"/>
+      <c r="D65" s="185">
         <v>199992.75</v>
       </c>
-      <c r="E70" s="148">
+      <c r="E65" s="145">
         <f t="shared" si="14"/>
         <v>183813.33652499999</v>
       </c>
-      <c r="F70" s="133">
+      <c r="F65" s="133">
         <f t="shared" si="15"/>
         <v>16179.413474999999</v>
       </c>
-      <c r="G70" s="108">
+      <c r="G65" s="108">
+        <f t="shared" si="9"/>
+        <v>199992.75</v>
+      </c>
+      <c r="H65" s="156">
+        <f t="shared" si="10"/>
+        <v>199992.75</v>
+      </c>
+      <c r="I65" s="173">
         <f t="shared" si="11"/>
-        <v>199992.75</v>
-      </c>
-      <c r="H70" s="159">
+        <v>0</v>
+      </c>
+      <c r="J65" s="173">
         <f t="shared" si="12"/>
-        <v>199992.75</v>
-      </c>
-      <c r="I70" s="176">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J70" s="176">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B71" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C71" s="7"/>
-      <c r="D71" s="112">
-        <v>83283.39</v>
-      </c>
-      <c r="E71" s="148">
+      <c r="B66" s="7"/>
+      <c r="C66" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D66" s="185"/>
+      <c r="E66" s="145">
         <f t="shared" si="14"/>
-        <v>76545.763748999991</v>
-      </c>
-      <c r="F71" s="133">
+        <v>0</v>
+      </c>
+      <c r="F66" s="133">
         <f t="shared" si="15"/>
-        <v>6737.6262509999997</v>
-      </c>
-      <c r="G71" s="108">
+        <v>0</v>
+      </c>
+      <c r="G66" s="108">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H66" s="156">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I66" s="173">
         <f t="shared" si="11"/>
-        <v>83283.39</v>
-      </c>
-      <c r="H71" s="159">
+        <v>0</v>
+      </c>
+      <c r="J66" s="173">
         <f t="shared" si="12"/>
-        <v>83283.389999999985</v>
-      </c>
-      <c r="I71" s="176">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J71" s="176">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="190"/>
-      <c r="B72" s="113"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="98" t="s">
+        <v>168</v>
+      </c>
+      <c r="B67" s="113"/>
+      <c r="C67" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D67" s="185">
         <v>260000</v>
       </c>
-      <c r="E72" s="148">
-        <f t="shared" ref="E72:E75" si="16">D72</f>
+      <c r="E67" s="145">
+        <f t="shared" ref="E67:E70" si="16">D67</f>
         <v>260000</v>
       </c>
-      <c r="F72" s="133"/>
-      <c r="G72" s="108">
+      <c r="F67" s="133"/>
+      <c r="G67" s="108">
+        <f t="shared" si="9"/>
+        <v>260000</v>
+      </c>
+      <c r="H67" s="156">
+        <f t="shared" si="10"/>
+        <v>260000</v>
+      </c>
+      <c r="I67" s="173">
         <f t="shared" si="11"/>
-        <v>260000</v>
-      </c>
-      <c r="H72" s="159">
+        <v>0</v>
+      </c>
+      <c r="J67" s="173">
         <f t="shared" si="12"/>
-        <v>260000</v>
-      </c>
-      <c r="I72" s="176">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J72" s="176">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="190"/>
-      <c r="B73" s="113"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="98" t="s">
+        <v>169</v>
+      </c>
+      <c r="B68" s="113"/>
+      <c r="C68" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D68" s="185">
         <v>256310.6</v>
       </c>
-      <c r="E73" s="148">
+      <c r="E68" s="145">
         <f t="shared" si="16"/>
         <v>256310.6</v>
       </c>
-      <c r="F73" s="133"/>
-      <c r="G73" s="108"/>
-      <c r="H73" s="159"/>
-      <c r="I73" s="176"/>
-      <c r="J73" s="176"/>
-    </row>
-    <row r="74" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="190"/>
-      <c r="B74" s="113"/>
-      <c r="C74" s="160"/>
-      <c r="D74" s="191">
-        <v>124007</v>
-      </c>
-      <c r="E74" s="148">
+      <c r="F68" s="133"/>
+      <c r="G68" s="108">
+        <f t="shared" si="9"/>
+        <v>256310.6</v>
+      </c>
+      <c r="H68" s="156">
+        <f t="shared" si="10"/>
+        <v>256310.6</v>
+      </c>
+      <c r="I68" s="173"/>
+      <c r="J68" s="173"/>
+    </row>
+    <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="98" t="s">
+        <v>172</v>
+      </c>
+      <c r="B69" s="113"/>
+      <c r="C69" s="157"/>
+      <c r="D69" s="185">
+        <v>248007.9</v>
+      </c>
+      <c r="E69" s="145">
         <f t="shared" si="16"/>
-        <v>124007</v>
-      </c>
-      <c r="F74" s="133"/>
-      <c r="G74" s="108">
+        <v>248007.9</v>
+      </c>
+      <c r="F69" s="133"/>
+      <c r="G69" s="108">
+        <f t="shared" si="9"/>
+        <v>248007.9</v>
+      </c>
+      <c r="H69" s="156">
+        <f t="shared" si="10"/>
+        <v>248007.9</v>
+      </c>
+      <c r="I69" s="173">
         <f t="shared" si="11"/>
-        <v>124007</v>
-      </c>
-      <c r="H74" s="159">
+        <v>0</v>
+      </c>
+      <c r="J69" s="173">
         <f t="shared" si="12"/>
-        <v>124007</v>
-      </c>
-      <c r="I74" s="176">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J74" s="176">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A75" s="251"/>
-      <c r="B75" s="154"/>
-      <c r="C75" s="154"/>
-      <c r="D75" s="250">
-        <v>123999.96</v>
-      </c>
-      <c r="E75" s="148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="190" t="s">
+        <v>173</v>
+      </c>
+      <c r="B70" s="151"/>
+      <c r="C70" s="151"/>
+      <c r="D70" s="188">
+        <v>25000</v>
+      </c>
+      <c r="E70" s="145">
         <f t="shared" si="16"/>
-        <v>123999.96</v>
-      </c>
-      <c r="F75" s="133"/>
-      <c r="G75" s="108">
-        <f t="shared" si="11"/>
-        <v>123999.96</v>
-      </c>
-      <c r="H75" s="159">
+        <v>25000</v>
+      </c>
+      <c r="F70" s="133"/>
+      <c r="G70" s="108">
+        <f t="shared" si="9"/>
+        <v>25000</v>
+      </c>
+      <c r="H70" s="156">
+        <f t="shared" si="10"/>
+        <v>25000</v>
+      </c>
+      <c r="I70" t="str">
+        <f>IF(G70=H70, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J70" s="173">
         <f t="shared" si="12"/>
-        <v>123999.96</v>
-      </c>
-      <c r="I75" t="str">
-        <f>IF(G75=H75, "", "Error")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="95" t="s">
+        <v>12</v>
+      </c>
+      <c r="B71" s="96"/>
+      <c r="C71" s="96"/>
+      <c r="D71" s="107">
+        <f>SUM(D51:D70)</f>
+        <v>5945233.0299999993</v>
+      </c>
+      <c r="E71" s="107">
+        <f>SUM(E51:E70)</f>
+        <v>5606107.1445229994</v>
+      </c>
+      <c r="F71" s="107">
+        <f>SUM(F51:F70)</f>
+        <v>339125.88547699997</v>
+      </c>
+      <c r="G71" s="108">
+        <f>E71+F71</f>
+        <v>5945233.0299999993</v>
+      </c>
+      <c r="H71" s="146" t="str">
+        <f>IF(D71=G71, "", "Error")</f>
         <v/>
       </c>
-      <c r="J75" s="176">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A76" s="95" t="s">
-        <v>12</v>
-      </c>
-      <c r="B76" s="96"/>
-      <c r="C76" s="96"/>
-      <c r="D76" s="107">
-        <f>SUM(D51:D75)</f>
-        <v>8221915.879999999</v>
-      </c>
-      <c r="E76" s="107">
-        <f>SUM(E51:E75)</f>
-        <v>7783891.0559119983</v>
-      </c>
-      <c r="F76" s="107">
-        <f>SUM(F51:F75)</f>
-        <v>438024.82408799999</v>
-      </c>
-      <c r="G76" s="108">
-        <f>E76+F76</f>
-        <v>8221915.879999998</v>
-      </c>
-      <c r="H76" s="149" t="str">
-        <f>IF(D76=G76, "", "Error")</f>
+      <c r="I71" s="173">
+        <f>D71-G71</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="7"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="178"/>
+      <c r="E72" s="114"/>
+      <c r="F72" s="7"/>
+      <c r="H72" s="146"/>
+    </row>
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="7"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="178"/>
+      <c r="E73" s="113"/>
+      <c r="F73" s="7"/>
+      <c r="H73" s="146"/>
+    </row>
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="7"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="178"/>
+      <c r="E74" s="113"/>
+      <c r="F74" s="7"/>
+      <c r="H74" s="146"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="94" t="s">
+        <v>141</v>
+      </c>
+      <c r="B75" s="98"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="185">
+        <v>124980</v>
+      </c>
+      <c r="E75" s="145">
+        <f>D75*91.91%</f>
+        <v>114869.11799999999</v>
+      </c>
+      <c r="F75" s="133">
+        <f>D75*8.09%</f>
+        <v>10110.882</v>
+      </c>
+      <c r="G75" s="155"/>
+      <c r="H75" s="146"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="7"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="112"/>
+      <c r="E76" s="159">
+        <f>D76</f>
+        <v>0</v>
+      </c>
+      <c r="F76" s="7"/>
+      <c r="H76" s="146"/>
+      <c r="I76" s="108"/>
+    </row>
+    <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="95" t="s">
+        <v>16</v>
+      </c>
+      <c r="B77" s="95"/>
+      <c r="C77" s="95"/>
+      <c r="D77" s="107">
+        <f>SUM(D75:D76)</f>
+        <v>124980</v>
+      </c>
+      <c r="E77" s="107">
+        <f>SUM(E75:E76)</f>
+        <v>114869.11799999999</v>
+      </c>
+      <c r="F77" s="107">
+        <f>SUM(F75:F76)</f>
+        <v>10110.882</v>
+      </c>
+      <c r="G77" s="108">
+        <f>E77+F77</f>
+        <v>124979.99999999999</v>
+      </c>
+      <c r="H77" s="146" t="str">
+        <f>IF(D77=G77, "", "Error")</f>
         <v/>
       </c>
-      <c r="I76" s="176">
-        <f>D76-G76</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="181"/>
-      <c r="E77" s="114"/>
-      <c r="F77" s="7"/>
-      <c r="H77" s="149"/>
-    </row>
-    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="J77" s="108"/>
+    </row>
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
-      <c r="D78" s="181"/>
-      <c r="E78" s="113"/>
+      <c r="D78" s="178"/>
+      <c r="E78" s="114"/>
       <c r="F78" s="7"/>
-      <c r="H78" s="149"/>
-    </row>
-    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H78" s="146"/>
+    </row>
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
-      <c r="D79" s="181"/>
+      <c r="D79" s="178"/>
       <c r="E79" s="113"/>
       <c r="F79" s="7"/>
-      <c r="H79" s="149"/>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="H79" s="146"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="94" t="s">
-        <v>146</v>
-      </c>
-      <c r="B80" s="98"/>
+        <v>13</v>
+      </c>
+      <c r="B80" s="7"/>
       <c r="C80" s="7"/>
-      <c r="D80" s="191">
-        <v>124980</v>
-      </c>
-      <c r="E80" s="148">
-        <f>D80*91.91%</f>
-        <v>114869.11799999999</v>
-      </c>
-      <c r="F80" s="133">
-        <f>D80*8.09%</f>
-        <v>10110.882</v>
-      </c>
-      <c r="G80" s="158"/>
-      <c r="H80" s="149"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A81" s="7"/>
-      <c r="B81" s="7"/>
+      <c r="D80" s="178"/>
+      <c r="E80" s="113"/>
+      <c r="F80" s="7"/>
+      <c r="H80" s="146"/>
+    </row>
+    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="94" t="s">
+        <v>14</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>116</v>
+      </c>
       <c r="C81" s="7"/>
-      <c r="D81" s="112"/>
-      <c r="E81" s="162">
-        <f>D81</f>
-        <v>0</v>
-      </c>
-      <c r="F81" s="7"/>
-      <c r="H81" s="149"/>
-      <c r="I81" s="108"/>
-    </row>
-    <row r="82" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="95" t="s">
-        <v>16</v>
-      </c>
-      <c r="B82" s="95"/>
-      <c r="C82" s="95"/>
-      <c r="D82" s="107">
-        <f>SUM(D80:D81)</f>
-        <v>124980</v>
-      </c>
-      <c r="E82" s="107">
-        <f>SUM(E80:E81)</f>
-        <v>114869.11799999999</v>
-      </c>
-      <c r="F82" s="107">
-        <f>SUM(F80:F81)</f>
-        <v>10110.882</v>
-      </c>
-      <c r="G82" s="108">
-        <f>E82+F82</f>
-        <v>124979.99999999999</v>
-      </c>
-      <c r="H82" s="149" t="str">
-        <f>IF(D82=G82, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J82" s="108"/>
-    </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D81" s="185">
+        <v>246000</v>
+      </c>
+      <c r="E81" s="145">
+        <f>D81*91.91%</f>
+        <v>226098.59999999998</v>
+      </c>
+      <c r="F81" s="133">
+        <f>D81*8.09%</f>
+        <v>19901.400000000001</v>
+      </c>
+      <c r="G81" t="s">
+        <v>139</v>
+      </c>
+      <c r="H81" s="146"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="94" t="s">
+        <v>107</v>
+      </c>
+      <c r="B82" s="7"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="185">
+        <v>30000</v>
+      </c>
+      <c r="E82" s="145">
+        <f>D82*91.91%</f>
+        <v>27572.999999999996</v>
+      </c>
+      <c r="F82" s="133">
+        <f>D82*8.09%</f>
+        <v>2427</v>
+      </c>
+      <c r="H82" s="146"/>
+      <c r="J82" s="112"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
-      <c r="D83" s="181"/>
-      <c r="E83" s="114"/>
+      <c r="D83" s="178"/>
+      <c r="E83" s="115"/>
       <c r="F83" s="7"/>
-      <c r="H83" s="149"/>
-    </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="7"/>
-      <c r="B84" s="7"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="181"/>
-      <c r="E84" s="113"/>
-      <c r="F84" s="7"/>
-      <c r="H84" s="149"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H83" s="146"/>
+      <c r="J83" s="108"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="95" t="s">
+        <v>100</v>
+      </c>
+      <c r="B84" s="95"/>
+      <c r="C84" s="95"/>
+      <c r="D84" s="107">
+        <f>SUM(D81:D83)</f>
+        <v>276000</v>
+      </c>
+      <c r="E84" s="107">
+        <f>SUM(E81:E83)</f>
+        <v>253671.59999999998</v>
+      </c>
+      <c r="F84" s="107">
+        <f>SUM(F81:F83)</f>
+        <v>22328.400000000001</v>
+      </c>
+      <c r="G84" s="108">
+        <f>E84+F84</f>
+        <v>276000</v>
+      </c>
+      <c r="H84" s="146" t="str">
+        <f>IF(D84=G84, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J84" s="108"/>
+    </row>
+    <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="94" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
-      <c r="D85" s="181"/>
-      <c r="E85" s="113"/>
+      <c r="D85" s="112"/>
+      <c r="E85" s="116"/>
       <c r="F85" s="7"/>
-      <c r="H85" s="149"/>
-    </row>
-    <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H85" s="146"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="94" t="s">
-        <v>14</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>116</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="B86" s="7"/>
       <c r="C86" s="7"/>
-      <c r="D86" s="112">
-        <v>246000</v>
-      </c>
-      <c r="E86" s="148">
+      <c r="D86" s="185">
+        <v>114083.66</v>
+      </c>
+      <c r="E86" s="145">
         <f>D86*91.91%</f>
-        <v>226098.59999999998</v>
+        <v>104854.291906</v>
       </c>
       <c r="F86" s="133">
         <f>D86*8.09%</f>
-        <v>19901.400000000001</v>
-      </c>
-      <c r="G86" t="s">
-        <v>141</v>
-      </c>
-      <c r="H86" s="149"/>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+        <v>9229.3680939999995</v>
+      </c>
+      <c r="H86" s="146"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="94" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B87" s="7"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="112">
-        <v>30000</v>
-      </c>
-      <c r="E87" s="148">
+      <c r="C87" s="121"/>
+      <c r="D87" s="185">
+        <v>44400</v>
+      </c>
+      <c r="E87" s="145">
         <f>D87*91.91%</f>
-        <v>27572.999999999996</v>
+        <v>40808.039999999994</v>
       </c>
       <c r="F87" s="133">
         <f>D87*8.09%</f>
-        <v>2427</v>
-      </c>
-      <c r="H87" s="149"/>
-      <c r="J87" s="112"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88" s="7"/>
-      <c r="B88" s="7"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="181"/>
-      <c r="E88" s="115"/>
-      <c r="F88" s="7"/>
-      <c r="H88" s="149"/>
-      <c r="J88" s="108"/>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A89" s="95" t="s">
-        <v>100</v>
-      </c>
-      <c r="B89" s="95"/>
-      <c r="C89" s="95"/>
-      <c r="D89" s="107">
-        <f>SUM(D86:D88)</f>
-        <v>276000</v>
-      </c>
-      <c r="E89" s="107">
-        <f>SUM(E86:E88)</f>
-        <v>253671.59999999998</v>
-      </c>
-      <c r="F89" s="107">
-        <f>SUM(F86:F88)</f>
-        <v>22328.400000000001</v>
-      </c>
-      <c r="G89" s="108">
-        <f>E89+F89</f>
-        <v>276000</v>
-      </c>
-      <c r="H89" s="149" t="str">
-        <f>IF(D89=G89, "", "Error")</f>
+        <v>3591.96</v>
+      </c>
+      <c r="H87" s="146"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" s="95"/>
+      <c r="C88" s="95"/>
+      <c r="D88" s="153">
+        <f>SUM(D86:D87)</f>
+        <v>158483.66</v>
+      </c>
+      <c r="E88" s="143">
+        <f t="shared" ref="E88:F88" si="17">SUM(E86:E87)</f>
+        <v>145662.33190599998</v>
+      </c>
+      <c r="F88" s="143">
+        <f t="shared" si="17"/>
+        <v>12821.328094</v>
+      </c>
+      <c r="G88" s="108">
+        <f>E88+F88</f>
+        <v>158483.65999999997</v>
+      </c>
+      <c r="H88" s="146" t="str">
+        <f>IF(D88=G88, "", "Error")</f>
         <v/>
       </c>
-      <c r="J89" s="108"/>
-    </row>
-    <row r="90" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="7"/>
-      <c r="B90" s="7"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="112"/>
-      <c r="E90" s="116"/>
-      <c r="F90" s="7"/>
-      <c r="H90" s="149"/>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A91" s="94" t="s">
-        <v>101</v>
-      </c>
-      <c r="B91" s="7"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="112">
-        <v>126577.59</v>
-      </c>
-      <c r="E91" s="148">
-        <f>D91*91.91%</f>
-        <v>116337.46296899999</v>
-      </c>
-      <c r="F91" s="133">
-        <f>D91*8.09%</f>
-        <v>10240.127031</v>
-      </c>
-      <c r="H91" s="149"/>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A92" s="94" t="s">
-        <v>102</v>
-      </c>
-      <c r="B92" s="7"/>
-      <c r="C92" s="121"/>
-      <c r="D92" s="112">
-        <v>44400</v>
-      </c>
-      <c r="E92" s="148">
-        <f>D92*91.91%</f>
-        <v>40808.039999999994</v>
-      </c>
-      <c r="F92" s="133">
-        <f>D92*8.09%</f>
-        <v>3591.96</v>
-      </c>
-      <c r="H92" s="149"/>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A93" s="95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" s="95"/>
-      <c r="C93" s="95"/>
-      <c r="D93" s="156">
-        <f>SUM(D91:D92)</f>
-        <v>170977.59</v>
-      </c>
-      <c r="E93" s="146">
-        <f t="shared" ref="E93:F93" si="17">SUM(E91:E92)</f>
-        <v>157145.50296899996</v>
-      </c>
-      <c r="F93" s="146">
-        <f t="shared" si="17"/>
-        <v>13832.087030999999</v>
-      </c>
-      <c r="G93" s="108">
-        <f>E93+F93</f>
-        <v>170977.58999999997</v>
-      </c>
-      <c r="H93" s="149" t="str">
-        <f>IF(D93=G93, "", "Error")</f>
+    </row>
+    <row r="89" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="7"/>
+      <c r="B89" s="7"/>
+      <c r="C89" s="7"/>
+      <c r="D89" s="179"/>
+      <c r="E89" s="12"/>
+      <c r="F89" s="7"/>
+      <c r="H89" s="146"/>
+    </row>
+    <row r="90" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="99" t="s">
+        <v>133</v>
+      </c>
+      <c r="B90" s="99"/>
+      <c r="C90" s="99"/>
+      <c r="D90" s="180"/>
+      <c r="E90" s="117">
+        <f>D90*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F90" s="135">
+        <f>D90*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G90" s="108">
+        <f>E90+F90</f>
+        <v>0</v>
+      </c>
+      <c r="H90" s="146" t="str">
+        <f>IF(D90=G90, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="7"/>
-      <c r="B94" s="7"/>
-      <c r="C94" s="7"/>
-      <c r="D94" s="182"/>
-      <c r="E94" s="12"/>
-      <c r="F94" s="7"/>
-      <c r="H94" s="149"/>
-    </row>
-    <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="99" t="s">
-        <v>133</v>
-      </c>
-      <c r="B95" s="99"/>
-      <c r="C95" s="99"/>
-      <c r="D95" s="183"/>
-      <c r="E95" s="117">
-        <f>D95*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F95" s="135">
-        <f>D95*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G95" s="108">
-        <f>E95+F95</f>
-        <v>0</v>
-      </c>
-      <c r="H95" s="149" t="str">
-        <f>IF(D95=G95, "", "Error")</f>
+    <row r="91" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="1"/>
+      <c r="D91" s="177"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="10"/>
+      <c r="G91" s="152"/>
+      <c r="H91" s="146"/>
+    </row>
+    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B92" s="60"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="181">
+        <f>SUM(D90+D88+D84+D77+D71+D49+D32+D27+D44)</f>
+        <v>8226649.5599999996</v>
+      </c>
+      <c r="E92" s="144">
+        <f>SUM(E90+E88+E84+E77+E71+E49+E32+E27+E44)</f>
+        <v>7702957.0772459991</v>
+      </c>
+      <c r="F92" s="144">
+        <f>SUM(F90+F88+F84+F77+F71+F49+F32+F27+F44)</f>
+        <v>523692.482754</v>
+      </c>
+      <c r="G92" s="108">
+        <f>E92+F92</f>
+        <v>8226649.5599999987</v>
+      </c>
+      <c r="H92" s="146" t="str">
+        <f>IF(D92=G92, "", "Error")</f>
         <v/>
       </c>
-    </row>
-    <row r="96" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I92" s="173">
+        <f>D92-G92</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D93" s="177"/>
+      <c r="E93" s="108"/>
+    </row>
+    <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="191" t="s">
+        <v>177</v>
+      </c>
+      <c r="B94" s="140"/>
+      <c r="C94" s="140"/>
+      <c r="E94" s="108"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="1"/>
+      <c r="C95" s="138"/>
+      <c r="E95" s="108"/>
+    </row>
+    <row r="96" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
-      <c r="D96" s="180"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="10"/>
-      <c r="G96" s="155"/>
-      <c r="H96" s="149"/>
-    </row>
-    <row r="97" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B97" s="60"/>
-      <c r="C97" s="5"/>
-      <c r="D97" s="184">
-        <f>SUM(D95+D93+D89+D82+D76+D49+D32+D27+D44)</f>
-        <v>10825310.289999999</v>
-      </c>
-      <c r="E97" s="147">
-        <f>SUM(E95+E93+E89+E82+E76+E49+E32+E27+E44)</f>
-        <v>10176670.858142998</v>
-      </c>
-      <c r="F97" s="147">
-        <f>SUM(F95+F93+F89+F82+F76+F49+F32+F27+F44)</f>
-        <v>648639.43185699999</v>
-      </c>
-      <c r="G97" s="108">
-        <f>E97+F97</f>
-        <v>10825310.289999997</v>
-      </c>
-      <c r="H97" s="149" t="str">
-        <f>IF(D97=G97, "", "Error")</f>
+      <c r="C96" s="138"/>
+      <c r="E96" s="108"/>
+    </row>
+    <row r="97" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="141" t="s">
+        <v>29</v>
+      </c>
+      <c r="B97" s="142"/>
+      <c r="C97" s="139">
+        <f>SUM(C95:C96)</f>
+        <v>0</v>
+      </c>
+      <c r="E97" s="108"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E98" s="108"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E99" s="136"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="220" t="s">
+        <v>113</v>
+      </c>
+      <c r="B100" s="221"/>
+      <c r="C100" s="221"/>
+      <c r="D100" s="221"/>
+      <c r="E100" s="166" t="s">
+        <v>21</v>
+      </c>
+      <c r="F100" s="167" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="217"/>
+      <c r="B101" s="218"/>
+      <c r="C101" s="219"/>
+      <c r="D101" s="161"/>
+      <c r="E101" s="145"/>
+      <c r="F101" s="133"/>
+    </row>
+    <row r="102" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="214"/>
+      <c r="B102" s="215"/>
+      <c r="C102" s="168"/>
+      <c r="D102" s="112"/>
+      <c r="E102" s="145">
+        <f t="shared" ref="E102:E103" si="18">D102*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F102" s="133">
+        <f t="shared" ref="F102:F103" si="19">D102*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="214"/>
+      <c r="B103" s="215"/>
+      <c r="C103" s="168"/>
+      <c r="D103" s="112"/>
+      <c r="E103" s="145">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="F103" s="133">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="214"/>
+      <c r="B104" s="215"/>
+      <c r="C104" s="216"/>
+      <c r="D104" s="112"/>
+      <c r="E104" s="145">
+        <f>D104*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F104" s="133">
+        <f>D104*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="211" t="s">
+        <v>29</v>
+      </c>
+      <c r="B105" s="212"/>
+      <c r="C105" s="213"/>
+      <c r="D105" s="165">
+        <f>SUM(D101:D104)</f>
+        <v>0</v>
+      </c>
+      <c r="E105" s="165">
+        <f>SUM(E101:E104)</f>
+        <v>0</v>
+      </c>
+      <c r="F105" s="165">
+        <f>SUM(F101:F104)</f>
+        <v>0</v>
+      </c>
+      <c r="H105" s="108">
+        <f>E105+F105</f>
+        <v>0</v>
+      </c>
+      <c r="I105" s="146" t="str">
+        <f>IF(D105=H105, "", "Error")</f>
         <v/>
       </c>
-      <c r="I97" s="176">
-        <f>D97-G97</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D98" s="180"/>
-      <c r="E98" s="108"/>
-    </row>
-    <row r="99" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="141" t="s">
+    </row>
+    <row r="107" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E107" s="108"/>
+    </row>
+    <row r="108" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="102" t="s">
+        <v>104</v>
+      </c>
+      <c r="B108" s="103">
+        <f>D92</f>
+        <v>8226649.5599999996</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="104" t="s">
+        <v>106</v>
+      </c>
+      <c r="B109" s="105">
+        <f>D92-D90</f>
+        <v>8226649.5599999996</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D110" s="201"/>
+      <c r="E110" s="201"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="74" t="s">
+        <v>90</v>
+      </c>
+      <c r="B111" s="75"/>
+      <c r="C111" s="76"/>
+      <c r="D111" s="201"/>
+      <c r="E111" s="201"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="B112" s="11">
+        <v>-3599025.7822533529</v>
+      </c>
+      <c r="C112" s="78"/>
+      <c r="D112" s="201"/>
+      <c r="E112" s="201"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="79" t="s">
+        <v>92</v>
+      </c>
+      <c r="B113" s="92">
+        <f>PRORRATEO!G52</f>
+        <v>8723308.1338689979</v>
+      </c>
+      <c r="C113" s="78" t="s">
+        <v>93</v>
+      </c>
+      <c r="D113" s="201"/>
+      <c r="E113" s="201"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="79" t="s">
+        <v>115</v>
+      </c>
+      <c r="B114" s="170">
+        <f>-B109</f>
+        <v>-8226649.5599999996</v>
+      </c>
+      <c r="C114" s="76"/>
+      <c r="D114" s="201"/>
+      <c r="E114" s="201"/>
+      <c r="G114" s="112"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="79" t="s">
+        <v>114</v>
+      </c>
+      <c r="B115" s="170">
+        <f>-D105</f>
+        <v>0</v>
+      </c>
+      <c r="C115" s="76"/>
+      <c r="D115" s="201"/>
+      <c r="E115" s="201"/>
+      <c r="G115" s="124"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="79" t="s">
+        <v>105</v>
+      </c>
+      <c r="B116" s="170">
+        <f>-B123</f>
+        <v>-40000</v>
+      </c>
+      <c r="C116" s="80"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="B99" s="140"/>
-      <c r="C99" s="140"/>
-      <c r="E99" s="108"/>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A100" s="1"/>
-      <c r="C100" s="138"/>
-      <c r="E100" s="108"/>
-    </row>
-    <row r="101" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="1"/>
-      <c r="C101" s="138"/>
-      <c r="E101" s="108"/>
-    </row>
-    <row r="102" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="142" t="s">
+      <c r="B117" s="93">
+        <f>-C97</f>
+        <v>0</v>
+      </c>
+      <c r="C117" s="80"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="79"/>
+      <c r="B118" s="75"/>
+      <c r="C118" s="80"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="77" t="s">
+        <v>94</v>
+      </c>
+      <c r="B119" s="81">
+        <f>SUM(B112:B118)</f>
+        <v>-3142367.2083843546</v>
+      </c>
+      <c r="C119" s="150"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="80"/>
+      <c r="C120" s="76"/>
+      <c r="D120" s="83"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C121" s="76"/>
+      <c r="D121" s="108"/>
+      <c r="E121" s="173"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="74" t="s">
+        <v>95</v>
+      </c>
+      <c r="B122" s="11">
+        <v>-352694.54000000004</v>
+      </c>
+      <c r="C122" s="82"/>
+      <c r="D122" s="173"/>
+      <c r="E122" s="173"/>
+      <c r="F122" s="173"/>
+    </row>
+    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="77" t="s">
+        <v>158</v>
+      </c>
+      <c r="B123" s="93">
+        <v>40000</v>
+      </c>
+      <c r="C123" s="82"/>
+      <c r="D123" s="173"/>
+      <c r="E123" s="183"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="77" t="s">
+        <v>142</v>
+      </c>
+      <c r="B124" s="170"/>
+      <c r="C124" s="82"/>
+      <c r="E124" s="108"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="77"/>
+      <c r="B125" s="170"/>
+      <c r="C125" s="82"/>
+      <c r="E125" s="108"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="B102" s="143"/>
-      <c r="C102" s="139">
-        <f>SUM(C100:C101)</f>
-        <v>0</v>
-      </c>
-      <c r="E102" s="108"/>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E103" s="108"/>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E104" s="136"/>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A105" s="222" t="s">
-        <v>113</v>
-      </c>
-      <c r="B105" s="223"/>
-      <c r="C105" s="223"/>
-      <c r="D105" s="223"/>
-      <c r="E105" s="169" t="s">
-        <v>21</v>
-      </c>
-      <c r="F105" s="170" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="219"/>
-      <c r="B106" s="220"/>
-      <c r="C106" s="221"/>
-      <c r="D106" s="164"/>
-      <c r="E106" s="148"/>
-      <c r="F106" s="133"/>
-    </row>
-    <row r="107" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="216"/>
-      <c r="B107" s="217"/>
-      <c r="C107" s="171"/>
-      <c r="D107" s="112"/>
-      <c r="E107" s="148">
-        <f t="shared" ref="E107:E108" si="18">D107*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F107" s="133">
-        <f t="shared" ref="F107:F108" si="19">D107*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="216"/>
-      <c r="B108" s="217"/>
-      <c r="C108" s="171"/>
-      <c r="D108" s="112"/>
-      <c r="E108" s="148">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="F108" s="133">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="216"/>
-      <c r="B109" s="217"/>
-      <c r="C109" s="218"/>
-      <c r="D109" s="112"/>
-      <c r="E109" s="148">
-        <f>D109*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F109" s="133">
-        <f>D109*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A110" s="213" t="s">
-        <v>29</v>
-      </c>
-      <c r="B110" s="214"/>
-      <c r="C110" s="215"/>
-      <c r="D110" s="168">
-        <f>SUM(D106:D109)</f>
-        <v>0</v>
-      </c>
-      <c r="E110" s="168">
-        <f>SUM(E106:E109)</f>
-        <v>0</v>
-      </c>
-      <c r="F110" s="168">
-        <f>SUM(F106:F109)</f>
-        <v>0</v>
-      </c>
-      <c r="H110" s="108">
-        <f>E110+F110</f>
-        <v>0</v>
-      </c>
-      <c r="I110" s="149" t="str">
-        <f>IF(D110=H110, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E112" s="108"/>
-    </row>
-    <row r="113" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="102" t="s">
-        <v>104</v>
-      </c>
-      <c r="B113" s="103">
-        <f>D97</f>
-        <v>10825310.289999999</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="104" t="s">
-        <v>106</v>
-      </c>
-      <c r="B114" s="105">
-        <f>D97-D95</f>
-        <v>10825310.289999999</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D115" s="203"/>
-      <c r="E115" s="203"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A116" s="74" t="s">
-        <v>90</v>
-      </c>
-      <c r="B116" s="75"/>
-      <c r="C116" s="76"/>
-      <c r="D116" s="203"/>
-      <c r="E116" s="203"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A117" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="B117" s="11">
-        <v>-630321.16476135515</v>
-      </c>
-      <c r="C117" s="78"/>
-      <c r="D117" s="203"/>
-      <c r="E117" s="203"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" s="79" t="s">
-        <v>92</v>
-      </c>
-      <c r="B118" s="92">
-        <f>PRORRATEO!G52</f>
-        <v>6975889.7925080024</v>
-      </c>
-      <c r="C118" s="78" t="s">
-        <v>93</v>
-      </c>
-      <c r="D118" s="203"/>
-      <c r="E118" s="203"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" s="79" t="s">
-        <v>115</v>
-      </c>
-      <c r="B119" s="173">
-        <f>-B114</f>
-        <v>-10825310.289999999</v>
-      </c>
-      <c r="C119" s="76"/>
-      <c r="D119" s="203"/>
-      <c r="E119" s="203"/>
-      <c r="G119" s="112"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" s="79" t="s">
-        <v>114</v>
-      </c>
-      <c r="B120" s="173">
-        <f>-D110</f>
-        <v>0</v>
-      </c>
-      <c r="C120" s="76"/>
-      <c r="D120" s="203"/>
-      <c r="E120" s="203"/>
-      <c r="G120" s="124"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" s="79" t="s">
-        <v>105</v>
-      </c>
-      <c r="B121" s="173">
-        <f>-B128</f>
-        <v>-50000</v>
-      </c>
-      <c r="C121" s="80"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" s="79" t="s">
-        <v>120</v>
-      </c>
-      <c r="B122" s="93">
-        <f>-C102</f>
-        <v>0</v>
-      </c>
-      <c r="C122" s="80"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" s="79"/>
-      <c r="B123" s="75"/>
-      <c r="C123" s="80"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" s="77" t="s">
-        <v>94</v>
-      </c>
-      <c r="B124" s="81">
-        <f>SUM(B117:B123)</f>
-        <v>-4529741.6622533519</v>
-      </c>
-      <c r="C124" s="153"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" s="80"/>
-      <c r="C125" s="76"/>
-      <c r="D125" s="83"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C126" s="76"/>
-      <c r="D126" s="108"/>
-      <c r="E126" s="176"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" s="74" t="s">
-        <v>95</v>
-      </c>
-      <c r="B127" s="11">
-        <v>-365694.54000000004</v>
-      </c>
-      <c r="C127" s="82"/>
-      <c r="D127" s="176"/>
-      <c r="E127" s="176"/>
-      <c r="F127" s="176"/>
-    </row>
-    <row r="128" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="77" t="s">
-        <v>174</v>
-      </c>
-      <c r="B128" s="93">
-        <v>50000</v>
-      </c>
-      <c r="C128" s="82"/>
-      <c r="D128" s="176"/>
-      <c r="E128" s="189"/>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A129" s="77" t="s">
-        <v>150</v>
-      </c>
-      <c r="B129" s="173">
-        <v>-37000</v>
-      </c>
-      <c r="C129" s="82"/>
-      <c r="E129" s="108"/>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A130" s="77"/>
-      <c r="B130" s="173"/>
-      <c r="C130" s="82"/>
-      <c r="E130" s="108"/>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A131" s="100" t="s">
-        <v>29</v>
-      </c>
-      <c r="B131" s="101">
-        <f>SUM(B127:B130)</f>
-        <v>-352694.54000000004</v>
-      </c>
-      <c r="C131" s="82"/>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C132" s="83"/>
-      <c r="D132" s="176"/>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B133" s="80"/>
-      <c r="C133" s="76"/>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N135" s="12"/>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B138" s="202"/>
-      <c r="C138" s="202"/>
-      <c r="D138" s="202"/>
-      <c r="E138" s="202"/>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B139" s="202"/>
-      <c r="C139" s="202"/>
-      <c r="D139" s="202"/>
-      <c r="E139" s="202"/>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B140" s="202"/>
-      <c r="C140" s="202"/>
-      <c r="D140" s="202"/>
-      <c r="E140" s="202"/>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B141" s="202"/>
-      <c r="C141" s="202"/>
-      <c r="D141" s="202"/>
-      <c r="E141" s="202"/>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B142" s="202"/>
-      <c r="C142" s="202"/>
-      <c r="D142" s="202"/>
-      <c r="E142" s="202"/>
+      <c r="B126" s="101">
+        <f>SUM(B122:B125)</f>
+        <v>-312694.54000000004</v>
+      </c>
+      <c r="C126" s="82"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C127" s="83"/>
+      <c r="D127" s="173"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B128" s="80"/>
+      <c r="C128" s="76"/>
+    </row>
+    <row r="130" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N130" s="12"/>
+    </row>
+    <row r="133" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B133" s="200"/>
+      <c r="C133" s="200"/>
+      <c r="D133" s="200"/>
+      <c r="E133" s="200"/>
+    </row>
+    <row r="134" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B134" s="200"/>
+      <c r="C134" s="200"/>
+      <c r="D134" s="200"/>
+      <c r="E134" s="200"/>
+    </row>
+    <row r="135" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B135" s="200"/>
+      <c r="C135" s="200"/>
+      <c r="D135" s="200"/>
+      <c r="E135" s="200"/>
+    </row>
+    <row r="136" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B136" s="200"/>
+      <c r="C136" s="200"/>
+      <c r="D136" s="200"/>
+      <c r="E136" s="200"/>
+    </row>
+    <row r="137" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B137" s="200"/>
+      <c r="C137" s="200"/>
+      <c r="D137" s="200"/>
+      <c r="E137" s="200"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="B138:E142"/>
-    <mergeCell ref="D115:E120"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="B133:E137"/>
+    <mergeCell ref="D110:E115"/>
     <mergeCell ref="B14:D17"/>
-    <mergeCell ref="A110:C110"/>
-    <mergeCell ref="A109:C109"/>
-    <mergeCell ref="A106:C106"/>
-    <mergeCell ref="A105:D105"/>
+    <mergeCell ref="A105:C105"/>
+    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="A102:B102"/>
+    <mergeCell ref="A63:C63"/>
     <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A60:C60"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4272,26 +4100,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" customWidth="1"/>
     <col min="6" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="13.6640625" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" customWidth="1"/>
-    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4307,18 +4135,18 @@
       <c r="K1" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="L1" s="227">
-        <f>RESUMEN!D97</f>
-        <v>10825310.289999999</v>
-      </c>
-      <c r="M1" s="228"/>
-      <c r="N1" s="151"/>
+      <c r="L1" s="225">
+        <f>RESUMEN!D92</f>
+        <v>8226649.5599999996</v>
+      </c>
+      <c r="M1" s="226"/>
+      <c r="N1" s="148"/>
       <c r="O1" s="134">
         <f>L1*8.09%</f>
-        <v>875767.60246099997</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+        <v>665535.94940399996</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4333,17 +4161,17 @@
         <v>125</v>
       </c>
       <c r="L2" s="8"/>
-      <c r="M2" s="151">
+      <c r="M2" s="148">
         <f>7519700+7519700*10%</f>
         <v>8271670</v>
       </c>
-      <c r="N2" s="152"/>
+      <c r="N2" s="149"/>
       <c r="O2" s="134">
         <f>O1-K7-553-50-86-8</f>
-        <v>260400.94469200005</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+        <v>50169.291635000031</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="str">
         <f>RESUMEN!C5</f>
         <v>VTO: 15/09</v>
@@ -4362,13 +4190,13 @@
       </c>
       <c r="L3" s="8"/>
       <c r="M3" s="127">
-        <f>RESUMEN!D110</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="150"/>
+        <f>RESUMEN!D105</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="147"/>
       <c r="O3" s="73"/>
     </row>
-    <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -4391,67 +4219,67 @@
       </c>
       <c r="N4" s="123"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="224" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="222" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="238" t="s">
+      <c r="B5" s="236" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="224" t="s">
+      <c r="C5" s="222" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="236" t="s">
+      <c r="D5" s="234" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="224" t="s">
+      <c r="E5" s="222" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="224" t="s">
+      <c r="F5" s="222" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="224" t="s">
+      <c r="G5" s="222" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="231" t="s">
+      <c r="H5" s="229" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="236" t="s">
+      <c r="I5" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="229" t="s">
+      <c r="J5" s="227" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="229" t="s">
+      <c r="K5" s="227" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="234" t="s">
+      <c r="L5" s="232" t="s">
         <v>123</v>
       </c>
-      <c r="M5" s="229" t="s">
+      <c r="M5" s="227" t="s">
         <v>67</v>
       </c>
-      <c r="N5" s="229" t="s">
+      <c r="N5" s="227" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="225"/>
-      <c r="B6" s="239"/>
-      <c r="C6" s="225"/>
-      <c r="D6" s="240"/>
-      <c r="E6" s="225"/>
-      <c r="F6" s="225"/>
-      <c r="G6" s="225"/>
-      <c r="H6" s="232"/>
-      <c r="I6" s="237"/>
-      <c r="J6" s="230"/>
-      <c r="K6" s="233"/>
-      <c r="L6" s="235"/>
-      <c r="M6" s="233"/>
-      <c r="N6" s="230"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="223"/>
+      <c r="B6" s="237"/>
+      <c r="C6" s="223"/>
+      <c r="D6" s="238"/>
+      <c r="E6" s="223"/>
+      <c r="F6" s="223"/>
+      <c r="G6" s="223"/>
+      <c r="H6" s="230"/>
+      <c r="I6" s="235"/>
+      <c r="J6" s="228"/>
+      <c r="K6" s="231"/>
+      <c r="L6" s="233"/>
+      <c r="M6" s="231"/>
+      <c r="N6" s="228"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>33</v>
       </c>
@@ -4466,18 +4294,18 @@
         <v>8.09</v>
       </c>
       <c r="F7" s="88">
-        <v>412157.680108</v>
-      </c>
-      <c r="G7" s="193">
+        <v>614669.65776899992</v>
+      </c>
+      <c r="G7" s="196">
         <f>F7</f>
-        <v>412157.680108</v>
+        <v>614669.65776899992</v>
       </c>
       <c r="H7" s="130">
         <f>F7-G7</f>
         <v>0</v>
       </c>
       <c r="I7" s="106">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J7" s="88"/>
       <c r="K7" s="88">
@@ -4495,7 +4323,7 @@
         <v>651549.83723513992</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>35</v>
       </c>
@@ -4510,14 +4338,14 @@
         <v>2.21</v>
       </c>
       <c r="F8" s="88">
-        <v>173244.21501451588</v>
-      </c>
-      <c r="G8" s="193">
-        <v>175000</v>
+        <v>181048.12201451589</v>
+      </c>
+      <c r="G8" s="196">
+        <v>180000</v>
       </c>
       <c r="H8" s="130">
         <f t="shared" ref="H8:H51" si="0">F8-G8</f>
-        <v>-1755.7849854841188</v>
+        <v>1048.1220145158877</v>
       </c>
       <c r="I8" s="106">
         <v>11</v>
@@ -4530,20 +4358,20 @@
         <f>M$2*E8 /100</f>
         <v>182803.90700000001</v>
       </c>
-      <c r="L8" s="163">
+      <c r="L8" s="160">
         <f>J$3*E8%+J$4</f>
         <v>0</v>
       </c>
       <c r="M8" s="6">
         <f>K8+J8+H8+L8</f>
-        <v>181048.12201451589</v>
+        <v>183852.02901451589</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" ref="N8:N51" si="1">M8*6% + M8</f>
-        <v>191911.00933538683</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+        <v>194883.15075538686</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
@@ -4558,18 +4386,18 @@
         <v>4.21</v>
       </c>
       <c r="F9" s="88">
-        <v>326579.3682842633</v>
-      </c>
-      <c r="G9" s="194">
-        <f>366606-G34</f>
-        <v>325999.62</v>
+        <v>348817.05528426333</v>
+      </c>
+      <c r="G9" s="195">
+        <f>392904-G34</f>
+        <v>348236.98199999996</v>
       </c>
       <c r="H9" s="130">
         <f t="shared" si="0"/>
-        <v>579.7482842633035</v>
+        <v>580.07328426337335</v>
       </c>
       <c r="I9" s="106">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J9" s="88">
         <f t="shared" ref="J9:J51" si="2">M$4*E9%</f>
@@ -4579,20 +4407,20 @@
         <f t="shared" ref="K9:K51" si="3">M$2*E9 /100</f>
         <v>348237.30700000003</v>
       </c>
-      <c r="L9" s="163">
+      <c r="L9" s="160">
         <f t="shared" ref="L9:L50" si="4">J$3*E9%+J$4</f>
         <v>0</v>
       </c>
       <c r="M9" s="6">
         <f t="shared" ref="M9:M51" si="5">K9+J9+H9+L9</f>
-        <v>348817.05528426333</v>
+        <v>348817.3802842634</v>
       </c>
       <c r="N9" s="11">
         <f t="shared" si="1"/>
-        <v>369746.07860131911</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <v>369746.42310131923</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>38</v>
       </c>
@@ -4607,17 +4435,17 @@
         <v>2.84</v>
       </c>
       <c r="F10" s="88">
-        <v>257752.68620596873</v>
-      </c>
-      <c r="G10" s="193">
-        <v>213558</v>
+        <v>279110.11420596868</v>
+      </c>
+      <c r="G10" s="196">
+        <v>213555</v>
       </c>
       <c r="H10" s="130">
         <f t="shared" si="0"/>
-        <v>44194.686205968726</v>
+        <v>65555.114205968683</v>
       </c>
       <c r="I10" s="106">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J10" s="88">
         <f t="shared" si="2"/>
@@ -4627,20 +4455,20 @@
         <f t="shared" si="3"/>
         <v>234915.42799999996</v>
       </c>
-      <c r="L10" s="163">
+      <c r="L10" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M10" s="6">
         <f t="shared" si="5"/>
-        <v>279110.11420596868</v>
+        <v>300470.54220596864</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="1"/>
-        <v>295856.72105832677</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <v>318498.77473832679</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>38</v>
       </c>
@@ -4655,18 +4483,18 @@
         <v>3.43</v>
       </c>
       <c r="F11" s="88">
-        <v>269508.94160000002</v>
-      </c>
-      <c r="G11" s="193">
+        <v>283718.28100000002</v>
+      </c>
+      <c r="G11" s="196">
         <f>F11</f>
-        <v>269508.94160000002</v>
+        <v>283718.28100000002</v>
       </c>
       <c r="H11" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I11" s="106">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J11" s="88">
         <f t="shared" si="2"/>
@@ -4676,7 +4504,7 @@
         <f t="shared" si="3"/>
         <v>283718.28100000002</v>
       </c>
-      <c r="L11" s="163">
+      <c r="L11" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4690,7 +4518,7 @@
       </c>
       <c r="P11" s="108"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>41</v>
       </c>
@@ -4705,18 +4533,18 @@
         <v>2.84</v>
       </c>
       <c r="F12" s="88">
-        <v>223559.48</v>
-      </c>
-      <c r="G12" s="194">
+        <v>234915.42799999996</v>
+      </c>
+      <c r="G12" s="195">
         <f>F12</f>
-        <v>223559.48</v>
+        <v>234915.42799999996</v>
       </c>
       <c r="H12" s="130">
         <f>F12-G12</f>
         <v>0</v>
       </c>
       <c r="I12" s="106">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J12" s="88">
         <f t="shared" si="2"/>
@@ -4726,7 +4554,7 @@
         <f t="shared" si="3"/>
         <v>234915.42799999996</v>
       </c>
-      <c r="L12" s="163">
+      <c r="L12" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4739,7 +4567,7 @@
         <v>249010.35367999994</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>41</v>
       </c>
@@ -4754,18 +4582,18 @@
         <v>3.43</v>
       </c>
       <c r="F13" s="88">
-        <v>308384.31311924173</v>
-      </c>
-      <c r="G13" s="194">
-        <f>352750-G50</f>
-        <v>308383.77</v>
+        <v>283718.82411924173</v>
+      </c>
+      <c r="G13" s="195">
+        <f>332521-G50</f>
+        <v>283718.147</v>
       </c>
       <c r="H13" s="130">
         <f t="shared" si="0"/>
-        <v>0.54311924171634018</v>
+        <v>0.67711924173636362</v>
       </c>
       <c r="I13" s="106">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J13" s="88">
         <f t="shared" si="2"/>
@@ -4775,20 +4603,20 @@
         <f t="shared" si="3"/>
         <v>283718.28100000002</v>
       </c>
-      <c r="L13" s="163">
+      <c r="L13" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M13" s="6">
         <f t="shared" si="5"/>
-        <v>283718.82411924173</v>
+        <v>283718.95811924175</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="1"/>
-        <v>300741.95356639626</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+        <v>300742.09560639627</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>43</v>
       </c>
@@ -4803,18 +4631,17 @@
         <v>2.84</v>
       </c>
       <c r="F14" s="88">
-        <v>223150.98080000002</v>
-      </c>
-      <c r="G14" s="193">
-        <f>214000</f>
-        <v>214000</v>
+        <v>258710.39332799998</v>
+      </c>
+      <c r="G14" s="196">
+        <v>234915</v>
       </c>
       <c r="H14" s="130">
         <f t="shared" si="0"/>
-        <v>9150.9808000000194</v>
+        <v>23795.393327999976</v>
       </c>
       <c r="I14" s="106">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J14" s="88">
         <f t="shared" si="2"/>
@@ -4824,20 +4651,20 @@
         <f t="shared" si="3"/>
         <v>234915.42799999996</v>
       </c>
-      <c r="L14" s="163">
+      <c r="L14" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M14" s="6">
         <f t="shared" si="5"/>
-        <v>244066.40879999998</v>
+        <v>258710.82132799993</v>
       </c>
       <c r="N14" s="11">
         <f t="shared" si="1"/>
-        <v>258710.39332799998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+        <v>274233.47060767992</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>43</v>
       </c>
@@ -4846,24 +4673,24 @@
         <v>31</v>
       </c>
       <c r="D15" s="132" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E15" s="7">
         <v>3.43</v>
       </c>
       <c r="F15" s="88">
-        <v>257925.38604653394</v>
-      </c>
-      <c r="G15" s="194">
-        <f>295524-G35</f>
-        <v>257925.5</v>
+        <v>283718.16704653396</v>
+      </c>
+      <c r="G15" s="195">
+        <f>325076-G35</f>
+        <v>283717.65000000002</v>
       </c>
       <c r="H15" s="130">
         <f t="shared" si="0"/>
-        <v>-0.1139534660615027</v>
+        <v>0.51704653393244371</v>
       </c>
       <c r="I15" s="106">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J15" s="88">
         <f t="shared" si="2"/>
@@ -4873,20 +4700,20 @@
         <f t="shared" si="3"/>
         <v>283718.28100000002</v>
       </c>
-      <c r="L15" s="163">
+      <c r="L15" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M15" s="6">
         <f t="shared" si="5"/>
-        <v>283718.16704653396</v>
+        <v>283718.79804653395</v>
       </c>
       <c r="N15" s="11">
         <f t="shared" si="1"/>
-        <v>300741.25706932601</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+        <v>300741.92592932598</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
@@ -4901,15 +4728,15 @@
         <v>2.84</v>
       </c>
       <c r="F16" s="88">
-        <v>213560.22460066073</v>
+        <v>280282</v>
       </c>
       <c r="G16" s="195">
-        <f>250407-G49</f>
-        <v>213560.47</v>
+        <f>275546+45267-G49</f>
+        <v>280281.81699999998</v>
       </c>
       <c r="H16" s="130">
         <f t="shared" si="0"/>
-        <v>-0.24539933927007951</v>
+        <v>0.18300000001909211</v>
       </c>
       <c r="I16" s="106">
         <v>4</v>
@@ -4922,23 +4749,20 @@
         <f t="shared" si="3"/>
         <v>234915.42799999996</v>
       </c>
-      <c r="L16" s="163">
+      <c r="L16" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M16" s="6">
         <f t="shared" si="5"/>
-        <v>234915.18260066069</v>
+        <v>234915.61099999998</v>
       </c>
       <c r="N16" s="11">
         <f t="shared" si="1"/>
-        <v>249010.09355670033</v>
-      </c>
-      <c r="P16" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+        <v>249010.54765999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>46</v>
       </c>
@@ -4953,18 +4777,18 @@
         <v>3.43</v>
       </c>
       <c r="F17" s="88">
-        <v>257925.83371111474</v>
-      </c>
-      <c r="G17" s="193">
-        <f>332372-G47-G48</f>
-        <v>257926.97</v>
+        <v>293717.14471111476</v>
+      </c>
+      <c r="G17" s="196">
+        <f>375606+1-G47-G48</f>
+        <v>293717.467</v>
       </c>
       <c r="H17" s="130">
         <f t="shared" si="0"/>
-        <v>-1.1362888852600008</v>
+        <v>-0.32228888524696231</v>
       </c>
       <c r="I17" s="106">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J17" s="88">
         <f t="shared" si="2"/>
@@ -4974,19 +4798,20 @@
         <f t="shared" si="3"/>
         <v>283718.28100000002</v>
       </c>
-      <c r="L17" s="163">
-        <v>10000</v>
+      <c r="L17" s="247">
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="M17" s="6">
         <f t="shared" si="5"/>
-        <v>293717.14471111476</v>
+        <v>283717.95871111477</v>
       </c>
       <c r="N17" s="11">
         <f t="shared" si="1"/>
-        <v>311340.17339378165</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+        <v>300741.03623378166</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>48</v>
       </c>
@@ -5001,18 +4826,18 @@
         <v>2.84</v>
       </c>
       <c r="F18" s="88">
-        <v>223827.22398325134</v>
-      </c>
-      <c r="G18" s="193">
-        <f>270000-G51</f>
-        <v>227137.71</v>
+        <v>231604.94198325131</v>
+      </c>
+      <c r="G18" s="196">
+        <f>112000+160000+8000-G51</f>
+        <v>232851.481</v>
       </c>
       <c r="H18" s="130">
         <f t="shared" si="0"/>
-        <v>-3310.4860167486477</v>
+        <v>-1246.5390167486912</v>
       </c>
       <c r="I18" s="106">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J18" s="88">
         <f t="shared" si="2"/>
@@ -5022,20 +4847,20 @@
         <f t="shared" si="3"/>
         <v>234915.42799999996</v>
       </c>
-      <c r="L18" s="163">
+      <c r="L18" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M18" s="6">
         <f t="shared" si="5"/>
-        <v>231604.94198325131</v>
+        <v>233668.88898325127</v>
       </c>
       <c r="N18" s="11">
         <f t="shared" si="1"/>
-        <v>245501.23850224639</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+        <v>247689.02232224634</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>48</v>
       </c>
@@ -5050,18 +4875,18 @@
         <v>3.43</v>
       </c>
       <c r="F19" s="88">
-        <v>257926.19276516797</v>
-      </c>
-      <c r="G19" s="194">
-        <f>298532-G41</f>
-        <v>257925.62</v>
+        <v>283718.85376516799</v>
+      </c>
+      <c r="G19" s="195">
+        <f>328385-G41</f>
+        <v>283717.98199999996</v>
       </c>
       <c r="H19" s="130">
         <f t="shared" si="0"/>
-        <v>0.57276516797719523</v>
+        <v>0.87176516803447157</v>
       </c>
       <c r="I19" s="106">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19" s="88">
         <f t="shared" si="2"/>
@@ -5071,20 +4896,20 @@
         <f t="shared" si="3"/>
         <v>283718.28100000002</v>
       </c>
-      <c r="L19" s="163">
+      <c r="L19" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M19" s="6">
         <f t="shared" si="5"/>
-        <v>283718.85376516799</v>
+        <v>283719.15276516805</v>
       </c>
       <c r="N19" s="11">
         <f t="shared" si="1"/>
-        <v>300741.98499107809</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+        <v>300742.30193107814</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
@@ -5099,18 +4924,18 @@
         <v>2.84</v>
       </c>
       <c r="F20" s="88">
-        <v>224805.06990707474</v>
-      </c>
-      <c r="G20" s="193">
-        <f>250406-G38</f>
-        <v>213559.47</v>
+        <v>246161.02790707469</v>
+      </c>
+      <c r="G20" s="196">
+        <f>275446-G38</f>
+        <v>234914.81700000001</v>
       </c>
       <c r="H20" s="130">
         <f t="shared" si="0"/>
-        <v>11245.599907074735</v>
+        <v>11246.210907074681</v>
       </c>
       <c r="I20" s="106">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J20" s="88">
         <f t="shared" si="2"/>
@@ -5120,20 +4945,20 @@
         <f t="shared" si="3"/>
         <v>234915.42799999996</v>
       </c>
-      <c r="L20" s="163">
+      <c r="L20" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M20" s="6">
         <f t="shared" si="5"/>
-        <v>246161.02790707469</v>
+        <v>246161.63890707464</v>
       </c>
       <c r="N20" s="11">
         <f t="shared" si="1"/>
-        <v>260930.68958149917</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+        <v>260931.3372414991</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
@@ -5148,18 +4973,18 @@
         <v>3.43</v>
       </c>
       <c r="F21" s="88">
-        <v>257925.59509179581</v>
-      </c>
-      <c r="G21" s="193">
-        <f>298532-G45</f>
-        <v>257925.62</v>
+        <v>283718.25609179586</v>
+      </c>
+      <c r="G21" s="196">
+        <f>328385-G45</f>
+        <v>283717.98199999996</v>
       </c>
       <c r="H21" s="130">
         <f t="shared" si="0"/>
-        <v>-2.4908204184612259E-2</v>
+        <v>0.27409179590176791</v>
       </c>
       <c r="I21" s="106">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J21" s="88">
         <f t="shared" si="2"/>
@@ -5169,20 +4994,20 @@
         <f t="shared" si="3"/>
         <v>283718.28100000002</v>
       </c>
-      <c r="L21" s="163">
+      <c r="L21" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M21" s="6">
         <f t="shared" si="5"/>
-        <v>283718.25609179586</v>
+        <v>283718.55509179592</v>
       </c>
       <c r="N21" s="11">
         <f t="shared" si="1"/>
-        <v>300741.35145730362</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+        <v>300741.66839730367</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>54</v>
       </c>
@@ -5190,25 +5015,25 @@
       <c r="C22" s="7">
         <v>38</v>
       </c>
-      <c r="D22" s="165" t="s">
+      <c r="D22" s="162" t="s">
         <v>128</v>
       </c>
       <c r="E22" s="7">
         <v>2.84</v>
       </c>
       <c r="F22" s="88">
-        <v>223150.98080000002</v>
-      </c>
-      <c r="G22" s="193">
+        <v>254915.42799999996</v>
+      </c>
+      <c r="G22" s="196">
         <f>F22</f>
-        <v>223150.98080000002</v>
+        <v>254915.42799999996</v>
       </c>
       <c r="H22" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I22" s="106">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J22" s="88">
         <f t="shared" si="2"/>
@@ -5218,19 +5043,20 @@
         <f t="shared" si="3"/>
         <v>234915.42799999996</v>
       </c>
-      <c r="L22" s="163">
-        <v>20000</v>
+      <c r="L22" s="247">
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="M22" s="6">
         <f t="shared" si="5"/>
-        <v>254915.42799999996</v>
+        <v>234915.42799999996</v>
       </c>
       <c r="N22" s="11">
         <f t="shared" si="1"/>
-        <v>270210.35367999994</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+        <v>249010.35367999994</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>54</v>
       </c>
@@ -5245,18 +5071,18 @@
         <v>3.43</v>
       </c>
       <c r="F23" s="88">
-        <v>240712.43648409515</v>
-      </c>
-      <c r="G23" s="194">
-        <f>280000-G46</f>
-        <v>242401.5</v>
+        <v>309550.97053314082</v>
+      </c>
+      <c r="G23" s="195">
+        <f>334000-G46</f>
+        <v>290160.14899999998</v>
       </c>
       <c r="H23" s="130">
         <f t="shared" si="0"/>
-        <v>-1689.0635159048543</v>
+        <v>19390.821533140843</v>
       </c>
       <c r="I23" s="106">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="J23" s="88">
         <f t="shared" si="2"/>
@@ -5266,19 +5092,20 @@
         <f t="shared" si="3"/>
         <v>283718.28100000002</v>
       </c>
-      <c r="L23" s="163">
-        <v>10000</v>
+      <c r="L23" s="247">
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="M23" s="6">
         <f t="shared" si="5"/>
-        <v>292029.21748409513</v>
+        <v>303109.10253314086</v>
       </c>
       <c r="N23" s="11">
         <f t="shared" si="1"/>
-        <v>309550.97053314082</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+        <v>321295.6486851293</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>56</v>
       </c>
@@ -5293,18 +5120,18 @@
         <v>2.84</v>
       </c>
       <c r="F24" s="88">
-        <v>206644.78747107476</v>
-      </c>
-      <c r="G24" s="193">
-        <f>245000-G37</f>
-        <v>208153.47</v>
+        <v>233406.74547107471</v>
+      </c>
+      <c r="G24" s="196">
+        <f>266000+14000-G37</f>
+        <v>239468.81700000001</v>
       </c>
       <c r="H24" s="130">
         <f t="shared" si="0"/>
-        <v>-1508.6825289252447</v>
-      </c>
-      <c r="I24" s="177">
-        <v>7</v>
+        <v>-6062.0715289252985</v>
+      </c>
+      <c r="I24" s="174">
+        <v>6</v>
       </c>
       <c r="J24" s="88">
         <f t="shared" si="2"/>
@@ -5314,20 +5141,20 @@
         <f t="shared" si="3"/>
         <v>234915.42799999996</v>
       </c>
-      <c r="L24" s="163">
+      <c r="L24" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M24" s="6">
         <f t="shared" si="5"/>
-        <v>233406.74547107471</v>
+        <v>228853.35647107466</v>
       </c>
       <c r="N24" s="11">
         <f t="shared" si="1"/>
-        <v>247411.1501993392</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+        <v>242584.55785933914</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>56</v>
       </c>
@@ -5342,18 +5169,18 @@
         <v>3.43</v>
       </c>
       <c r="F25" s="88">
-        <v>267925.70999999996</v>
-      </c>
-      <c r="G25" s="193">
+        <v>322090.1091</v>
+      </c>
+      <c r="G25" s="196">
         <f>F25</f>
-        <v>267925.70999999996</v>
+        <v>322090.1091</v>
       </c>
       <c r="H25" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I25" s="106">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J25" s="88">
         <f t="shared" si="2"/>
@@ -5363,20 +5190,20 @@
         <f t="shared" si="3"/>
         <v>283718.28100000002</v>
       </c>
-      <c r="L25" s="163">
-        <f>10000+K25*0.1</f>
-        <v>38371.828099999999</v>
+      <c r="L25" s="247">
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="M25" s="6">
         <f t="shared" si="5"/>
-        <v>322090.1091</v>
+        <v>283718.28100000002</v>
       </c>
       <c r="N25" s="11">
         <f t="shared" si="1"/>
-        <v>341415.51564599999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+        <v>300741.37786000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>59</v>
       </c>
@@ -5391,18 +5218,18 @@
         <v>6</v>
       </c>
       <c r="F26" s="88">
-        <v>3958.5408160369843</v>
-      </c>
-      <c r="G26" s="194">
-        <f>119563+3959-G30-G31-G36</f>
-        <v>3958.7699999999895</v>
+        <v>496299.97081603704</v>
+      </c>
+      <c r="G26" s="195">
+        <f>676478.23-G30-G31-G36</f>
+        <v>544958.67700000003</v>
       </c>
       <c r="H26" s="131">
         <f t="shared" si="0"/>
-        <v>-0.22918396300519817</v>
+        <v>-48658.70618396299</v>
       </c>
       <c r="I26" s="106">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J26" s="88">
         <f t="shared" si="2"/>
@@ -5412,20 +5239,20 @@
         <f t="shared" si="3"/>
         <v>496300.2</v>
       </c>
-      <c r="L26" s="163">
+      <c r="L26" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M26" s="6">
         <f t="shared" si="5"/>
-        <v>496299.97081603704</v>
+        <v>447641.49381603702</v>
       </c>
       <c r="N26" s="11">
         <f t="shared" si="1"/>
-        <v>526077.96906499926</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+        <v>474499.98344499926</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>61</v>
       </c>
@@ -5440,15 +5267,15 @@
         <v>5.89</v>
       </c>
       <c r="F27" s="88">
-        <v>442910.4355352656</v>
-      </c>
-      <c r="G27" s="193">
-        <f>526378-G39-G40</f>
-        <v>439149.48000000004</v>
+        <v>490962.31853526551</v>
+      </c>
+      <c r="G27" s="196">
+        <f>586914-G39-G40</f>
+        <v>490962.62800000003</v>
       </c>
       <c r="H27" s="130">
         <f t="shared" si="0"/>
-        <v>3760.9555352655589</v>
+        <v>-0.30946473451331258</v>
       </c>
       <c r="I27" s="106">
         <v>14</v>
@@ -5461,20 +5288,20 @@
         <f t="shared" si="3"/>
         <v>487201.36299999995</v>
       </c>
-      <c r="L27" s="163">
+      <c r="L27" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M27" s="6">
         <f t="shared" si="5"/>
-        <v>490962.31853526551</v>
+        <v>487201.05353526544</v>
       </c>
       <c r="N27" s="11">
         <f t="shared" si="1"/>
-        <v>520420.05764738144</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+        <v>516433.11674738134</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>63</v>
       </c>
@@ -5489,18 +5316,18 @@
         <v>5.89</v>
       </c>
       <c r="F28" s="88">
-        <v>466343.09357654094</v>
-      </c>
-      <c r="G28" s="193">
-        <f>523000-G32-G33</f>
-        <v>443291.18</v>
+        <v>510253.2765765409</v>
+      </c>
+      <c r="G28" s="196">
+        <f>598000-G32-G33</f>
+        <v>510320.29799999995</v>
       </c>
       <c r="H28" s="130">
         <f t="shared" si="0"/>
-        <v>23051.913576540945</v>
+        <v>-67.02142345905304</v>
       </c>
       <c r="I28" s="106">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J28" s="88">
         <f t="shared" si="2"/>
@@ -5510,20 +5337,20 @@
         <f t="shared" si="3"/>
         <v>487201.36299999995</v>
       </c>
-      <c r="L28" s="163">
+      <c r="L28" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M28" s="6">
         <f t="shared" si="5"/>
-        <v>510253.2765765409</v>
+        <v>487134.3415765409</v>
       </c>
       <c r="N28" s="11">
         <f t="shared" si="1"/>
-        <v>540868.47317113332</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+        <v>516362.40207113337</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>65</v>
       </c>
@@ -5538,15 +5365,15 @@
         <v>5.89</v>
       </c>
       <c r="F29" s="88">
-        <v>771000.92145669996</v>
-      </c>
-      <c r="G29" s="194">
-        <f>564000-G42-G43-G44</f>
-        <v>442932.83</v>
+        <v>815269.4544566999</v>
+      </c>
+      <c r="G29" s="195">
+        <f>950000-G42-G43-G44</f>
+        <v>816826.1129999999</v>
       </c>
       <c r="H29" s="131">
         <f t="shared" si="0"/>
-        <v>328068.09145669994</v>
+        <v>-1556.6585433</v>
       </c>
       <c r="I29" s="106">
         <v>3</v>
@@ -5559,20 +5386,20 @@
         <f t="shared" si="3"/>
         <v>487201.36299999995</v>
       </c>
-      <c r="L29" s="163">
+      <c r="L29" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M29" s="6">
         <f t="shared" si="5"/>
-        <v>815269.4544566999</v>
+        <v>485644.70445669995</v>
       </c>
       <c r="N29" s="11">
         <f t="shared" si="1"/>
-        <v>864185.62172410195</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+        <v>514783.38672410196</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="125" t="s">
         <v>96</v>
       </c>
@@ -5587,11 +5414,11 @@
         <v>0.54</v>
       </c>
       <c r="F30" s="88">
-        <v>40606.380000000005</v>
-      </c>
-      <c r="G30" s="193">
+        <v>44667.018000000011</v>
+      </c>
+      <c r="G30" s="196">
         <f t="shared" ref="G30:G34" si="6">F30</f>
-        <v>40606.380000000005</v>
+        <v>44667.018000000011</v>
       </c>
       <c r="H30" s="130">
         <f t="shared" si="0"/>
@@ -5606,7 +5433,7 @@
         <f t="shared" si="3"/>
         <v>44667.018000000011</v>
       </c>
-      <c r="L30" s="163">
+      <c r="L30" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5619,7 +5446,7 @@
         <v>47347.03908000001</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="125" t="s">
         <v>96</v>
       </c>
@@ -5634,11 +5461,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F31" s="88">
-        <v>41358.350000000006</v>
-      </c>
-      <c r="G31" s="193">
+        <v>45494.184999999998</v>
+      </c>
+      <c r="G31" s="196">
         <f t="shared" si="6"/>
-        <v>41358.350000000006</v>
+        <v>45494.184999999998</v>
       </c>
       <c r="H31" s="130">
         <f t="shared" si="0"/>
@@ -5653,7 +5480,7 @@
         <f t="shared" si="3"/>
         <v>45494.184999999998</v>
       </c>
-      <c r="L31" s="163">
+      <c r="L31" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5666,7 +5493,7 @@
         <v>48223.8361</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="125" t="s">
         <v>96</v>
       </c>
@@ -5681,11 +5508,11 @@
         <v>0.45</v>
       </c>
       <c r="F32" s="88">
-        <v>33838.65</v>
-      </c>
-      <c r="G32" s="193">
+        <v>37222.514999999999</v>
+      </c>
+      <c r="G32" s="196">
         <f>F32</f>
-        <v>33838.65</v>
+        <v>37222.514999999999</v>
       </c>
       <c r="H32" s="130">
         <f t="shared" si="0"/>
@@ -5700,7 +5527,7 @@
         <f t="shared" si="3"/>
         <v>37222.514999999999</v>
       </c>
-      <c r="L32" s="163">
+      <c r="L32" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5713,7 +5540,7 @@
         <v>39455.865899999997</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="125" t="s">
         <v>96</v>
       </c>
@@ -5728,11 +5555,11 @@
         <v>0.61</v>
       </c>
       <c r="F33" s="88">
-        <v>45870.17</v>
-      </c>
-      <c r="G33" s="193">
+        <v>50457.187000000005</v>
+      </c>
+      <c r="G33" s="196">
         <f t="shared" si="6"/>
-        <v>45870.17</v>
+        <v>50457.187000000005</v>
       </c>
       <c r="H33" s="130">
         <f t="shared" si="0"/>
@@ -5747,7 +5574,7 @@
         <f t="shared" si="3"/>
         <v>50457.187000000005</v>
       </c>
-      <c r="L33" s="163">
+      <c r="L33" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5760,7 +5587,7 @@
         <v>53484.618220000004</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="125" t="s">
         <v>96</v>
       </c>
@@ -5775,11 +5602,11 @@
         <v>0.54</v>
       </c>
       <c r="F34" s="88">
-        <v>40606.380000000005</v>
-      </c>
-      <c r="G34" s="193">
+        <v>44667.018000000011</v>
+      </c>
+      <c r="G34" s="196">
         <f t="shared" si="6"/>
-        <v>40606.380000000005</v>
+        <v>44667.018000000011</v>
       </c>
       <c r="H34" s="130">
         <f t="shared" si="0"/>
@@ -5794,7 +5621,7 @@
         <f t="shared" si="3"/>
         <v>44667.018000000011</v>
       </c>
-      <c r="L34" s="163">
+      <c r="L34" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5807,7 +5634,7 @@
         <v>47347.03908000001</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="125" t="s">
         <v>96</v>
       </c>
@@ -5816,17 +5643,17 @@
         <v>6</v>
       </c>
       <c r="D35" s="132" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E35" s="7">
         <v>0.5</v>
       </c>
       <c r="F35" s="11">
-        <v>37598.5</v>
-      </c>
-      <c r="G35" s="194">
+        <v>41358.35</v>
+      </c>
+      <c r="G35" s="195">
         <f>F35</f>
-        <v>37598.5</v>
+        <v>41358.35</v>
       </c>
       <c r="H35" s="130">
         <f t="shared" si="0"/>
@@ -5841,7 +5668,7 @@
         <f t="shared" si="3"/>
         <v>41358.35</v>
       </c>
-      <c r="L35" s="163">
+      <c r="L35" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5854,7 +5681,7 @@
         <v>43839.850999999995</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="125" t="s">
         <v>96</v>
       </c>
@@ -5869,11 +5696,11 @@
         <v>0.5</v>
       </c>
       <c r="F36" s="88">
-        <v>37598.5</v>
-      </c>
-      <c r="G36" s="193">
+        <v>41358.35</v>
+      </c>
+      <c r="G36" s="196">
         <f t="shared" ref="G36:G41" si="7">F36</f>
-        <v>37598.5</v>
+        <v>41358.35</v>
       </c>
       <c r="H36" s="130">
         <f t="shared" si="0"/>
@@ -5888,7 +5715,7 @@
         <f t="shared" si="3"/>
         <v>41358.35</v>
       </c>
-      <c r="L36" s="163">
+      <c r="L36" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5901,7 +5728,7 @@
         <v>43839.850999999995</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="125" t="s">
         <v>96</v>
       </c>
@@ -5916,11 +5743,11 @@
         <v>0.49</v>
       </c>
       <c r="F37" s="88">
-        <v>36846.53</v>
-      </c>
-      <c r="G37" s="193">
+        <v>40531.182999999997</v>
+      </c>
+      <c r="G37" s="196">
         <f t="shared" si="7"/>
-        <v>36846.53</v>
+        <v>40531.182999999997</v>
       </c>
       <c r="H37" s="130">
         <f t="shared" si="0"/>
@@ -5935,7 +5762,7 @@
         <f t="shared" si="3"/>
         <v>40531.182999999997</v>
       </c>
-      <c r="L37" s="163">
+      <c r="L37" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5948,7 +5775,7 @@
         <v>42963.053979999997</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="125" t="s">
         <v>96</v>
       </c>
@@ -5963,11 +5790,11 @@
         <v>0.49</v>
       </c>
       <c r="F38" s="88">
-        <v>36846.53</v>
-      </c>
-      <c r="G38" s="193">
+        <v>40531.182999999997</v>
+      </c>
+      <c r="G38" s="196">
         <f t="shared" si="7"/>
-        <v>36846.53</v>
+        <v>40531.182999999997</v>
       </c>
       <c r="H38" s="130">
         <f t="shared" si="0"/>
@@ -5982,7 +5809,7 @@
         <f t="shared" si="3"/>
         <v>40531.182999999997</v>
       </c>
-      <c r="L38" s="163">
+      <c r="L38" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5995,7 +5822,7 @@
         <v>42963.053979999997</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="125" t="s">
         <v>96</v>
       </c>
@@ -6010,11 +5837,11 @@
         <v>0.59</v>
       </c>
       <c r="F39" s="88">
-        <v>44366.23</v>
-      </c>
-      <c r="G39" s="193">
+        <v>48802.852999999996</v>
+      </c>
+      <c r="G39" s="196">
         <f t="shared" si="7"/>
-        <v>44366.23</v>
+        <v>48802.852999999996</v>
       </c>
       <c r="H39" s="130">
         <f t="shared" si="0"/>
@@ -6029,7 +5856,7 @@
         <f t="shared" si="3"/>
         <v>48802.852999999996</v>
       </c>
-      <c r="L39" s="163">
+      <c r="L39" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6042,7 +5869,7 @@
         <v>51731.024179999993</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="125" t="s">
         <v>96</v>
       </c>
@@ -6057,11 +5884,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F40" s="88">
-        <v>42862.29</v>
-      </c>
-      <c r="G40" s="193">
+        <v>47148.518999999993</v>
+      </c>
+      <c r="G40" s="196">
         <f t="shared" si="7"/>
-        <v>42862.29</v>
+        <v>47148.518999999993</v>
       </c>
       <c r="H40" s="130">
         <f t="shared" si="0"/>
@@ -6076,7 +5903,7 @@
         <f t="shared" si="3"/>
         <v>47148.518999999993</v>
       </c>
-      <c r="L40" s="163">
+      <c r="L40" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6089,7 +5916,7 @@
         <v>49977.430139999989</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="125" t="s">
         <v>96</v>
       </c>
@@ -6104,11 +5931,11 @@
         <v>0.54</v>
       </c>
       <c r="F41" s="88">
-        <v>40606.380000000005</v>
-      </c>
-      <c r="G41" s="193">
+        <v>44667.018000000011</v>
+      </c>
+      <c r="G41" s="196">
         <f t="shared" si="7"/>
-        <v>40606.380000000005</v>
+        <v>44667.018000000011</v>
       </c>
       <c r="H41" s="130">
         <f t="shared" si="0"/>
@@ -6123,7 +5950,7 @@
         <f t="shared" si="3"/>
         <v>44667.018000000011</v>
       </c>
-      <c r="L41" s="163">
+      <c r="L41" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6136,7 +5963,7 @@
         <v>47347.03908000001</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="125" t="s">
         <v>96</v>
       </c>
@@ -6151,11 +5978,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F42" s="88">
-        <v>41358.350000000006</v>
-      </c>
-      <c r="G42" s="193">
+        <v>45494.184999999998</v>
+      </c>
+      <c r="G42" s="196">
         <f>F42</f>
-        <v>41358.350000000006</v>
+        <v>45494.184999999998</v>
       </c>
       <c r="H42" s="130">
         <f t="shared" si="0"/>
@@ -6170,7 +5997,7 @@
         <f t="shared" si="3"/>
         <v>45494.184999999998</v>
       </c>
-      <c r="L42" s="163">
+      <c r="L42" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6183,7 +6010,7 @@
         <v>48223.8361</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="125" t="s">
         <v>96</v>
       </c>
@@ -6198,11 +6025,11 @@
         <v>0.45</v>
       </c>
       <c r="F43" s="88">
-        <v>33838.65</v>
-      </c>
-      <c r="G43" s="193">
+        <v>37222.514999999999</v>
+      </c>
+      <c r="G43" s="196">
         <f t="shared" ref="G43:G44" si="8">F43</f>
-        <v>33838.65</v>
+        <v>37222.514999999999</v>
       </c>
       <c r="H43" s="130">
         <f t="shared" si="0"/>
@@ -6217,7 +6044,7 @@
         <f t="shared" si="3"/>
         <v>37222.514999999999</v>
       </c>
-      <c r="L43" s="163">
+      <c r="L43" s="247">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6231,10 +6058,10 @@
       </c>
       <c r="P43" s="108">
         <f>L1-K52</f>
-        <v>2608148.735231</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+        <v>9488.005231000483</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="125" t="s">
         <v>96</v>
       </c>
@@ -6249,11 +6076,11 @@
         <v>0.61</v>
       </c>
       <c r="F44" s="88">
-        <v>45870.17</v>
-      </c>
-      <c r="G44" s="193">
+        <v>50457.187000000005</v>
+      </c>
+      <c r="G44" s="196">
         <f t="shared" si="8"/>
-        <v>45870.17</v>
+        <v>50457.187000000005</v>
       </c>
       <c r="H44" s="130">
         <f t="shared" si="0"/>
@@ -6268,7 +6095,7 @@
         <f t="shared" si="3"/>
         <v>50457.187000000005</v>
       </c>
-      <c r="L44" s="163">
+      <c r="L44" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6281,7 +6108,7 @@
         <v>53484.618220000004</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="125" t="s">
         <v>96</v>
       </c>
@@ -6296,11 +6123,11 @@
         <v>0.54</v>
       </c>
       <c r="F45" s="88">
-        <v>40606.380000000005</v>
-      </c>
-      <c r="G45" s="193">
+        <v>44667.018000000011</v>
+      </c>
+      <c r="G45" s="196">
         <f t="shared" ref="G45:G51" si="9">F45</f>
-        <v>40606.380000000005</v>
+        <v>44667.018000000011</v>
       </c>
       <c r="H45" s="130">
         <f t="shared" si="0"/>
@@ -6315,7 +6142,7 @@
         <f t="shared" si="3"/>
         <v>44667.018000000011</v>
       </c>
-      <c r="L45" s="163">
+      <c r="L45" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6328,7 +6155,7 @@
         <v>47347.03908000001</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="125" t="s">
         <v>96</v>
       </c>
@@ -6343,11 +6170,11 @@
         <v>0.5</v>
       </c>
       <c r="F46" s="88">
-        <v>37598.5</v>
-      </c>
-      <c r="G46" s="193">
+        <v>43839.850999999995</v>
+      </c>
+      <c r="G46" s="196">
         <f>F46</f>
-        <v>37598.5</v>
+        <v>43839.850999999995</v>
       </c>
       <c r="H46" s="130">
         <f t="shared" si="0"/>
@@ -6362,7 +6189,7 @@
         <f t="shared" si="3"/>
         <v>41358.35</v>
       </c>
-      <c r="L46" s="163">
+      <c r="L46" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6378,7 +6205,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="125" t="s">
         <v>96</v>
       </c>
@@ -6393,11 +6220,11 @@
         <v>0.5</v>
       </c>
       <c r="F47" s="88">
-        <v>37598.5</v>
-      </c>
-      <c r="G47" s="193">
+        <v>41358.35</v>
+      </c>
+      <c r="G47" s="196">
         <f t="shared" si="9"/>
-        <v>37598.5</v>
+        <v>41358.35</v>
       </c>
       <c r="H47" s="130">
         <f t="shared" si="0"/>
@@ -6412,7 +6239,7 @@
         <f t="shared" si="3"/>
         <v>41358.35</v>
       </c>
-      <c r="L47" s="163">
+      <c r="L47" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6430,7 +6257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="125" t="s">
         <v>96</v>
       </c>
@@ -6445,11 +6272,11 @@
         <v>0.49</v>
       </c>
       <c r="F48" s="88">
-        <v>36846.53</v>
-      </c>
-      <c r="G48" s="193">
+        <v>40531.182999999997</v>
+      </c>
+      <c r="G48" s="196">
         <f t="shared" si="9"/>
-        <v>36846.53</v>
+        <v>40531.182999999997</v>
       </c>
       <c r="H48" s="130">
         <f t="shared" si="0"/>
@@ -6464,7 +6291,7 @@
         <f t="shared" si="3"/>
         <v>40531.182999999997</v>
       </c>
-      <c r="L48" s="163">
+      <c r="L48" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6477,7 +6304,7 @@
         <v>42963.053979999997</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="125" t="s">
         <v>96</v>
       </c>
@@ -6493,11 +6320,11 @@
         <v>0.49</v>
       </c>
       <c r="F49" s="88">
-        <v>36846.53</v>
-      </c>
-      <c r="G49" s="193">
+        <v>40531.182999999997</v>
+      </c>
+      <c r="G49" s="196">
         <f>F49</f>
-        <v>36846.53</v>
+        <v>40531.182999999997</v>
       </c>
       <c r="H49" s="130">
         <f t="shared" si="0"/>
@@ -6512,7 +6339,7 @@
         <f t="shared" si="3"/>
         <v>40531.182999999997</v>
       </c>
-      <c r="L49" s="163">
+      <c r="L49" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6525,7 +6352,7 @@
         <v>42963.053979999997</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="125" t="s">
         <v>96</v>
       </c>
@@ -6540,11 +6367,11 @@
         <v>0.59</v>
       </c>
       <c r="F50" s="88">
-        <v>44366.23</v>
-      </c>
-      <c r="G50" s="194">
+        <v>48802.852999999996</v>
+      </c>
+      <c r="G50" s="195">
         <f>F50</f>
-        <v>44366.23</v>
+        <v>48802.852999999996</v>
       </c>
       <c r="H50" s="130">
         <f t="shared" si="0"/>
@@ -6559,7 +6386,7 @@
         <f t="shared" si="3"/>
         <v>48802.852999999996</v>
       </c>
-      <c r="L50" s="163">
+      <c r="L50" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6572,7 +6399,7 @@
         <v>51731.024179999993</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="125" t="s">
         <v>96</v>
       </c>
@@ -6587,11 +6414,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F51" s="88">
-        <v>42862.29</v>
-      </c>
-      <c r="G51" s="193">
+        <v>47148.518999999993</v>
+      </c>
+      <c r="G51" s="196">
         <f t="shared" si="9"/>
-        <v>42862.29</v>
+        <v>47148.518999999993</v>
       </c>
       <c r="H51" s="130">
         <f t="shared" si="0"/>
@@ -6606,7 +6433,7 @@
         <f t="shared" si="3"/>
         <v>47148.518999999993</v>
       </c>
-      <c r="L51" s="163">
+      <c r="L51" s="160">
         <f t="shared" ref="L51" si="10">J$3*E51%+J$4</f>
         <v>0</v>
       </c>
@@ -6619,7 +6446,7 @@
         <v>49977.430139999989</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="89"/>
       <c r="B52" s="89"/>
       <c r="C52" s="89"/>
@@ -6630,11 +6457,11 @@
       </c>
       <c r="F52" s="90">
         <f>SUM(F7:F51)</f>
-        <v>7387677.1173773035</v>
+        <v>8787334.7637146879</v>
       </c>
       <c r="G52" s="90">
         <f>SUM(G7:G51)</f>
-        <v>6975889.7925080024</v>
+        <v>8723308.1338689979</v>
       </c>
       <c r="H52" s="89"/>
       <c r="I52" s="89"/>
@@ -6646,167 +6473,167 @@
         <f>SUM(K7:K51)</f>
         <v>8217161.5547689991</v>
       </c>
-      <c r="L52" s="172">
+      <c r="L52" s="169">
         <f>SUM(L7:L51)</f>
-        <v>78371.828099999999</v>
+        <v>0</v>
       </c>
       <c r="M52" s="91">
         <f>SUM(M7:M51)</f>
-        <v>8707320.7077383008</v>
+        <v>8281188.1846146872</v>
       </c>
       <c r="N52" s="90">
         <f>SUM(N7:N51)</f>
-        <v>9229759.950202601</v>
+        <v>8778059.4756915644</v>
       </c>
       <c r="P52" s="134"/>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K53" s="137">
         <f>K52-L1</f>
-        <v>-2608148.735231</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="226"/>
-      <c r="D54" s="226"/>
-      <c r="E54" s="226"/>
-      <c r="F54" s="226"/>
-      <c r="G54" s="226"/>
-      <c r="H54" s="226"/>
-      <c r="I54" s="226"/>
-      <c r="J54" s="226"/>
-      <c r="K54" s="226"/>
-      <c r="L54" s="226"/>
-      <c r="M54" s="226"/>
-      <c r="N54" s="226"/>
-    </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="226"/>
-      <c r="D55" s="226"/>
-      <c r="E55" s="226"/>
-      <c r="F55" s="226"/>
-      <c r="G55" s="226"/>
-      <c r="H55" s="226"/>
-      <c r="I55" s="226"/>
-      <c r="J55" s="226"/>
-      <c r="K55" s="226"/>
-      <c r="L55" s="226"/>
-      <c r="M55" s="226"/>
-      <c r="N55" s="226"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C56" s="166"/>
-      <c r="D56" s="166"/>
-      <c r="E56" s="166"/>
-      <c r="F56" s="166"/>
-      <c r="G56" s="166"/>
-      <c r="H56" s="166"/>
-      <c r="I56" s="166"/>
-      <c r="J56" s="166"/>
-      <c r="K56" s="166"/>
-      <c r="L56" s="166"/>
-      <c r="M56" s="166"/>
-      <c r="N56" s="166"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C57" s="226" t="s">
+        <v>-9488.005231000483</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="224"/>
+      <c r="D54" s="224"/>
+      <c r="E54" s="224"/>
+      <c r="F54" s="224"/>
+      <c r="G54" s="224"/>
+      <c r="H54" s="224"/>
+      <c r="I54" s="224"/>
+      <c r="J54" s="224"/>
+      <c r="K54" s="224"/>
+      <c r="L54" s="224"/>
+      <c r="M54" s="224"/>
+      <c r="N54" s="224"/>
+    </row>
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="224"/>
+      <c r="D55" s="224"/>
+      <c r="E55" s="224"/>
+      <c r="F55" s="224"/>
+      <c r="G55" s="224"/>
+      <c r="H55" s="224"/>
+      <c r="I55" s="224"/>
+      <c r="J55" s="224"/>
+      <c r="K55" s="224"/>
+      <c r="L55" s="224"/>
+      <c r="M55" s="224"/>
+      <c r="N55" s="224"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C56" s="163"/>
+      <c r="D56" s="163"/>
+      <c r="E56" s="163"/>
+      <c r="F56" s="163"/>
+      <c r="G56" s="163"/>
+      <c r="H56" s="163"/>
+      <c r="I56" s="163"/>
+      <c r="J56" s="163"/>
+      <c r="K56" s="163"/>
+      <c r="L56" s="163"/>
+      <c r="M56" s="163"/>
+      <c r="N56" s="163"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C57" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="D57" s="226"/>
-      <c r="E57" s="226"/>
-      <c r="F57" s="226"/>
-      <c r="G57" s="226"/>
-      <c r="H57" s="226"/>
-      <c r="I57" s="226"/>
-      <c r="J57" s="226"/>
-      <c r="K57" s="226"/>
-      <c r="L57" s="226"/>
-      <c r="M57" s="226"/>
-      <c r="N57" s="226"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C58" s="226"/>
-      <c r="D58" s="226"/>
-      <c r="E58" s="226"/>
-      <c r="F58" s="226"/>
-      <c r="G58" s="226"/>
-      <c r="H58" s="226"/>
-      <c r="I58" s="226"/>
-      <c r="J58" s="226"/>
-      <c r="K58" s="226"/>
-      <c r="L58" s="226"/>
-      <c r="M58" s="226"/>
-      <c r="N58" s="226"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C59" s="226"/>
-      <c r="D59" s="226"/>
-      <c r="E59" s="226"/>
-      <c r="F59" s="226"/>
-      <c r="G59" s="226"/>
-      <c r="H59" s="226"/>
-      <c r="I59" s="226"/>
-      <c r="J59" s="226"/>
-      <c r="K59" s="226"/>
-      <c r="L59" s="226"/>
-      <c r="M59" s="226"/>
-      <c r="N59" s="226"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C60" s="226"/>
-      <c r="D60" s="226"/>
-      <c r="E60" s="226"/>
-      <c r="F60" s="226"/>
-      <c r="G60" s="226"/>
-      <c r="H60" s="226"/>
-      <c r="I60" s="226"/>
-      <c r="J60" s="226"/>
-      <c r="K60" s="226"/>
-      <c r="L60" s="226"/>
-      <c r="M60" s="226"/>
-      <c r="N60" s="226"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C61" s="226"/>
-      <c r="D61" s="226"/>
-      <c r="E61" s="226"/>
-      <c r="F61" s="226"/>
-      <c r="G61" s="226"/>
-      <c r="H61" s="226"/>
-      <c r="I61" s="226"/>
-      <c r="J61" s="226"/>
-      <c r="K61" s="226"/>
-      <c r="L61" s="226"/>
-      <c r="M61" s="226"/>
-      <c r="N61" s="226"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C62" s="226"/>
-      <c r="D62" s="226"/>
-      <c r="E62" s="226"/>
-      <c r="F62" s="226"/>
-      <c r="G62" s="226"/>
-      <c r="H62" s="226"/>
-      <c r="I62" s="226"/>
-      <c r="J62" s="226"/>
-      <c r="K62" s="226"/>
-      <c r="L62" s="226"/>
-      <c r="M62" s="226"/>
-      <c r="N62" s="226"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C63" s="226"/>
-      <c r="D63" s="226"/>
-      <c r="E63" s="226"/>
-      <c r="F63" s="226"/>
-      <c r="G63" s="226"/>
-      <c r="H63" s="226"/>
-      <c r="I63" s="226"/>
-      <c r="J63" s="226"/>
-      <c r="K63" s="226"/>
-      <c r="L63" s="226"/>
-      <c r="M63" s="226"/>
-      <c r="N63" s="226"/>
+      <c r="D57" s="224"/>
+      <c r="E57" s="224"/>
+      <c r="F57" s="224"/>
+      <c r="G57" s="224"/>
+      <c r="H57" s="224"/>
+      <c r="I57" s="224"/>
+      <c r="J57" s="224"/>
+      <c r="K57" s="224"/>
+      <c r="L57" s="224"/>
+      <c r="M57" s="224"/>
+      <c r="N57" s="224"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C58" s="224"/>
+      <c r="D58" s="224"/>
+      <c r="E58" s="224"/>
+      <c r="F58" s="224"/>
+      <c r="G58" s="224"/>
+      <c r="H58" s="224"/>
+      <c r="I58" s="224"/>
+      <c r="J58" s="224"/>
+      <c r="K58" s="224"/>
+      <c r="L58" s="224"/>
+      <c r="M58" s="224"/>
+      <c r="N58" s="224"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C59" s="224"/>
+      <c r="D59" s="224"/>
+      <c r="E59" s="224"/>
+      <c r="F59" s="224"/>
+      <c r="G59" s="224"/>
+      <c r="H59" s="224"/>
+      <c r="I59" s="224"/>
+      <c r="J59" s="224"/>
+      <c r="K59" s="224"/>
+      <c r="L59" s="224"/>
+      <c r="M59" s="224"/>
+      <c r="N59" s="224"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C60" s="224"/>
+      <c r="D60" s="224"/>
+      <c r="E60" s="224"/>
+      <c r="F60" s="224"/>
+      <c r="G60" s="224"/>
+      <c r="H60" s="224"/>
+      <c r="I60" s="224"/>
+      <c r="J60" s="224"/>
+      <c r="K60" s="224"/>
+      <c r="L60" s="224"/>
+      <c r="M60" s="224"/>
+      <c r="N60" s="224"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C61" s="224"/>
+      <c r="D61" s="224"/>
+      <c r="E61" s="224"/>
+      <c r="F61" s="224"/>
+      <c r="G61" s="224"/>
+      <c r="H61" s="224"/>
+      <c r="I61" s="224"/>
+      <c r="J61" s="224"/>
+      <c r="K61" s="224"/>
+      <c r="L61" s="224"/>
+      <c r="M61" s="224"/>
+      <c r="N61" s="224"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C62" s="224"/>
+      <c r="D62" s="224"/>
+      <c r="E62" s="224"/>
+      <c r="F62" s="224"/>
+      <c r="G62" s="224"/>
+      <c r="H62" s="224"/>
+      <c r="I62" s="224"/>
+      <c r="J62" s="224"/>
+      <c r="K62" s="224"/>
+      <c r="L62" s="224"/>
+      <c r="M62" s="224"/>
+      <c r="N62" s="224"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C63" s="224"/>
+      <c r="D63" s="224"/>
+      <c r="E63" s="224"/>
+      <c r="F63" s="224"/>
+      <c r="G63" s="224"/>
+      <c r="H63" s="224"/>
+      <c r="I63" s="224"/>
+      <c r="J63" s="224"/>
+      <c r="K63" s="224"/>
+      <c r="L63" s="224"/>
+      <c r="M63" s="224"/>
+      <c r="N63" s="224"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -6836,88 +6663,88 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{596D2FF5-218B-41A1-9BCB-F43114942886}">
   <dimension ref="C4:H25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="14.88671875" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C4" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D5" s="192">
+        <v>146</v>
+      </c>
+      <c r="D5" s="186">
         <v>-447223.45918396302</v>
       </c>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D6" s="192">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+      <c r="D6" s="186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D7" s="192">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+      <c r="D7" s="186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>163</v>
-      </c>
-      <c r="D8" s="192">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+      <c r="D8" s="186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C10" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>160</v>
-      </c>
-      <c r="D11" s="192">
+        <v>146</v>
+      </c>
+      <c r="D11" s="186">
         <v>451182</v>
       </c>
     </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D12" s="192">
+        <v>147</v>
+      </c>
+      <c r="D12" s="186">
         <v>40606.380000000005</v>
       </c>
     </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>162</v>
-      </c>
-      <c r="D13" s="192">
+        <v>148</v>
+      </c>
+      <c r="D13" s="186">
         <v>41358.350000000006</v>
       </c>
     </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>163</v>
-      </c>
-      <c r="D14" s="192">
+        <v>149</v>
+      </c>
+      <c r="D14" s="186">
         <v>37598.5</v>
       </c>
     </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C16" s="3" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6925,67 +6752,67 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>160</v>
-      </c>
-      <c r="D17" s="192">
+        <v>146</v>
+      </c>
+      <c r="D17" s="186">
         <f>D11+D5</f>
         <v>3958.5408160369843</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
-        <v>161</v>
-      </c>
-      <c r="D18" s="192">
+        <v>147</v>
+      </c>
+      <c r="D18" s="186">
         <v>40606.380000000005</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>162</v>
-      </c>
-      <c r="D19" s="192">
+        <v>148</v>
+      </c>
+      <c r="D19" s="186">
         <v>41358.350000000006</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>163</v>
-      </c>
-      <c r="D20" s="192">
+        <v>149</v>
+      </c>
+      <c r="D20" s="186">
         <v>37598.5</v>
       </c>
     </row>
-    <row r="21" spans="3:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
-        <v>167</v>
-      </c>
-      <c r="D21" s="192">
+        <v>153</v>
+      </c>
+      <c r="D21" s="186">
         <v>-25000</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C22" s="241" t="s">
-        <v>166</v>
-      </c>
-      <c r="D22" s="244">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C22" s="239" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" s="242">
         <f>SUM(D17:D21)</f>
         <v>98521.770816036995</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C23" s="242"/>
-      <c r="D23" s="245"/>
-    </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C24" s="242"/>
-      <c r="D24" s="245"/>
-    </row>
-    <row r="25" spans="3:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C25" s="243"/>
-      <c r="D25" s="246"/>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C23" s="240"/>
+      <c r="D23" s="243"/>
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C24" s="240"/>
+      <c r="D24" s="243"/>
+    </row>
+    <row r="25" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="241"/>
+      <c r="D25" s="244"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7000,16 +6827,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="48"/>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
@@ -7033,7 +6860,7 @@
       </c>
       <c r="O1" s="52"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="49"/>
       <c r="B2" s="51"/>
       <c r="C2" s="51"/>
@@ -7052,7 +6879,7 @@
       <c r="N2" s="49"/>
       <c r="O2" s="49"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="49"/>
       <c r="B3" s="51"/>
       <c r="C3" s="51"/>
@@ -7075,7 +6902,7 @@
       </c>
       <c r="O3" s="54"/>
     </row>
-    <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
@@ -7096,11 +6923,11 @@
       <c r="N4" s="49"/>
       <c r="O4" s="49"/>
     </row>
-    <row r="5" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="247" t="s">
+    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="245" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="247" t="s">
+      <c r="B5" s="245" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="55" t="s">
@@ -7112,7 +6939,7 @@
       <c r="E5" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="247" t="s">
+      <c r="F5" s="245" t="s">
         <v>75</v>
       </c>
       <c r="G5" s="37" t="s">
@@ -7134,16 +6961,16 @@
         <v>29</v>
       </c>
       <c r="M5" s="41"/>
-      <c r="N5" s="247" t="s">
+      <c r="N5" s="245" t="s">
         <v>78</v>
       </c>
-      <c r="O5" s="247" t="s">
+      <c r="O5" s="245" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="248"/>
-      <c r="B6" s="248"/>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="246"/>
+      <c r="B6" s="246"/>
       <c r="C6" s="56" t="s">
         <v>80</v>
       </c>
@@ -7153,7 +6980,7 @@
       <c r="E6" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="248"/>
+      <c r="F6" s="246"/>
       <c r="G6" s="44" t="s">
         <v>81</v>
       </c>
@@ -7173,10 +7000,10 @@
         <v>84</v>
       </c>
       <c r="M6" s="47"/>
-      <c r="N6" s="248"/>
-      <c r="O6" s="248"/>
-    </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N6" s="246"/>
+      <c r="O6" s="246"/>
+    </row>
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
         <v>1</v>
       </c>
@@ -7222,7 +7049,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <v>2</v>
       </c>
@@ -7268,7 +7095,7 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
         <v>3</v>
       </c>
@@ -7314,7 +7141,7 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
         <v>4</v>
       </c>
@@ -7360,7 +7187,7 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15">
         <v>5</v>
       </c>
@@ -7406,7 +7233,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>6</v>
       </c>
@@ -7452,7 +7279,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15">
         <v>7</v>
       </c>
@@ -7498,7 +7325,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15">
         <v>8</v>
       </c>
@@ -7544,7 +7371,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15">
         <v>9</v>
       </c>
@@ -7590,7 +7417,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <v>10</v>
       </c>
@@ -7636,7 +7463,7 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15">
         <v>11</v>
       </c>
@@ -7682,7 +7509,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15">
         <v>12</v>
       </c>
@@ -7728,7 +7555,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
         <v>13</v>
       </c>
@@ -7774,7 +7601,7 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15">
         <v>14</v>
       </c>
@@ -7820,7 +7647,7 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="15">
         <v>15</v>
       </c>
@@ -7866,7 +7693,7 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15">
         <v>16</v>
       </c>
@@ -7912,7 +7739,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="15">
         <v>17</v>
       </c>
@@ -7958,7 +7785,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15">
         <v>18</v>
       </c>
@@ -8004,7 +7831,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15">
         <v>19</v>
       </c>
@@ -8050,7 +7877,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15">
         <v>20</v>
       </c>
@@ -8096,7 +7923,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15">
         <v>21</v>
       </c>
@@ -8142,7 +7969,7 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15">
         <v>22</v>
       </c>
@@ -8188,7 +8015,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="15"/>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
@@ -8205,7 +8032,7 @@
       <c r="N29" s="6"/>
       <c r="O29" s="6"/>
     </row>
-    <row r="30" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
       <c r="B30" s="14"/>
       <c r="C30" s="57">
@@ -8246,7 +8073,7 @@
         <v>264873.42966686888</v>
       </c>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E33" s="33"/>
       <c r="F33" s="33"/>
     </row>

--- a/BELGRANO 1646/Agosto/Agosto-BLG1646.xlsx
+++ b/BELGRANO 1646/Agosto/Agosto-BLG1646.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BELGRANO 1646\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EA71FE-E90E-4848-A622-C7445FDFFEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92877A7C-2C8E-4A1F-B2D0-F1A48DBC0CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,14 +20,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$127</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$124</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="180">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -599,6 +599,9 @@
   </si>
   <si>
     <t>No hubo boleta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julio Dadona - Arreglo piso 5to </t>
   </si>
 </sst>
 </file>
@@ -1327,7 +1330,7 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="243">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
@@ -1564,9 +1567,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="15" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="21" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
@@ -1591,9 +1591,6 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="6" fillId="11" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1605,8 +1602,6 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="20" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1658,24 +1653,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1688,6 +1665,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1718,21 +1707,9 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1757,7 +1734,24 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2123,7 +2117,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P137"/>
+  <dimension ref="A1:P134"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.42578125" customWidth="1"/>
@@ -2212,26 +2206,26 @@
     <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="202" t="s">
+      <c r="B14" s="196" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="203"/>
-      <c r="D14" s="204"/>
+      <c r="C14" s="197"/>
+      <c r="D14" s="198"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="205"/>
-      <c r="C15" s="206"/>
-      <c r="D15" s="207"/>
+      <c r="B15" s="199"/>
+      <c r="C15" s="200"/>
+      <c r="D15" s="201"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="205"/>
-      <c r="C16" s="206"/>
-      <c r="D16" s="207"/>
+      <c r="B16" s="199"/>
+      <c r="C16" s="200"/>
+      <c r="D16" s="201"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="208"/>
-      <c r="C17" s="209"/>
-      <c r="D17" s="210"/>
+      <c r="B17" s="202"/>
+      <c r="C17" s="203"/>
+      <c r="D17" s="204"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
@@ -2244,10 +2238,10 @@
       <c r="B21" s="62"/>
       <c r="C21" s="63"/>
       <c r="D21" s="59"/>
-      <c r="E21" s="193" t="s">
+      <c r="E21" s="189" t="s">
         <v>121</v>
       </c>
-      <c r="F21" s="194" t="s">
+      <c r="F21" s="190" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2260,8 +2254,8 @@
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="129"/>
-      <c r="E22" s="192"/>
-      <c r="F22" s="192"/>
+      <c r="E22" s="188"/>
+      <c r="F22" s="188"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="120" t="s">
@@ -2269,16 +2263,16 @@
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="189">
-        <v>1262522.3</v>
+      <c r="D23" s="174">
+        <v>1277708.7</v>
       </c>
       <c r="E23" s="133">
         <f>D23*91.91%</f>
-        <v>1160384.24593</v>
+        <v>1174342.0661699998</v>
       </c>
       <c r="F23" s="133">
         <f>D23*8.09%</f>
-        <v>102138.05407</v>
+        <v>103366.63382999999</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -2287,16 +2281,16 @@
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="189">
-        <v>-274598.59999999998</v>
+      <c r="D24" s="174">
+        <v>-277901.65000000002</v>
       </c>
       <c r="E24" s="133">
         <f t="shared" ref="E24:E25" si="0">D24*91.91%</f>
-        <v>-252383.57325999995</v>
+        <v>-255419.40651500001</v>
       </c>
       <c r="F24" s="133">
         <f t="shared" ref="F24:F25" si="1">D24*8.09%</f>
-        <v>-22215.026739999998</v>
+        <v>-22482.243485000003</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -2305,23 +2299,23 @@
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="189">
-        <v>0.3</v>
+      <c r="D25" s="174">
+        <v>0.95</v>
       </c>
       <c r="E25" s="133">
         <f t="shared" si="0"/>
-        <v>0.27572999999999998</v>
+        <v>0.87314499999999984</v>
       </c>
       <c r="F25" s="133">
         <f t="shared" si="1"/>
-        <v>2.427E-2</v>
+        <v>7.6854999999999993E-2</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="120"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="175"/>
+      <c r="D26" s="174"/>
       <c r="E26" s="133"/>
       <c r="F26" s="7"/>
     </row>
@@ -2333,19 +2327,19 @@
       <c r="C27" s="95"/>
       <c r="D27" s="107">
         <f>SUM(D23:D26)</f>
-        <v>987924.00000000012</v>
+        <v>999807.99999999988</v>
       </c>
       <c r="E27" s="107">
         <f>SUM(E23:E26)</f>
-        <v>908000.94839999999</v>
+        <v>918923.5327999997</v>
       </c>
       <c r="F27" s="107">
         <f>SUM(F23:F26)</f>
-        <v>79923.051599999992</v>
+        <v>80884.467199999999</v>
       </c>
       <c r="G27" s="108">
         <f>E27+F27</f>
-        <v>987924</v>
+        <v>999807.99999999965</v>
       </c>
       <c r="H27" s="146" t="str">
         <f>IF(D27=G27, "", "Error")</f>
@@ -2358,7 +2352,7 @@
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="176">
+      <c r="D28" s="175">
         <v>0</v>
       </c>
       <c r="E28" s="133">
@@ -2375,7 +2369,7 @@
       <c r="A29" s="94"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="175">
+      <c r="D29" s="174">
         <v>0</v>
       </c>
       <c r="E29" s="133">
@@ -2392,7 +2386,7 @@
       <c r="A30" s="94"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="175"/>
+      <c r="D30" s="174"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="H30" s="146"/>
@@ -2401,7 +2395,7 @@
       <c r="A31" s="94"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="175"/>
+      <c r="D31" s="174"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="H31" s="146"/>
@@ -2439,7 +2433,7 @@
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="176"/>
+      <c r="D33" s="175"/>
       <c r="E33" s="133">
         <f>D33*91.91%</f>
         <v>0</v>
@@ -2456,7 +2450,7 @@
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="175"/>
+      <c r="D34" s="174"/>
       <c r="E34" s="133">
         <f t="shared" ref="E34:E35" si="3">D34*91.91%</f>
         <v>0</v>
@@ -2473,7 +2467,7 @@
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="175"/>
+      <c r="D35" s="174"/>
       <c r="E35" s="133">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2508,7 +2502,7 @@
       <c r="A37" s="128"/>
       <c r="B37" s="98"/>
       <c r="C37" s="98"/>
-      <c r="D37" s="175"/>
+      <c r="D37" s="174"/>
       <c r="E37" s="119"/>
       <c r="F37" s="119"/>
       <c r="H37" s="146"/>
@@ -2517,7 +2511,7 @@
       <c r="A38" s="128"/>
       <c r="B38" s="98"/>
       <c r="C38" s="98"/>
-      <c r="D38" s="175"/>
+      <c r="D38" s="174"/>
       <c r="E38" s="119"/>
       <c r="F38" s="119"/>
       <c r="H38" s="146"/>
@@ -2526,7 +2520,7 @@
       <c r="A39" s="98"/>
       <c r="B39" s="98"/>
       <c r="C39" s="110"/>
-      <c r="D39" s="175"/>
+      <c r="D39" s="174"/>
       <c r="E39" s="119"/>
       <c r="F39" s="119"/>
       <c r="H39" s="146"/>
@@ -2582,7 +2576,7 @@
       <c r="A43" s="94"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="178"/>
+      <c r="D43" s="177"/>
       <c r="E43" s="133">
         <f>D43*91.91%</f>
         <v>0</v>
@@ -2623,7 +2617,7 @@
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="178"/>
+      <c r="D45" s="177"/>
       <c r="E45" s="113"/>
       <c r="F45" s="100"/>
       <c r="H45" s="146"/>
@@ -2634,7 +2628,7 @@
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="98"/>
-      <c r="D46" s="185">
+      <c r="D46" s="112">
         <v>5020</v>
       </c>
       <c r="E46" s="133">
@@ -2655,7 +2649,7 @@
         <v>165</v>
       </c>
       <c r="C47" s="7"/>
-      <c r="D47" s="185">
+      <c r="D47" s="112">
         <f>106691.95+6312.61+56813.5</f>
         <v>169818.06</v>
       </c>
@@ -2677,7 +2671,7 @@
         <v>164</v>
       </c>
       <c r="C48" s="7"/>
-      <c r="D48" s="185">
+      <c r="D48" s="112">
         <v>559190.81000000006</v>
       </c>
       <c r="E48" s="133">
@@ -2723,18 +2717,18 @@
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="178"/>
+      <c r="D50" s="177"/>
       <c r="E50" s="114"/>
       <c r="F50" s="7"/>
       <c r="H50" s="146"/>
     </row>
     <row r="51" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="182" t="s">
+      <c r="A51" s="181" t="s">
         <v>163</v>
       </c>
-      <c r="B51" s="171"/>
-      <c r="C51" s="172"/>
-      <c r="D51" s="187">
+      <c r="B51" s="170"/>
+      <c r="C51" s="171"/>
+      <c r="D51" s="177">
         <v>160000</v>
       </c>
       <c r="E51" s="145">
@@ -2750,16 +2744,16 @@
         <f>E51+F51</f>
         <v>160000</v>
       </c>
-      <c r="I51" s="173"/>
-      <c r="J51" s="173"/>
+      <c r="I51" s="172"/>
+      <c r="J51" s="172"/>
     </row>
     <row r="52" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="182" t="s">
+      <c r="A52" s="181" t="s">
         <v>138</v>
       </c>
-      <c r="B52" s="171"/>
-      <c r="C52" s="172"/>
-      <c r="D52" s="185">
+      <c r="B52" s="170"/>
+      <c r="C52" s="171"/>
+      <c r="D52" s="112">
         <v>372000</v>
       </c>
       <c r="E52" s="145">
@@ -2775,11 +2769,11 @@
         <f>E52+F52</f>
         <v>372000</v>
       </c>
-      <c r="I52" s="173">
+      <c r="I52" s="172">
         <f>H52-D52</f>
         <v>0</v>
       </c>
-      <c r="J52" s="173"/>
+      <c r="J52" s="172"/>
     </row>
     <row r="53" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="120" t="s">
@@ -2797,15 +2791,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="108">
-        <f t="shared" ref="G53:G70" si="9">D53</f>
+        <f t="shared" ref="G53:G67" si="9">D53</f>
         <v>0</v>
       </c>
       <c r="H53" s="156">
-        <f t="shared" ref="H53:H70" si="10">E53+F53</f>
-        <v>0</v>
-      </c>
-      <c r="I53" s="173"/>
-      <c r="J53" s="173"/>
+        <f t="shared" ref="H53:H67" si="10">E53+F53</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="172"/>
+      <c r="J53" s="172"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="94" t="s">
@@ -2813,7 +2807,7 @@
       </c>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="185">
+      <c r="D54" s="112">
         <v>148200</v>
       </c>
       <c r="E54" s="145">
@@ -2832,12 +2826,12 @@
         <f t="shared" si="10"/>
         <v>148200</v>
       </c>
-      <c r="I54" s="173">
-        <f t="shared" ref="I54:I69" si="11">H54-D54</f>
-        <v>0</v>
-      </c>
-      <c r="J54" s="173">
-        <f t="shared" ref="J54:J70" si="12">G54-D54</f>
+      <c r="I54" s="172">
+        <f t="shared" ref="I54:I66" si="11">H54-D54</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="172">
+        <f t="shared" ref="J54:J67" si="12">G54-D54</f>
         <v>0</v>
       </c>
     </row>
@@ -2849,7 +2843,7 @@
         <v>167</v>
       </c>
       <c r="C55" s="7"/>
-      <c r="D55" s="185">
+      <c r="D55" s="112">
         <v>129320</v>
       </c>
       <c r="E55" s="145">
@@ -2868,11 +2862,11 @@
         <f>E55+F55</f>
         <v>129319.99999999999</v>
       </c>
-      <c r="I55" s="173">
+      <c r="I55" s="172">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J55" s="173">
+      <c r="J55" s="172">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -2904,11 +2898,11 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I56" s="173">
+      <c r="I56" s="172">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J56" s="173">
+      <c r="J56" s="172">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -2921,7 +2915,7 @@
         <v>171</v>
       </c>
       <c r="C57" s="98"/>
-      <c r="D57" s="185">
+      <c r="D57" s="112">
         <v>1173289.52</v>
       </c>
       <c r="E57" s="145">
@@ -2940,26 +2934,26 @@
         <f t="shared" si="10"/>
         <v>1173289.52</v>
       </c>
-      <c r="I57" s="173">
+      <c r="I57" s="172">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J57" s="173">
+      <c r="J57" s="172">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="197" t="s">
+      <c r="A58" s="191" t="s">
         <v>162</v>
       </c>
-      <c r="B58" s="198"/>
-      <c r="C58" s="199"/>
-      <c r="D58" s="185">
+      <c r="B58" s="192"/>
+      <c r="C58" s="193"/>
+      <c r="D58" s="112">
         <v>67000</v>
       </c>
       <c r="E58" s="145">
-        <f t="shared" ref="E58:E63" si="13">D58</f>
+        <f t="shared" ref="E58:E61" si="13">D58</f>
         <v>67000</v>
       </c>
       <c r="F58" s="133"/>
@@ -2971,1125 +2965,1071 @@
         <f t="shared" si="10"/>
         <v>67000</v>
       </c>
-      <c r="I58" s="173">
+      <c r="I58" s="172">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J58" s="173">
+      <c r="J58" s="172">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="197" t="s">
-        <v>175</v>
-      </c>
-      <c r="B59" s="198"/>
-      <c r="C59" s="199"/>
-      <c r="D59" s="185">
-        <v>1400000</v>
+    <row r="59" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="236" t="s">
+        <v>160</v>
+      </c>
+      <c r="B59" s="237"/>
+      <c r="C59" s="238"/>
+      <c r="D59" s="112">
+        <v>35500</v>
       </c>
       <c r="E59" s="145">
-        <f t="shared" ref="E59:E66" si="14">D59*91.91%</f>
-        <v>1286740</v>
+        <f t="shared" ref="E59:E61" si="14">D59*91.91%</f>
+        <v>32628.049999999996</v>
       </c>
       <c r="F59" s="133">
-        <f t="shared" ref="F59:F66" si="15">D59*8.09%</f>
-        <v>113260</v>
+        <f t="shared" ref="F59:F61" si="15">D59*8.09%</f>
+        <v>2871.95</v>
       </c>
       <c r="G59" s="108">
         <f t="shared" si="9"/>
-        <v>1400000</v>
+        <v>35500</v>
       </c>
       <c r="H59" s="156">
         <f t="shared" si="10"/>
-        <v>1400000</v>
-      </c>
-      <c r="I59" s="173">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="173"/>
-    </row>
-    <row r="60" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="197" t="s">
-        <v>176</v>
-      </c>
-      <c r="B60" s="198"/>
-      <c r="C60" s="199"/>
-      <c r="D60" s="185">
-        <v>1000000</v>
+        <v>35499.999999999993</v>
+      </c>
+      <c r="I59" s="172"/>
+      <c r="J59" s="172"/>
+    </row>
+    <row r="60" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="236" t="s">
+        <v>161</v>
+      </c>
+      <c r="B60" s="237"/>
+      <c r="C60" s="238"/>
+      <c r="D60" s="112">
+        <v>159500</v>
       </c>
       <c r="E60" s="145">
         <f t="shared" si="14"/>
-        <v>919099.99999999988</v>
+        <v>146596.44999999998</v>
       </c>
       <c r="F60" s="133">
         <f t="shared" si="15"/>
-        <v>80900</v>
+        <v>12903.55</v>
       </c>
       <c r="G60" s="108">
         <f t="shared" si="9"/>
-        <v>1000000</v>
-      </c>
-      <c r="H60" s="156"/>
-      <c r="I60" s="173"/>
-      <c r="J60" s="173"/>
+        <v>159500</v>
+      </c>
+      <c r="H60" s="156">
+        <f t="shared" si="10"/>
+        <v>159499.99999999997</v>
+      </c>
+      <c r="I60" s="172"/>
+      <c r="J60" s="172"/>
     </row>
     <row r="61" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="197" t="s">
-        <v>160</v>
-      </c>
-      <c r="B61" s="198"/>
-      <c r="C61" s="199"/>
-      <c r="D61" s="185">
-        <v>35500</v>
+      <c r="A61" s="236" t="s">
+        <v>159</v>
+      </c>
+      <c r="B61" s="237"/>
+      <c r="C61" s="238"/>
+      <c r="D61" s="112">
+        <v>170000</v>
       </c>
       <c r="E61" s="145">
-        <f t="shared" si="13"/>
-        <v>35500</v>
-      </c>
-      <c r="F61" s="133"/>
+        <f t="shared" si="14"/>
+        <v>156247</v>
+      </c>
+      <c r="F61" s="133">
+        <f t="shared" si="15"/>
+        <v>13753</v>
+      </c>
       <c r="G61" s="108">
         <f t="shared" si="9"/>
-        <v>35500</v>
+        <v>170000</v>
       </c>
       <c r="H61" s="156">
         <f t="shared" si="10"/>
-        <v>35500</v>
-      </c>
-      <c r="I61" s="173"/>
-      <c r="J61" s="173"/>
-    </row>
-    <row r="62" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="197" t="s">
-        <v>161</v>
-      </c>
-      <c r="B62" s="198"/>
-      <c r="C62" s="199"/>
-      <c r="D62" s="185">
-        <v>159500</v>
+        <v>170000</v>
+      </c>
+      <c r="I61" s="172"/>
+      <c r="J61" s="172"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A62" s="235" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" s="98" t="s">
+        <v>144</v>
+      </c>
+      <c r="C62" s="98"/>
+      <c r="D62" s="112">
+        <v>141112.26</v>
       </c>
       <c r="E62" s="145">
-        <f t="shared" si="13"/>
-        <v>159500</v>
-      </c>
-      <c r="F62" s="133"/>
+        <f t="shared" ref="E62:E64" si="16">D62*91.91%</f>
+        <v>129696.278166</v>
+      </c>
+      <c r="F62" s="133">
+        <f t="shared" ref="F62:F67" si="17">D62*8.09%</f>
+        <v>11415.981834</v>
+      </c>
       <c r="G62" s="108">
         <f t="shared" si="9"/>
-        <v>159500</v>
+        <v>141112.26</v>
       </c>
       <c r="H62" s="156">
         <f t="shared" si="10"/>
-        <v>159500</v>
-      </c>
-      <c r="I62" s="173"/>
-      <c r="J62" s="173"/>
-    </row>
-    <row r="63" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="197" t="s">
-        <v>159</v>
-      </c>
-      <c r="B63" s="198"/>
-      <c r="C63" s="199"/>
-      <c r="D63" s="185">
-        <v>170000</v>
+        <v>141112.26</v>
+      </c>
+      <c r="I62" s="172">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J62" s="172">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M62" s="183" t="s">
+        <v>137</v>
+      </c>
+      <c r="N62" s="7"/>
+      <c r="O62" s="7"/>
+      <c r="P62" s="184">
+        <v>358487.12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" s="235" t="s">
+        <v>137</v>
+      </c>
+      <c r="B63" s="98" t="s">
+        <v>144</v>
+      </c>
+      <c r="C63" s="98"/>
+      <c r="D63" s="112">
+        <v>199992.75</v>
       </c>
       <c r="E63" s="145">
-        <f t="shared" si="13"/>
-        <v>170000</v>
-      </c>
-      <c r="F63" s="7"/>
+        <f>D63*91.91%</f>
+        <v>183813.33652499999</v>
+      </c>
+      <c r="F63" s="133">
+        <f t="shared" si="17"/>
+        <v>16179.413474999999</v>
+      </c>
       <c r="G63" s="108">
         <f t="shared" si="9"/>
-        <v>170000</v>
+        <v>199992.75</v>
       </c>
       <c r="H63" s="156">
         <f t="shared" si="10"/>
-        <v>170000</v>
-      </c>
-      <c r="I63" s="173"/>
-      <c r="J63" s="173"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A64" s="98" t="s">
-        <v>137</v>
-      </c>
-      <c r="B64" s="98" t="s">
-        <v>144</v>
-      </c>
-      <c r="C64" s="98"/>
-      <c r="D64" s="185">
-        <v>141112.26</v>
-      </c>
+        <v>199992.75</v>
+      </c>
+      <c r="I63" s="172">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J63" s="172">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D64" s="112"/>
       <c r="E64" s="145">
-        <f t="shared" si="14"/>
-        <v>129696.278166</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="F64" s="133">
-        <f t="shared" si="15"/>
-        <v>11415.981834</v>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="G64" s="108">
         <f t="shared" si="9"/>
-        <v>141112.26</v>
+        <v>0</v>
       </c>
       <c r="H64" s="156">
         <f t="shared" si="10"/>
-        <v>141112.26</v>
-      </c>
-      <c r="I64" s="173">
+        <v>0</v>
+      </c>
+      <c r="I64" s="172">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J64" s="173">
+      <c r="J64" s="172">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="M64" s="184" t="s">
-        <v>137</v>
-      </c>
-      <c r="N64" s="7"/>
-      <c r="O64" s="7"/>
-      <c r="P64" s="185">
-        <v>358487.12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="98" t="s">
-        <v>137</v>
-      </c>
-      <c r="B65" s="98" t="s">
-        <v>144</v>
-      </c>
-      <c r="C65" s="98"/>
-      <c r="D65" s="185">
-        <v>199992.75</v>
+    </row>
+    <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="120" t="s">
+        <v>179</v>
+      </c>
+      <c r="B65" s="113"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="112">
+        <v>360000</v>
       </c>
       <c r="E65" s="145">
-        <f t="shared" si="14"/>
-        <v>183813.33652499999</v>
+        <f>D65*91.91%</f>
+        <v>330875.99999999994</v>
       </c>
       <c r="F65" s="133">
-        <f t="shared" si="15"/>
-        <v>16179.413474999999</v>
-      </c>
-      <c r="G65" s="108">
-        <f t="shared" si="9"/>
-        <v>199992.75</v>
-      </c>
-      <c r="H65" s="156">
-        <f t="shared" si="10"/>
-        <v>199992.75</v>
-      </c>
-      <c r="I65" s="173">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J65" s="173">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="17"/>
+        <v>29124</v>
+      </c>
+      <c r="G65" s="108"/>
+      <c r="H65" s="156"/>
+      <c r="I65" s="172"/>
+      <c r="J65" s="172"/>
     </row>
     <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D66" s="185"/>
+      <c r="A66" s="235" t="s">
+        <v>172</v>
+      </c>
+      <c r="B66" s="113"/>
+      <c r="C66" s="157"/>
+      <c r="D66" s="112">
+        <v>248007.9</v>
+      </c>
       <c r="E66" s="145">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" ref="E66:E67" si="18">D66*91.91%</f>
+        <v>227944.06088999996</v>
       </c>
       <c r="F66" s="133">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>20063.839110000001</v>
       </c>
       <c r="G66" s="108">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>248007.9</v>
       </c>
       <c r="H66" s="156">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="I66" s="173">
+        <v>248007.89999999997</v>
+      </c>
+      <c r="I66" s="172">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J66" s="173">
+      <c r="J66" s="172">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="98" t="s">
-        <v>168</v>
-      </c>
-      <c r="B67" s="113"/>
-      <c r="C67" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D67" s="185">
-        <v>260000</v>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="239" t="s">
+        <v>173</v>
+      </c>
+      <c r="B67" s="151"/>
+      <c r="C67" s="151"/>
+      <c r="D67" s="161">
+        <v>25000</v>
       </c>
       <c r="E67" s="145">
-        <f t="shared" ref="E67:E70" si="16">D67</f>
-        <v>260000</v>
-      </c>
-      <c r="F67" s="133"/>
+        <f t="shared" si="18"/>
+        <v>22977.499999999996</v>
+      </c>
+      <c r="F67" s="133">
+        <f t="shared" si="17"/>
+        <v>2022.5</v>
+      </c>
       <c r="G67" s="108">
         <f t="shared" si="9"/>
-        <v>260000</v>
+        <v>25000</v>
       </c>
       <c r="H67" s="156">
         <f t="shared" si="10"/>
-        <v>260000</v>
-      </c>
-      <c r="I67" s="173">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J67" s="173">
+        <v>24999.999999999996</v>
+      </c>
+      <c r="I67" t="str">
+        <f>IF(G67=H67, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J67" s="172">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="98" t="s">
-        <v>169</v>
-      </c>
-      <c r="B68" s="113"/>
-      <c r="C68" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D68" s="185">
-        <v>256310.6</v>
-      </c>
-      <c r="E68" s="145">
-        <f t="shared" si="16"/>
-        <v>256310.6</v>
-      </c>
-      <c r="F68" s="133"/>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="95" t="s">
+        <v>12</v>
+      </c>
+      <c r="B68" s="96"/>
+      <c r="C68" s="96"/>
+      <c r="D68" s="107">
+        <f>SUM(D51:D67)</f>
+        <v>3388922.43</v>
+      </c>
+      <c r="E68" s="107">
+        <f>SUM(E51:E67)</f>
+        <v>3163217.7054129997</v>
+      </c>
+      <c r="F68" s="107">
+        <f>SUM(F51:F67)</f>
+        <v>225704.724587</v>
+      </c>
       <c r="G68" s="108">
-        <f t="shared" si="9"/>
-        <v>256310.6</v>
-      </c>
-      <c r="H68" s="156">
-        <f t="shared" si="10"/>
-        <v>256310.6</v>
-      </c>
-      <c r="I68" s="173"/>
-      <c r="J68" s="173"/>
-    </row>
-    <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="98" t="s">
-        <v>172</v>
-      </c>
-      <c r="B69" s="113"/>
-      <c r="C69" s="157"/>
-      <c r="D69" s="185">
-        <v>248007.9</v>
-      </c>
-      <c r="E69" s="145">
-        <f t="shared" si="16"/>
-        <v>248007.9</v>
-      </c>
-      <c r="F69" s="133"/>
-      <c r="G69" s="108">
-        <f t="shared" si="9"/>
-        <v>248007.9</v>
-      </c>
-      <c r="H69" s="156">
-        <f t="shared" si="10"/>
-        <v>248007.9</v>
-      </c>
-      <c r="I69" s="173">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J69" s="173">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="190" t="s">
-        <v>173</v>
-      </c>
-      <c r="B70" s="151"/>
-      <c r="C70" s="151"/>
-      <c r="D70" s="188">
-        <v>25000</v>
-      </c>
-      <c r="E70" s="145">
-        <f t="shared" si="16"/>
-        <v>25000</v>
-      </c>
-      <c r="F70" s="133"/>
-      <c r="G70" s="108">
-        <f t="shared" si="9"/>
-        <v>25000</v>
-      </c>
-      <c r="H70" s="156">
-        <f t="shared" si="10"/>
-        <v>25000</v>
-      </c>
-      <c r="I70" t="str">
-        <f>IF(G70=H70, "", "Error")</f>
+        <f>E68+F68</f>
+        <v>3388922.4299999997</v>
+      </c>
+      <c r="H68" s="146" t="str">
+        <f>IF(D68=G68, "", "Error")</f>
         <v/>
       </c>
-      <c r="J70" s="173">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="95" t="s">
-        <v>12</v>
-      </c>
-      <c r="B71" s="96"/>
-      <c r="C71" s="96"/>
-      <c r="D71" s="107">
-        <f>SUM(D51:D70)</f>
-        <v>5945233.0299999993</v>
-      </c>
-      <c r="E71" s="107">
-        <f>SUM(E51:E70)</f>
-        <v>5606107.1445229994</v>
-      </c>
-      <c r="F71" s="107">
-        <f>SUM(F51:F70)</f>
-        <v>339125.88547699997</v>
-      </c>
-      <c r="G71" s="108">
-        <f>E71+F71</f>
-        <v>5945233.0299999993</v>
-      </c>
-      <c r="H71" s="146" t="str">
-        <f>IF(D71=G71, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="I71" s="173">
-        <f>D71-G71</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="7"/>
-      <c r="B72" s="7"/>
+      <c r="I68" s="172">
+        <f>D68-G68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="7"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="177"/>
+      <c r="E69" s="114"/>
+      <c r="F69" s="7"/>
+      <c r="H69" s="146"/>
+    </row>
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="7"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="177"/>
+      <c r="E70" s="113"/>
+      <c r="F70" s="7"/>
+      <c r="H70" s="146"/>
+    </row>
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="7"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="177"/>
+      <c r="E71" s="113"/>
+      <c r="F71" s="7"/>
+      <c r="H71" s="146"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="94" t="s">
+        <v>141</v>
+      </c>
+      <c r="B72" s="98"/>
       <c r="C72" s="7"/>
-      <c r="D72" s="178"/>
-      <c r="E72" s="114"/>
-      <c r="F72" s="7"/>
+      <c r="D72" s="112">
+        <v>124980</v>
+      </c>
+      <c r="E72" s="145">
+        <f>D72*91.91%</f>
+        <v>114869.11799999999</v>
+      </c>
+      <c r="F72" s="133">
+        <f>D72*8.09%</f>
+        <v>10110.882</v>
+      </c>
+      <c r="G72" s="155"/>
       <c r="H72" s="146"/>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
-      <c r="D73" s="178"/>
-      <c r="E73" s="113"/>
+      <c r="D73" s="112"/>
+      <c r="E73" s="159">
+        <f>D73</f>
+        <v>0</v>
+      </c>
       <c r="F73" s="7"/>
       <c r="H73" s="146"/>
-    </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="178"/>
-      <c r="E74" s="113"/>
-      <c r="F74" s="7"/>
-      <c r="H74" s="146"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="94" t="s">
-        <v>141</v>
-      </c>
-      <c r="B75" s="98"/>
+      <c r="I73" s="108"/>
+    </row>
+    <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="95" t="s">
+        <v>16</v>
+      </c>
+      <c r="B74" s="95"/>
+      <c r="C74" s="95"/>
+      <c r="D74" s="107">
+        <f>SUM(D72:D73)</f>
+        <v>124980</v>
+      </c>
+      <c r="E74" s="107">
+        <f>SUM(E72:E73)</f>
+        <v>114869.11799999999</v>
+      </c>
+      <c r="F74" s="107">
+        <f>SUM(F72:F73)</f>
+        <v>10110.882</v>
+      </c>
+      <c r="G74" s="108">
+        <f>E74+F74</f>
+        <v>124979.99999999999</v>
+      </c>
+      <c r="H74" s="146" t="str">
+        <f>IF(D74=G74, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J74" s="108"/>
+    </row>
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="7"/>
+      <c r="B75" s="7"/>
       <c r="C75" s="7"/>
-      <c r="D75" s="185">
-        <v>124980</v>
-      </c>
-      <c r="E75" s="145">
-        <f>D75*91.91%</f>
-        <v>114869.11799999999</v>
-      </c>
-      <c r="F75" s="133">
-        <f>D75*8.09%</f>
-        <v>10110.882</v>
-      </c>
-      <c r="G75" s="155"/>
+      <c r="D75" s="177"/>
+      <c r="E75" s="114"/>
+      <c r="F75" s="7"/>
       <c r="H75" s="146"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
-      <c r="D76" s="112"/>
-      <c r="E76" s="159">
-        <f>D76</f>
-        <v>0</v>
-      </c>
+      <c r="D76" s="177"/>
+      <c r="E76" s="113"/>
       <c r="F76" s="7"/>
       <c r="H76" s="146"/>
-      <c r="I76" s="108"/>
-    </row>
-    <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="95" t="s">
-        <v>16</v>
-      </c>
-      <c r="B77" s="95"/>
-      <c r="C77" s="95"/>
-      <c r="D77" s="107">
-        <f>SUM(D75:D76)</f>
-        <v>124980</v>
-      </c>
-      <c r="E77" s="107">
-        <f>SUM(E75:E76)</f>
-        <v>114869.11799999999</v>
-      </c>
-      <c r="F77" s="107">
-        <f>SUM(F75:F76)</f>
-        <v>10110.882</v>
-      </c>
-      <c r="G77" s="108">
-        <f>E77+F77</f>
-        <v>124979.99999999999</v>
-      </c>
-      <c r="H77" s="146" t="str">
-        <f>IF(D77=G77, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J77" s="108"/>
-    </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="7"/>
-      <c r="B78" s="7"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="94" t="s">
+        <v>13</v>
+      </c>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="177"/>
+      <c r="E77" s="113"/>
+      <c r="F77" s="7"/>
+      <c r="H77" s="146"/>
+    </row>
+    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="94" t="s">
+        <v>14</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>116</v>
+      </c>
       <c r="C78" s="7"/>
-      <c r="D78" s="178"/>
-      <c r="E78" s="114"/>
-      <c r="F78" s="7"/>
+      <c r="D78" s="112">
+        <v>246000</v>
+      </c>
+      <c r="E78" s="145">
+        <f>D78*91.91%</f>
+        <v>226098.59999999998</v>
+      </c>
+      <c r="F78" s="133">
+        <f>D78*8.09%</f>
+        <v>19901.400000000001</v>
+      </c>
+      <c r="G78" t="s">
+        <v>139</v>
+      </c>
       <c r="H78" s="146"/>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="7"/>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="94" t="s">
+        <v>107</v>
+      </c>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
-      <c r="D79" s="178"/>
-      <c r="E79" s="113"/>
-      <c r="F79" s="7"/>
+      <c r="D79" s="112">
+        <v>30000</v>
+      </c>
+      <c r="E79" s="145">
+        <f>D79*91.91%</f>
+        <v>27572.999999999996</v>
+      </c>
+      <c r="F79" s="133">
+        <f>D79*8.09%</f>
+        <v>2427</v>
+      </c>
       <c r="H79" s="146"/>
+      <c r="J79" s="112"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="94" t="s">
-        <v>13</v>
-      </c>
+      <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
-      <c r="D80" s="178"/>
-      <c r="E80" s="113"/>
+      <c r="D80" s="177"/>
+      <c r="E80" s="115"/>
       <c r="F80" s="7"/>
       <c r="H80" s="146"/>
-    </row>
-    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="94" t="s">
-        <v>14</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C81" s="7"/>
-      <c r="D81" s="185">
-        <v>246000</v>
-      </c>
-      <c r="E81" s="145">
-        <f>D81*91.91%</f>
-        <v>226098.59999999998</v>
-      </c>
-      <c r="F81" s="133">
-        <f>D81*8.09%</f>
-        <v>19901.400000000001</v>
-      </c>
-      <c r="G81" t="s">
-        <v>139</v>
-      </c>
-      <c r="H81" s="146"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J80" s="108"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="95" t="s">
+        <v>100</v>
+      </c>
+      <c r="B81" s="95"/>
+      <c r="C81" s="95"/>
+      <c r="D81" s="107">
+        <f>SUM(D78:D80)</f>
+        <v>276000</v>
+      </c>
+      <c r="E81" s="107">
+        <f>SUM(E78:E80)</f>
+        <v>253671.59999999998</v>
+      </c>
+      <c r="F81" s="107">
+        <f>SUM(F78:F80)</f>
+        <v>22328.400000000001</v>
+      </c>
+      <c r="G81" s="108">
+        <f>E81+F81</f>
+        <v>276000</v>
+      </c>
+      <c r="H81" s="146" t="str">
+        <f>IF(D81=G81, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J81" s="108"/>
+    </row>
+    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="94" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
-      <c r="D82" s="185">
-        <v>30000</v>
-      </c>
-      <c r="E82" s="145">
-        <f>D82*91.91%</f>
-        <v>27572.999999999996</v>
-      </c>
-      <c r="F82" s="133">
-        <f>D82*8.09%</f>
-        <v>2427</v>
-      </c>
+      <c r="D82" s="112"/>
+      <c r="E82" s="116"/>
+      <c r="F82" s="7"/>
       <c r="H82" s="146"/>
-      <c r="J82" s="112"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="7"/>
+      <c r="A83" s="94" t="s">
+        <v>101</v>
+      </c>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
-      <c r="D83" s="178"/>
-      <c r="E83" s="115"/>
-      <c r="F83" s="7"/>
+      <c r="D83" s="112">
+        <v>114083.66</v>
+      </c>
+      <c r="E83" s="145">
+        <f>D83*91.91%</f>
+        <v>104854.291906</v>
+      </c>
+      <c r="F83" s="133">
+        <f>D83*8.09%</f>
+        <v>9229.3680939999995</v>
+      </c>
       <c r="H83" s="146"/>
-      <c r="J83" s="108"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" s="95" t="s">
-        <v>100</v>
-      </c>
-      <c r="B84" s="95"/>
-      <c r="C84" s="95"/>
-      <c r="D84" s="107">
-        <f>SUM(D81:D83)</f>
-        <v>276000</v>
-      </c>
-      <c r="E84" s="107">
-        <f>SUM(E81:E83)</f>
-        <v>253671.59999999998</v>
-      </c>
-      <c r="F84" s="107">
-        <f>SUM(F81:F83)</f>
-        <v>22328.400000000001</v>
-      </c>
-      <c r="G84" s="108">
-        <f>E84+F84</f>
-        <v>276000</v>
-      </c>
-      <c r="H84" s="146" t="str">
-        <f>IF(D84=G84, "", "Error")</f>
+      <c r="A84" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="B84" s="7"/>
+      <c r="C84" s="121"/>
+      <c r="D84" s="112">
+        <v>44400</v>
+      </c>
+      <c r="E84" s="145">
+        <f>D84*91.91%</f>
+        <v>40808.039999999994</v>
+      </c>
+      <c r="F84" s="133">
+        <f>D84*8.09%</f>
+        <v>3591.96</v>
+      </c>
+      <c r="H84" s="146"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" s="95"/>
+      <c r="C85" s="95"/>
+      <c r="D85" s="153">
+        <f>SUM(D83:D84)</f>
+        <v>158483.66</v>
+      </c>
+      <c r="E85" s="143">
+        <f t="shared" ref="E85:F85" si="19">SUM(E83:E84)</f>
+        <v>145662.33190599998</v>
+      </c>
+      <c r="F85" s="143">
+        <f t="shared" si="19"/>
+        <v>12821.328094</v>
+      </c>
+      <c r="G85" s="108">
+        <f>E85+F85</f>
+        <v>158483.65999999997</v>
+      </c>
+      <c r="H85" s="146" t="str">
+        <f>IF(D85=G85, "", "Error")</f>
         <v/>
       </c>
-      <c r="J84" s="108"/>
-    </row>
-    <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="94" t="s">
-        <v>100</v>
-      </c>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="112"/>
-      <c r="E85" s="116"/>
-      <c r="F85" s="7"/>
-      <c r="H85" s="146"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" s="94" t="s">
-        <v>101</v>
-      </c>
+    </row>
+    <row r="86" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
-      <c r="D86" s="185">
-        <v>114083.66</v>
-      </c>
-      <c r="E86" s="145">
-        <f>D86*91.91%</f>
-        <v>104854.291906</v>
-      </c>
-      <c r="F86" s="133">
-        <f>D86*8.09%</f>
-        <v>9229.3680939999995</v>
-      </c>
+      <c r="D86" s="178"/>
+      <c r="E86" s="12"/>
+      <c r="F86" s="7"/>
       <c r="H86" s="146"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" s="94" t="s">
-        <v>102</v>
-      </c>
-      <c r="B87" s="7"/>
-      <c r="C87" s="121"/>
-      <c r="D87" s="185">
-        <v>44400</v>
-      </c>
-      <c r="E87" s="145">
+    <row r="87" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="99" t="s">
+        <v>133</v>
+      </c>
+      <c r="B87" s="99"/>
+      <c r="C87" s="99"/>
+      <c r="D87" s="179">
+        <f>9512420-5682222.96</f>
+        <v>3830197.04</v>
+      </c>
+      <c r="E87" s="117">
         <f>D87*91.91%</f>
-        <v>40808.039999999994</v>
-      </c>
-      <c r="F87" s="133">
+        <v>3520334.0994639997</v>
+      </c>
+      <c r="F87" s="135">
         <f>D87*8.09%</f>
-        <v>3591.96</v>
-      </c>
-      <c r="H87" s="146"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" s="95"/>
-      <c r="C88" s="95"/>
-      <c r="D88" s="153">
-        <f>SUM(D86:D87)</f>
-        <v>158483.66</v>
-      </c>
-      <c r="E88" s="143">
-        <f t="shared" ref="E88:F88" si="17">SUM(E86:E87)</f>
-        <v>145662.33190599998</v>
-      </c>
-      <c r="F88" s="143">
-        <f t="shared" si="17"/>
-        <v>12821.328094</v>
-      </c>
-      <c r="G88" s="108">
-        <f>E88+F88</f>
-        <v>158483.65999999997</v>
-      </c>
-      <c r="H88" s="146" t="str">
-        <f>IF(D88=G88, "", "Error")</f>
+        <v>309862.94053600001</v>
+      </c>
+      <c r="G87" s="108">
+        <f>E87+F87</f>
+        <v>3830197.0399999996</v>
+      </c>
+      <c r="H87" s="146" t="str">
+        <f>IF(D87=G87, "", "Error")</f>
         <v/>
       </c>
     </row>
+    <row r="88" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="1"/>
+      <c r="D88" s="176"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="10"/>
+      <c r="G88" s="152"/>
+      <c r="H88" s="146"/>
+    </row>
     <row r="89" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="7"/>
-      <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="179"/>
-      <c r="E89" s="12"/>
-      <c r="F89" s="7"/>
-      <c r="H89" s="146"/>
+      <c r="A89" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B89" s="60"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="180">
+        <f>SUM(D87+D85+D81+D74+D68+D49+D32+D27+D44)</f>
+        <v>9512420</v>
+      </c>
+      <c r="E89" s="144">
+        <f>SUM(E87+E85+E81+E74+E68+E49+E32+E27+E44)</f>
+        <v>8791324.3219999988</v>
+      </c>
+      <c r="F89" s="144">
+        <f>SUM(F87+F85+F81+F74+F68+F49+F32+F27+F44)</f>
+        <v>721095.67799999996</v>
+      </c>
+      <c r="G89" s="108">
+        <f>E89+F89</f>
+        <v>9512419.9999999981</v>
+      </c>
+      <c r="H89" s="146" t="str">
+        <f>IF(D89=G89, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="I89" s="172">
+        <f>D89-G89</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="90" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="99" t="s">
-        <v>133</v>
-      </c>
-      <c r="B90" s="99"/>
-      <c r="C90" s="99"/>
-      <c r="D90" s="180"/>
-      <c r="E90" s="117">
-        <f>D90*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F90" s="135">
-        <f>D90*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G90" s="108">
-        <f>E90+F90</f>
-        <v>0</v>
-      </c>
-      <c r="H90" s="146" t="str">
-        <f>IF(D90=G90, "", "Error")</f>
+      <c r="D90" s="176"/>
+      <c r="E90" s="108"/>
+    </row>
+    <row r="91" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="187" t="s">
+        <v>177</v>
+      </c>
+      <c r="B91" s="140"/>
+      <c r="C91" s="140"/>
+      <c r="E91" s="108"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="1"/>
+      <c r="C92" s="138"/>
+      <c r="E92" s="108"/>
+    </row>
+    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="1"/>
+      <c r="C93" s="138"/>
+      <c r="E93" s="108"/>
+    </row>
+    <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="141" t="s">
+        <v>29</v>
+      </c>
+      <c r="B94" s="142"/>
+      <c r="C94" s="139">
+        <f>SUM(C92:C93)</f>
+        <v>0</v>
+      </c>
+      <c r="E94" s="108"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E95" s="108"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E96" s="136"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="208" t="s">
+        <v>113</v>
+      </c>
+      <c r="B97" s="209"/>
+      <c r="C97" s="209"/>
+      <c r="D97" s="209"/>
+      <c r="E97" s="166" t="s">
+        <v>21</v>
+      </c>
+      <c r="F97" s="167" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="191" t="s">
+        <v>175</v>
+      </c>
+      <c r="B98" s="192"/>
+      <c r="C98" s="193"/>
+      <c r="D98" s="112">
+        <v>1400000</v>
+      </c>
+      <c r="E98" s="145">
+        <f t="shared" ref="E98:E99" si="20">D98*91.91%</f>
+        <v>1286740</v>
+      </c>
+      <c r="F98" s="133">
+        <f t="shared" ref="F98:F100" si="21">D98*8.09%</f>
+        <v>113260</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="191" t="s">
+        <v>176</v>
+      </c>
+      <c r="B99" s="192"/>
+      <c r="C99" s="193"/>
+      <c r="D99" s="112">
+        <v>1000000</v>
+      </c>
+      <c r="E99" s="145">
+        <f t="shared" si="20"/>
+        <v>919099.99999999988</v>
+      </c>
+      <c r="F99" s="133">
+        <f t="shared" si="21"/>
+        <v>80900</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="186" t="s">
+        <v>168</v>
+      </c>
+      <c r="B100" s="113"/>
+      <c r="C100" s="240" t="s">
+        <v>170</v>
+      </c>
+      <c r="D100" s="112">
+        <v>260000</v>
+      </c>
+      <c r="E100" s="145">
+        <f t="shared" ref="E100" si="22">D100*91.91%</f>
+        <v>238965.99999999997</v>
+      </c>
+      <c r="F100" s="133">
+        <f t="shared" si="21"/>
+        <v>21034</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="186" t="s">
+        <v>169</v>
+      </c>
+      <c r="B101" s="113"/>
+      <c r="C101" s="240" t="s">
+        <v>170</v>
+      </c>
+      <c r="D101" s="112">
+        <v>256310.6</v>
+      </c>
+      <c r="E101" s="145">
+        <f>D101*91.91%</f>
+        <v>235575.07246</v>
+      </c>
+      <c r="F101" s="133">
+        <f>D101*8.09%</f>
+        <v>20735.527539999999</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="205" t="s">
+        <v>29</v>
+      </c>
+      <c r="B102" s="206"/>
+      <c r="C102" s="207"/>
+      <c r="D102" s="165">
+        <f>SUM(D98:D101)</f>
+        <v>2916310.6</v>
+      </c>
+      <c r="E102" s="165">
+        <f>SUM(E98:E101)</f>
+        <v>2680381.0724599999</v>
+      </c>
+      <c r="F102" s="165">
+        <f>SUM(F98:F101)</f>
+        <v>235929.52754000001</v>
+      </c>
+      <c r="H102" s="108">
+        <f>E102+F102</f>
+        <v>2916310.6</v>
+      </c>
+      <c r="I102" s="146" t="str">
+        <f>IF(D102=H102, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="1"/>
-      <c r="D91" s="177"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="152"/>
-      <c r="H91" s="146"/>
-    </row>
-    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B92" s="60"/>
-      <c r="C92" s="5"/>
-      <c r="D92" s="181">
-        <f>SUM(D90+D88+D84+D77+D71+D49+D32+D27+D44)</f>
-        <v>8226649.5599999996</v>
-      </c>
-      <c r="E92" s="144">
-        <f>SUM(E90+E88+E84+E77+E71+E49+E32+E27+E44)</f>
-        <v>7702957.0772459991</v>
-      </c>
-      <c r="F92" s="144">
-        <f>SUM(F90+F88+F84+F77+F71+F49+F32+F27+F44)</f>
-        <v>523692.482754</v>
-      </c>
-      <c r="G92" s="108">
-        <f>E92+F92</f>
-        <v>8226649.5599999987</v>
-      </c>
-      <c r="H92" s="146" t="str">
-        <f>IF(D92=G92, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="I92" s="173">
-        <f>D92-G92</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D93" s="177"/>
-      <c r="E93" s="108"/>
-    </row>
-    <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="191" t="s">
-        <v>177</v>
-      </c>
-      <c r="B94" s="140"/>
-      <c r="C94" s="140"/>
-      <c r="E94" s="108"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="1"/>
-      <c r="C95" s="138"/>
-      <c r="E95" s="108"/>
-    </row>
-    <row r="96" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="1"/>
-      <c r="C96" s="138"/>
-      <c r="E96" s="108"/>
-    </row>
-    <row r="97" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="141" t="s">
-        <v>29</v>
-      </c>
-      <c r="B97" s="142"/>
-      <c r="C97" s="139">
-        <f>SUM(C95:C96)</f>
-        <v>0</v>
-      </c>
-      <c r="E97" s="108"/>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E98" s="108"/>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E99" s="136"/>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="220" t="s">
-        <v>113</v>
-      </c>
-      <c r="B100" s="221"/>
-      <c r="C100" s="221"/>
-      <c r="D100" s="221"/>
-      <c r="E100" s="166" t="s">
-        <v>21</v>
-      </c>
-      <c r="F100" s="167" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="217"/>
-      <c r="B101" s="218"/>
-      <c r="C101" s="219"/>
-      <c r="D101" s="161"/>
-      <c r="E101" s="145"/>
-      <c r="F101" s="133"/>
-    </row>
-    <row r="102" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="214"/>
-      <c r="B102" s="215"/>
-      <c r="C102" s="168"/>
-      <c r="D102" s="112"/>
-      <c r="E102" s="145">
-        <f t="shared" ref="E102:E103" si="18">D102*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F102" s="133">
-        <f t="shared" ref="F102:F103" si="19">D102*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="214"/>
-      <c r="B103" s="215"/>
-      <c r="C103" s="168"/>
-      <c r="D103" s="112"/>
-      <c r="E103" s="145">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="F103" s="133">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="214"/>
-      <c r="B104" s="215"/>
-      <c r="C104" s="216"/>
-      <c r="D104" s="112"/>
-      <c r="E104" s="145">
-        <f>D104*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F104" s="133">
-        <f>D104*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="211" t="s">
-        <v>29</v>
-      </c>
-      <c r="B105" s="212"/>
-      <c r="C105" s="213"/>
-      <c r="D105" s="165">
-        <f>SUM(D101:D104)</f>
-        <v>0</v>
-      </c>
-      <c r="E105" s="165">
-        <f>SUM(E101:E104)</f>
-        <v>0</v>
-      </c>
-      <c r="F105" s="165">
-        <f>SUM(F101:F104)</f>
-        <v>0</v>
-      </c>
-      <c r="H105" s="108">
-        <f>E105+F105</f>
-        <v>0</v>
-      </c>
-      <c r="I105" s="146" t="str">
-        <f>IF(D105=H105, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E107" s="108"/>
-    </row>
-    <row r="108" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="102" t="s">
+    <row r="104" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E104" s="108"/>
+    </row>
+    <row r="105" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="102" t="s">
         <v>104</v>
       </c>
-      <c r="B108" s="103">
-        <f>D92</f>
-        <v>8226649.5599999996</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="104" t="s">
+      <c r="B105" s="103">
+        <f>D89</f>
+        <v>9512420</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="104" t="s">
         <v>106</v>
       </c>
-      <c r="B109" s="105">
-        <f>D92-D90</f>
-        <v>8226649.5599999996</v>
-      </c>
+      <c r="B106" s="105">
+        <f>D89-D87</f>
+        <v>5682222.96</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D107" s="195"/>
+      <c r="E107" s="195"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="74" t="s">
+        <v>90</v>
+      </c>
+      <c r="B108" s="75"/>
+      <c r="C108" s="76"/>
+      <c r="D108" s="195"/>
+      <c r="E108" s="195"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="B109" s="11">
+        <v>-3599025.7822533529</v>
+      </c>
+      <c r="C109" s="78"/>
+      <c r="D109" s="195"/>
+      <c r="E109" s="195"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D110" s="201"/>
-      <c r="E110" s="201"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="74" t="s">
-        <v>90</v>
-      </c>
-      <c r="B111" s="75"/>
-      <c r="C111" s="76"/>
-      <c r="D111" s="201"/>
-      <c r="E111" s="201"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="B112" s="11">
-        <v>-3599025.7822533529</v>
-      </c>
-      <c r="C112" s="78"/>
-      <c r="D112" s="201"/>
-      <c r="E112" s="201"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="79" t="s">
+      <c r="A110" s="79" t="s">
         <v>92</v>
       </c>
-      <c r="B113" s="92">
+      <c r="B110" s="92">
         <f>PRORRATEO!G52</f>
         <v>8723308.1338689979</v>
       </c>
-      <c r="C113" s="78" t="s">
+      <c r="C110" s="78" t="s">
         <v>93</v>
       </c>
-      <c r="D113" s="201"/>
-      <c r="E113" s="201"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D110" s="195"/>
+      <c r="E110" s="195"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="79" t="s">
+        <v>115</v>
+      </c>
+      <c r="B111" s="169">
+        <f>-B106</f>
+        <v>-5682222.96</v>
+      </c>
+      <c r="C111" s="76"/>
+      <c r="D111" s="195"/>
+      <c r="E111" s="195"/>
+      <c r="G111" s="112"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="79" t="s">
+        <v>114</v>
+      </c>
+      <c r="B112" s="169">
+        <f>-D102</f>
+        <v>-2916310.6</v>
+      </c>
+      <c r="C112" s="76"/>
+      <c r="D112" s="195"/>
+      <c r="E112" s="195"/>
+      <c r="G112" s="124"/>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A113" s="79" t="s">
+        <v>105</v>
+      </c>
+      <c r="B113" s="169">
+        <f>-B120</f>
+        <v>-40000</v>
+      </c>
+      <c r="C113" s="80"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="79" t="s">
-        <v>115</v>
-      </c>
-      <c r="B114" s="170">
-        <f>-B109</f>
-        <v>-8226649.5599999996</v>
-      </c>
-      <c r="C114" s="76"/>
-      <c r="D114" s="201"/>
-      <c r="E114" s="201"/>
-      <c r="G114" s="112"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="79" t="s">
-        <v>114</v>
-      </c>
-      <c r="B115" s="170">
-        <f>-D105</f>
-        <v>0</v>
-      </c>
-      <c r="C115" s="76"/>
-      <c r="D115" s="201"/>
-      <c r="E115" s="201"/>
-      <c r="G115" s="124"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="79" t="s">
-        <v>105</v>
-      </c>
-      <c r="B116" s="170">
-        <f>-B123</f>
-        <v>-40000</v>
-      </c>
-      <c r="C116" s="80"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="B117" s="93">
-        <f>-C97</f>
-        <v>0</v>
-      </c>
-      <c r="C117" s="80"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="79"/>
-      <c r="B118" s="75"/>
-      <c r="C118" s="80"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="77" t="s">
+      <c r="B114" s="93">
+        <f>-C94</f>
+        <v>0</v>
+      </c>
+      <c r="C114" s="80"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A115" s="79"/>
+      <c r="B115" s="75"/>
+      <c r="C115" s="80"/>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A116" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="B119" s="81">
-        <f>SUM(B112:B118)</f>
-        <v>-3142367.2083843546</v>
-      </c>
-      <c r="C119" s="150"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="80"/>
-      <c r="C120" s="76"/>
-      <c r="D120" s="83"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C121" s="76"/>
-      <c r="D121" s="108"/>
-      <c r="E121" s="173"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="74" t="s">
+      <c r="B116" s="81">
+        <f>SUM(B109:B115)</f>
+        <v>-3514251.2083843551</v>
+      </c>
+      <c r="C116" s="150"/>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A117" s="80"/>
+      <c r="C117" s="76"/>
+      <c r="D117" s="83"/>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C118" s="76"/>
+      <c r="D118" s="108"/>
+      <c r="E118" s="172"/>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A119" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="B122" s="11">
+      <c r="B119" s="11">
         <v>-352694.54000000004</v>
       </c>
+      <c r="C119" s="82"/>
+      <c r="D119" s="172"/>
+      <c r="E119" s="172"/>
+      <c r="F119" s="172"/>
+    </row>
+    <row r="120" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="77" t="s">
+        <v>158</v>
+      </c>
+      <c r="B120" s="93">
+        <v>40000</v>
+      </c>
+      <c r="C120" s="82"/>
+      <c r="D120" s="172"/>
+      <c r="E120" s="182"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A121" s="77" t="s">
+        <v>142</v>
+      </c>
+      <c r="B121" s="169"/>
+      <c r="C121" s="82"/>
+      <c r="E121" s="108"/>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A122" s="77"/>
+      <c r="B122" s="169"/>
       <c r="C122" s="82"/>
-      <c r="D122" s="173"/>
-      <c r="E122" s="173"/>
-      <c r="F122" s="173"/>
-    </row>
-    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="77" t="s">
-        <v>158</v>
-      </c>
-      <c r="B123" s="93">
-        <v>40000</v>
+      <c r="E122" s="108"/>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A123" s="100" t="s">
+        <v>29</v>
+      </c>
+      <c r="B123" s="101">
+        <f>SUM(B119:B122)</f>
+        <v>-312694.54000000004</v>
       </c>
       <c r="C123" s="82"/>
-      <c r="D123" s="173"/>
-      <c r="E123" s="183"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124" s="77" t="s">
-        <v>142</v>
-      </c>
-      <c r="B124" s="170"/>
-      <c r="C124" s="82"/>
-      <c r="E124" s="108"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="77"/>
-      <c r="B125" s="170"/>
-      <c r="C125" s="82"/>
-      <c r="E125" s="108"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126" s="100" t="s">
-        <v>29</v>
-      </c>
-      <c r="B126" s="101">
-        <f>SUM(B122:B125)</f>
-        <v>-312694.54000000004</v>
-      </c>
-      <c r="C126" s="82"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C127" s="83"/>
-      <c r="D127" s="173"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B128" s="80"/>
-      <c r="C128" s="76"/>
-    </row>
-    <row r="130" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="N130" s="12"/>
-    </row>
-    <row r="133" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B133" s="200"/>
-      <c r="C133" s="200"/>
-      <c r="D133" s="200"/>
-      <c r="E133" s="200"/>
-    </row>
-    <row r="134" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B134" s="200"/>
-      <c r="C134" s="200"/>
-      <c r="D134" s="200"/>
-      <c r="E134" s="200"/>
-    </row>
-    <row r="135" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B135" s="200"/>
-      <c r="C135" s="200"/>
-      <c r="D135" s="200"/>
-      <c r="E135" s="200"/>
-    </row>
-    <row r="136" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B136" s="200"/>
-      <c r="C136" s="200"/>
-      <c r="D136" s="200"/>
-      <c r="E136" s="200"/>
-    </row>
-    <row r="137" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B137" s="200"/>
-      <c r="C137" s="200"/>
-      <c r="D137" s="200"/>
-      <c r="E137" s="200"/>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C124" s="83"/>
+      <c r="D124" s="172"/>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B125" s="80"/>
+      <c r="C125" s="76"/>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N127" s="12"/>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B130" s="194"/>
+      <c r="C130" s="194"/>
+      <c r="D130" s="194"/>
+      <c r="E130" s="194"/>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B131" s="194"/>
+      <c r="C131" s="194"/>
+      <c r="D131" s="194"/>
+      <c r="E131" s="194"/>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B132" s="194"/>
+      <c r="C132" s="194"/>
+      <c r="D132" s="194"/>
+      <c r="E132" s="194"/>
+    </row>
+    <row r="133" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B133" s="194"/>
+      <c r="C133" s="194"/>
+      <c r="D133" s="194"/>
+      <c r="E133" s="194"/>
+    </row>
+    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B134" s="194"/>
+      <c r="C134" s="194"/>
+      <c r="D134" s="194"/>
+      <c r="E134" s="194"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="11">
+    <mergeCell ref="B130:E134"/>
+    <mergeCell ref="D107:E112"/>
+    <mergeCell ref="B14:D17"/>
+    <mergeCell ref="A102:C102"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A61:C61"/>
     <mergeCell ref="A59:C59"/>
-    <mergeCell ref="B133:E137"/>
-    <mergeCell ref="D110:E115"/>
-    <mergeCell ref="B14:D17"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="A104:C104"/>
-    <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A100:D100"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="A102:B102"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A62:C62"/>
     <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A99:C99"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4135,15 +4075,15 @@
       <c r="K1" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="L1" s="225">
-        <f>RESUMEN!D92</f>
-        <v>8226649.5599999996</v>
-      </c>
-      <c r="M1" s="226"/>
+      <c r="L1" s="217">
+        <f>RESUMEN!D89</f>
+        <v>9512420</v>
+      </c>
+      <c r="M1" s="218"/>
       <c r="N1" s="148"/>
       <c r="O1" s="134">
         <f>L1*8.09%</f>
-        <v>665535.94940399996</v>
+        <v>769554.77800000005</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -4162,13 +4102,13 @@
       </c>
       <c r="L2" s="8"/>
       <c r="M2" s="148">
-        <f>7519700+7519700*10%</f>
-        <v>8271670</v>
+        <f>8271670+8271670*15%+49000+4000-276</f>
+        <v>9565144.5</v>
       </c>
       <c r="N2" s="149"/>
       <c r="O2" s="134">
         <f>O1-K7-553-50-86-8</f>
-        <v>50169.291635000031</v>
+        <v>47762.100000000093</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -4190,8 +4130,8 @@
       </c>
       <c r="L3" s="8"/>
       <c r="M3" s="127">
-        <f>RESUMEN!D105</f>
-        <v>0</v>
+        <f>RESUMEN!D102</f>
+        <v>2916310.6</v>
       </c>
       <c r="N3" s="147"/>
       <c r="O3" s="73"/>
@@ -4215,69 +4155,70 @@
       </c>
       <c r="L4" s="8"/>
       <c r="M4" s="127">
-        <v>0</v>
+        <f>3175000-2000+7</f>
+        <v>3173007</v>
       </c>
       <c r="N4" s="123"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="222" t="s">
+      <c r="A5" s="210" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="236" t="s">
+      <c r="B5" s="212" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="222" t="s">
+      <c r="C5" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="234" t="s">
+      <c r="D5" s="214" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="222" t="s">
+      <c r="E5" s="210" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="222" t="s">
+      <c r="F5" s="210" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="222" t="s">
+      <c r="G5" s="210" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="229" t="s">
+      <c r="H5" s="221" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="234" t="s">
+      <c r="I5" s="214" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="227" t="s">
+      <c r="J5" s="219" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="227" t="s">
+      <c r="K5" s="219" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="232" t="s">
+      <c r="L5" s="224" t="s">
         <v>123</v>
       </c>
-      <c r="M5" s="227" t="s">
+      <c r="M5" s="219" t="s">
         <v>67</v>
       </c>
-      <c r="N5" s="227" t="s">
+      <c r="N5" s="219" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="223"/>
-      <c r="B6" s="237"/>
-      <c r="C6" s="223"/>
-      <c r="D6" s="238"/>
-      <c r="E6" s="223"/>
-      <c r="F6" s="223"/>
-      <c r="G6" s="223"/>
-      <c r="H6" s="230"/>
-      <c r="I6" s="235"/>
-      <c r="J6" s="228"/>
-      <c r="K6" s="231"/>
-      <c r="L6" s="233"/>
-      <c r="M6" s="231"/>
-      <c r="N6" s="228"/>
+      <c r="A6" s="211"/>
+      <c r="B6" s="213"/>
+      <c r="C6" s="211"/>
+      <c r="D6" s="215"/>
+      <c r="E6" s="211"/>
+      <c r="F6" s="211"/>
+      <c r="G6" s="211"/>
+      <c r="H6" s="222"/>
+      <c r="I6" s="226"/>
+      <c r="J6" s="220"/>
+      <c r="K6" s="223"/>
+      <c r="L6" s="225"/>
+      <c r="M6" s="223"/>
+      <c r="N6" s="220"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -4296,7 +4237,7 @@
       <c r="F7" s="88">
         <v>614669.65776899992</v>
       </c>
-      <c r="G7" s="196">
+      <c r="G7" s="241">
         <f>F7</f>
         <v>614669.65776899992</v>
       </c>
@@ -4307,20 +4248,22 @@
       <c r="I7" s="106">
         <v>12</v>
       </c>
-      <c r="J7" s="88"/>
+      <c r="J7" s="88">
+        <v>235929.52754000001</v>
+      </c>
       <c r="K7" s="88">
-        <v>614669.65776899992</v>
+        <v>721095.67799999996</v>
       </c>
       <c r="L7" s="98">
         <v>0</v>
       </c>
       <c r="M7" s="6">
         <f>K7+J7+H7+L7</f>
-        <v>614669.65776899992</v>
+        <v>957025.20554</v>
       </c>
       <c r="N7" s="11">
         <f>M7*6% + M7</f>
-        <v>651549.83723513992</v>
+        <v>1014446.7178724</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -4340,7 +4283,7 @@
       <c r="F8" s="88">
         <v>181048.12201451589</v>
       </c>
-      <c r="G8" s="196">
+      <c r="G8" s="241">
         <v>180000</v>
       </c>
       <c r="H8" s="130">
@@ -4352,11 +4295,11 @@
       </c>
       <c r="J8" s="88">
         <f>M$4*E8%</f>
-        <v>0</v>
+        <v>70123.454699999987</v>
       </c>
       <c r="K8" s="88">
         <f>M$2*E8 /100</f>
-        <v>182803.90700000001</v>
+        <v>211389.69344999999</v>
       </c>
       <c r="L8" s="160">
         <f>J$3*E8%+J$4</f>
@@ -4364,11 +4307,11 @@
       </c>
       <c r="M8" s="6">
         <f>K8+J8+H8+L8</f>
-        <v>183852.02901451589</v>
+        <v>282561.27016451582</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" ref="N8:N51" si="1">M8*6% + M8</f>
-        <v>194883.15075538686</v>
+        <v>299514.94637438678</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -4388,7 +4331,7 @@
       <c r="F9" s="88">
         <v>348817.05528426333</v>
       </c>
-      <c r="G9" s="195">
+      <c r="G9" s="242">
         <f>392904-G34</f>
         <v>348236.98199999996</v>
       </c>
@@ -4401,11 +4344,11 @@
       </c>
       <c r="J9" s="88">
         <f t="shared" ref="J9:J51" si="2">M$4*E9%</f>
-        <v>0</v>
+        <v>133583.59469999999</v>
       </c>
       <c r="K9" s="88">
         <f t="shared" ref="K9:K51" si="3">M$2*E9 /100</f>
-        <v>348237.30700000003</v>
+        <v>402692.58344999998</v>
       </c>
       <c r="L9" s="160">
         <f t="shared" ref="L9:L50" si="4">J$3*E9%+J$4</f>
@@ -4413,11 +4356,11 @@
       </c>
       <c r="M9" s="6">
         <f t="shared" ref="M9:M51" si="5">K9+J9+H9+L9</f>
-        <v>348817.3802842634</v>
+        <v>536856.25143426331</v>
       </c>
       <c r="N9" s="11">
         <f t="shared" si="1"/>
-        <v>369746.42310131923</v>
+        <v>569067.62652031914</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -4437,7 +4380,7 @@
       <c r="F10" s="88">
         <v>279110.11420596868</v>
       </c>
-      <c r="G10" s="196">
+      <c r="G10" s="241">
         <v>213555</v>
       </c>
       <c r="H10" s="130">
@@ -4449,11 +4392,11 @@
       </c>
       <c r="J10" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>90113.398799999995</v>
       </c>
       <c r="K10" s="88">
         <f t="shared" si="3"/>
-        <v>234915.42799999996</v>
+        <v>271650.10379999998</v>
       </c>
       <c r="L10" s="160">
         <f t="shared" si="4"/>
@@ -4461,11 +4404,11 @@
       </c>
       <c r="M10" s="6">
         <f t="shared" si="5"/>
-        <v>300470.54220596864</v>
+        <v>427318.61680596869</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="1"/>
-        <v>318498.77473832679</v>
+        <v>452957.73381432681</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -4485,7 +4428,7 @@
       <c r="F11" s="88">
         <v>283718.28100000002</v>
       </c>
-      <c r="G11" s="196">
+      <c r="G11" s="241">
         <f>F11</f>
         <v>283718.28100000002</v>
       </c>
@@ -4498,11 +4441,11 @@
       </c>
       <c r="J11" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>108834.14010000002</v>
       </c>
       <c r="K11" s="88">
         <f t="shared" si="3"/>
-        <v>283718.28100000002</v>
+        <v>328084.45634999999</v>
       </c>
       <c r="L11" s="160">
         <f t="shared" si="4"/>
@@ -4510,11 +4453,11 @@
       </c>
       <c r="M11" s="6">
         <f t="shared" si="5"/>
-        <v>283718.28100000002</v>
+        <v>436918.59645000001</v>
       </c>
       <c r="N11" s="11">
         <f t="shared" si="1"/>
-        <v>300741.37786000001</v>
+        <v>463133.712237</v>
       </c>
       <c r="P11" s="108"/>
     </row>
@@ -4535,7 +4478,7 @@
       <c r="F12" s="88">
         <v>234915.42799999996</v>
       </c>
-      <c r="G12" s="195">
+      <c r="G12" s="242">
         <f>F12</f>
         <v>234915.42799999996</v>
       </c>
@@ -4548,11 +4491,11 @@
       </c>
       <c r="J12" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>90113.398799999995</v>
       </c>
       <c r="K12" s="88">
         <f t="shared" si="3"/>
-        <v>234915.42799999996</v>
+        <v>271650.10379999998</v>
       </c>
       <c r="L12" s="160">
         <f t="shared" si="4"/>
@@ -4560,11 +4503,11 @@
       </c>
       <c r="M12" s="6">
         <f t="shared" si="5"/>
-        <v>234915.42799999996</v>
+        <v>361763.50260000001</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="1"/>
-        <v>249010.35367999994</v>
+        <v>383469.31275600003</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -4584,7 +4527,7 @@
       <c r="F13" s="88">
         <v>283718.82411924173</v>
       </c>
-      <c r="G13" s="195">
+      <c r="G13" s="242">
         <f>332521-G50</f>
         <v>283718.147</v>
       </c>
@@ -4597,23 +4540,22 @@
       </c>
       <c r="J13" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>108834.14010000002</v>
       </c>
       <c r="K13" s="88">
         <f t="shared" si="3"/>
-        <v>283718.28100000002</v>
+        <v>328084.45634999999</v>
       </c>
       <c r="L13" s="160">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="M13" s="6">
         <f t="shared" si="5"/>
-        <v>283718.95811924175</v>
+        <v>446919.27356924175</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="1"/>
-        <v>300742.09560639627</v>
+        <v>473734.42998339626</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -4633,7 +4575,7 @@
       <c r="F14" s="88">
         <v>258710.39332799998</v>
       </c>
-      <c r="G14" s="196">
+      <c r="G14" s="241">
         <v>234915</v>
       </c>
       <c r="H14" s="130">
@@ -4645,23 +4587,23 @@
       </c>
       <c r="J14" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>90113.398799999995</v>
       </c>
       <c r="K14" s="88">
         <f t="shared" si="3"/>
-        <v>234915.42799999996</v>
-      </c>
-      <c r="L14" s="247">
+        <v>271650.10379999998</v>
+      </c>
+      <c r="L14" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M14" s="6">
         <f t="shared" si="5"/>
-        <v>258710.82132799993</v>
+        <v>385558.89592799998</v>
       </c>
       <c r="N14" s="11">
         <f t="shared" si="1"/>
-        <v>274233.47060767992</v>
+        <v>408692.42968368001</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -4681,7 +4623,7 @@
       <c r="F15" s="88">
         <v>283718.16704653396</v>
       </c>
-      <c r="G15" s="195">
+      <c r="G15" s="242">
         <f>325076-G35</f>
         <v>283717.65000000002</v>
       </c>
@@ -4694,23 +4636,23 @@
       </c>
       <c r="J15" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>108834.14010000002</v>
       </c>
       <c r="K15" s="88">
         <f t="shared" si="3"/>
-        <v>283718.28100000002</v>
-      </c>
-      <c r="L15" s="247">
+        <v>328084.45634999999</v>
+      </c>
+      <c r="L15" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M15" s="6">
         <f t="shared" si="5"/>
-        <v>283718.79804653395</v>
+        <v>436919.11349653394</v>
       </c>
       <c r="N15" s="11">
         <f t="shared" si="1"/>
-        <v>300741.92592932598</v>
+        <v>463134.26030632597</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -4730,7 +4672,7 @@
       <c r="F16" s="88">
         <v>280282</v>
       </c>
-      <c r="G16" s="195">
+      <c r="G16" s="242">
         <f>275546+45267-G49</f>
         <v>280281.81699999998</v>
       </c>
@@ -4743,23 +4685,23 @@
       </c>
       <c r="J16" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>90113.398799999995</v>
       </c>
       <c r="K16" s="88">
         <f t="shared" si="3"/>
-        <v>234915.42799999996</v>
-      </c>
-      <c r="L16" s="247">
+        <v>271650.10379999998</v>
+      </c>
+      <c r="L16" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M16" s="6">
         <f t="shared" si="5"/>
-        <v>234915.61099999998</v>
+        <v>361763.68560000003</v>
       </c>
       <c r="N16" s="11">
         <f t="shared" si="1"/>
-        <v>249010.54765999998</v>
+        <v>383469.50673600001</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -4779,7 +4721,7 @@
       <c r="F17" s="88">
         <v>293717.14471111476</v>
       </c>
-      <c r="G17" s="196">
+      <c r="G17" s="241">
         <f>375606+1-G47-G48</f>
         <v>293717.467</v>
       </c>
@@ -4792,23 +4734,22 @@
       </c>
       <c r="J17" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>108834.14010000002</v>
       </c>
       <c r="K17" s="88">
         <f t="shared" si="3"/>
-        <v>283718.28100000002</v>
-      </c>
-      <c r="L17" s="247">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>328084.45634999999</v>
+      </c>
+      <c r="L17" s="160">
+        <v>10000</v>
       </c>
       <c r="M17" s="6">
         <f t="shared" si="5"/>
-        <v>283717.95871111477</v>
+        <v>446918.27416111476</v>
       </c>
       <c r="N17" s="11">
         <f t="shared" si="1"/>
-        <v>300741.03623378166</v>
+        <v>473733.37061078165</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -4828,7 +4769,7 @@
       <c r="F18" s="88">
         <v>231604.94198325131</v>
       </c>
-      <c r="G18" s="196">
+      <c r="G18" s="241">
         <f>112000+160000+8000-G51</f>
         <v>232851.481</v>
       </c>
@@ -4841,23 +4782,23 @@
       </c>
       <c r="J18" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>90113.398799999995</v>
       </c>
       <c r="K18" s="88">
         <f t="shared" si="3"/>
-        <v>234915.42799999996</v>
-      </c>
-      <c r="L18" s="247">
+        <v>271650.10379999998</v>
+      </c>
+      <c r="L18" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M18" s="6">
         <f t="shared" si="5"/>
-        <v>233668.88898325127</v>
+        <v>360516.96358325134</v>
       </c>
       <c r="N18" s="11">
         <f t="shared" si="1"/>
-        <v>247689.02232224634</v>
+        <v>382147.98139824643</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -4877,7 +4818,7 @@
       <c r="F19" s="88">
         <v>283718.85376516799</v>
       </c>
-      <c r="G19" s="195">
+      <c r="G19" s="242">
         <f>328385-G41</f>
         <v>283717.98199999996</v>
       </c>
@@ -4890,23 +4831,23 @@
       </c>
       <c r="J19" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>108834.14010000002</v>
       </c>
       <c r="K19" s="88">
         <f t="shared" si="3"/>
-        <v>283718.28100000002</v>
-      </c>
-      <c r="L19" s="247">
+        <v>328084.45634999999</v>
+      </c>
+      <c r="L19" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M19" s="6">
         <f t="shared" si="5"/>
-        <v>283719.15276516805</v>
+        <v>436919.46821516805</v>
       </c>
       <c r="N19" s="11">
         <f t="shared" si="1"/>
-        <v>300742.30193107814</v>
+        <v>463134.63630807813</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -4926,7 +4867,7 @@
       <c r="F20" s="88">
         <v>246161.02790707469</v>
       </c>
-      <c r="G20" s="196">
+      <c r="G20" s="241">
         <f>275446-G38</f>
         <v>234914.81700000001</v>
       </c>
@@ -4939,23 +4880,23 @@
       </c>
       <c r="J20" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>90113.398799999995</v>
       </c>
       <c r="K20" s="88">
         <f t="shared" si="3"/>
-        <v>234915.42799999996</v>
-      </c>
-      <c r="L20" s="247">
+        <v>271650.10379999998</v>
+      </c>
+      <c r="L20" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M20" s="6">
         <f t="shared" si="5"/>
-        <v>246161.63890707464</v>
+        <v>373009.71350707469</v>
       </c>
       <c r="N20" s="11">
         <f t="shared" si="1"/>
-        <v>260931.3372414991</v>
+        <v>395390.29631749919</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -4975,7 +4916,7 @@
       <c r="F21" s="88">
         <v>283718.25609179586</v>
       </c>
-      <c r="G21" s="196">
+      <c r="G21" s="241">
         <f>328385-G45</f>
         <v>283717.98199999996</v>
       </c>
@@ -4988,23 +4929,23 @@
       </c>
       <c r="J21" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>108834.14010000002</v>
       </c>
       <c r="K21" s="88">
         <f t="shared" si="3"/>
-        <v>283718.28100000002</v>
-      </c>
-      <c r="L21" s="247">
+        <v>328084.45634999999</v>
+      </c>
+      <c r="L21" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M21" s="6">
         <f t="shared" si="5"/>
-        <v>283718.55509179592</v>
+        <v>436918.87054179591</v>
       </c>
       <c r="N21" s="11">
         <f t="shared" si="1"/>
-        <v>300741.66839730367</v>
+        <v>463134.00277430366</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -5024,7 +4965,7 @@
       <c r="F22" s="88">
         <v>254915.42799999996</v>
       </c>
-      <c r="G22" s="196">
+      <c r="G22" s="241">
         <f>F22</f>
         <v>254915.42799999996</v>
       </c>
@@ -5037,23 +4978,23 @@
       </c>
       <c r="J22" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>90113.398799999995</v>
       </c>
       <c r="K22" s="88">
         <f t="shared" si="3"/>
-        <v>234915.42799999996</v>
-      </c>
-      <c r="L22" s="247">
+        <v>271650.10379999998</v>
+      </c>
+      <c r="L22" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M22" s="6">
         <f t="shared" si="5"/>
-        <v>234915.42799999996</v>
+        <v>361763.50260000001</v>
       </c>
       <c r="N22" s="11">
         <f t="shared" si="1"/>
-        <v>249010.35367999994</v>
+        <v>383469.31275600003</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -5073,7 +5014,7 @@
       <c r="F23" s="88">
         <v>309550.97053314082</v>
       </c>
-      <c r="G23" s="195">
+      <c r="G23" s="242">
         <f>334000-G46</f>
         <v>290160.14899999998</v>
       </c>
@@ -5086,23 +5027,22 @@
       </c>
       <c r="J23" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>108834.14010000002</v>
       </c>
       <c r="K23" s="88">
         <f t="shared" si="3"/>
-        <v>283718.28100000002</v>
-      </c>
-      <c r="L23" s="247">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>328084.45634999999</v>
+      </c>
+      <c r="L23" s="160">
+        <v>10000</v>
       </c>
       <c r="M23" s="6">
         <f t="shared" si="5"/>
-        <v>303109.10253314086</v>
+        <v>466309.41798314085</v>
       </c>
       <c r="N23" s="11">
         <f t="shared" si="1"/>
-        <v>321295.6486851293</v>
+        <v>494287.98306212929</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -5122,7 +5062,7 @@
       <c r="F24" s="88">
         <v>233406.74547107471</v>
       </c>
-      <c r="G24" s="196">
+      <c r="G24" s="241">
         <f>266000+14000-G37</f>
         <v>239468.81700000001</v>
       </c>
@@ -5130,28 +5070,27 @@
         <f t="shared" si="0"/>
         <v>-6062.0715289252985</v>
       </c>
-      <c r="I24" s="174">
+      <c r="I24" s="173">
         <v>6</v>
       </c>
       <c r="J24" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>90113.398799999995</v>
       </c>
       <c r="K24" s="88">
         <f t="shared" si="3"/>
-        <v>234915.42799999996</v>
-      </c>
-      <c r="L24" s="247">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>271650.10379999998</v>
+      </c>
+      <c r="L24" s="160">
+        <v>10000</v>
       </c>
       <c r="M24" s="6">
         <f t="shared" si="5"/>
-        <v>228853.35647107466</v>
+        <v>365701.43107107468</v>
       </c>
       <c r="N24" s="11">
         <f t="shared" si="1"/>
-        <v>242584.55785933914</v>
+        <v>387643.51693533914</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -5171,7 +5110,7 @@
       <c r="F25" s="88">
         <v>322090.1091</v>
       </c>
-      <c r="G25" s="196">
+      <c r="G25" s="241">
         <f>F25</f>
         <v>322090.1091</v>
       </c>
@@ -5184,23 +5123,23 @@
       </c>
       <c r="J25" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>108834.14010000002</v>
       </c>
       <c r="K25" s="88">
         <f t="shared" si="3"/>
-        <v>283718.28100000002</v>
-      </c>
-      <c r="L25" s="247">
+        <v>328084.45634999999</v>
+      </c>
+      <c r="L25" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M25" s="6">
         <f t="shared" si="5"/>
-        <v>283718.28100000002</v>
+        <v>436918.59645000001</v>
       </c>
       <c r="N25" s="11">
         <f t="shared" si="1"/>
-        <v>300741.37786000001</v>
+        <v>463133.712237</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -5220,7 +5159,7 @@
       <c r="F26" s="88">
         <v>496299.97081603704</v>
       </c>
-      <c r="G26" s="195">
+      <c r="G26" s="242">
         <f>676478.23-G30-G31-G36</f>
         <v>544958.67700000003</v>
       </c>
@@ -5233,23 +5172,23 @@
       </c>
       <c r="J26" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>190380.41999999998</v>
       </c>
       <c r="K26" s="88">
         <f t="shared" si="3"/>
-        <v>496300.2</v>
-      </c>
-      <c r="L26" s="247">
+        <v>573908.67000000004</v>
+      </c>
+      <c r="L26" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M26" s="6">
         <f t="shared" si="5"/>
-        <v>447641.49381603702</v>
+        <v>715630.38381603709</v>
       </c>
       <c r="N26" s="11">
         <f t="shared" si="1"/>
-        <v>474499.98344499926</v>
+        <v>758568.20684499934</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -5269,7 +5208,7 @@
       <c r="F27" s="88">
         <v>490962.31853526551</v>
       </c>
-      <c r="G27" s="196">
+      <c r="G27" s="241">
         <f>586914-G39-G40</f>
         <v>490962.62800000003</v>
       </c>
@@ -5282,23 +5221,23 @@
       </c>
       <c r="J27" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>186890.11229999998</v>
       </c>
       <c r="K27" s="88">
         <f t="shared" si="3"/>
-        <v>487201.36299999995</v>
-      </c>
-      <c r="L27" s="247">
+        <v>563387.01104999997</v>
+      </c>
+      <c r="L27" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M27" s="6">
         <f t="shared" si="5"/>
-        <v>487201.05353526544</v>
+        <v>750276.8138852655</v>
       </c>
       <c r="N27" s="11">
         <f t="shared" si="1"/>
-        <v>516433.11674738134</v>
+        <v>795293.42271838139</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -5318,7 +5257,7 @@
       <c r="F28" s="88">
         <v>510253.2765765409</v>
       </c>
-      <c r="G28" s="196">
+      <c r="G28" s="241">
         <f>598000-G32-G33</f>
         <v>510320.29799999995</v>
       </c>
@@ -5331,23 +5270,23 @@
       </c>
       <c r="J28" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>186890.11229999998</v>
       </c>
       <c r="K28" s="88">
         <f t="shared" si="3"/>
-        <v>487201.36299999995</v>
-      </c>
-      <c r="L28" s="247">
+        <v>563387.01104999997</v>
+      </c>
+      <c r="L28" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M28" s="6">
         <f t="shared" si="5"/>
-        <v>487134.3415765409</v>
+        <v>750210.10192654096</v>
       </c>
       <c r="N28" s="11">
         <f t="shared" si="1"/>
-        <v>516362.40207113337</v>
+        <v>795222.70804213337</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -5367,7 +5306,7 @@
       <c r="F29" s="88">
         <v>815269.4544566999</v>
       </c>
-      <c r="G29" s="195">
+      <c r="G29" s="242">
         <f>950000-G42-G43-G44</f>
         <v>816826.1129999999</v>
       </c>
@@ -5380,23 +5319,23 @@
       </c>
       <c r="J29" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>186890.11229999998</v>
       </c>
       <c r="K29" s="88">
         <f t="shared" si="3"/>
-        <v>487201.36299999995</v>
-      </c>
-      <c r="L29" s="247">
+        <v>563387.01104999997</v>
+      </c>
+      <c r="L29" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M29" s="6">
         <f t="shared" si="5"/>
-        <v>485644.70445669995</v>
+        <v>748720.46480670001</v>
       </c>
       <c r="N29" s="11">
         <f t="shared" si="1"/>
-        <v>514783.38672410196</v>
+        <v>793643.69269510196</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -5416,7 +5355,7 @@
       <c r="F30" s="88">
         <v>44667.018000000011</v>
       </c>
-      <c r="G30" s="196">
+      <c r="G30" s="241">
         <f t="shared" ref="G30:G34" si="6">F30</f>
         <v>44667.018000000011</v>
       </c>
@@ -5427,23 +5366,23 @@
       <c r="I30" s="106"/>
       <c r="J30" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>17134.237800000003</v>
       </c>
       <c r="K30" s="88">
         <f t="shared" si="3"/>
-        <v>44667.018000000011</v>
-      </c>
-      <c r="L30" s="247">
+        <v>51651.780300000006</v>
+      </c>
+      <c r="L30" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M30" s="6">
         <f t="shared" si="5"/>
-        <v>44667.018000000011</v>
+        <v>68786.018100000016</v>
       </c>
       <c r="N30" s="11">
         <f t="shared" si="1"/>
-        <v>47347.03908000001</v>
+        <v>72913.179186000023</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -5463,7 +5402,7 @@
       <c r="F31" s="88">
         <v>45494.184999999998</v>
       </c>
-      <c r="G31" s="196">
+      <c r="G31" s="241">
         <f t="shared" si="6"/>
         <v>45494.184999999998</v>
       </c>
@@ -5474,23 +5413,23 @@
       <c r="I31" s="106"/>
       <c r="J31" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>17451.538500000002</v>
       </c>
       <c r="K31" s="88">
         <f t="shared" si="3"/>
-        <v>45494.184999999998</v>
-      </c>
-      <c r="L31" s="247">
+        <v>52608.294750000008</v>
+      </c>
+      <c r="L31" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M31" s="6">
         <f t="shared" si="5"/>
-        <v>45494.184999999998</v>
+        <v>70059.833250000011</v>
       </c>
       <c r="N31" s="11">
         <f t="shared" si="1"/>
-        <v>48223.8361</v>
+        <v>74263.423245000013</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -5510,7 +5449,7 @@
       <c r="F32" s="88">
         <v>37222.514999999999</v>
       </c>
-      <c r="G32" s="196">
+      <c r="G32" s="241">
         <f>F32</f>
         <v>37222.514999999999</v>
       </c>
@@ -5521,23 +5460,23 @@
       <c r="I32" s="106"/>
       <c r="J32" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>14278.531500000001</v>
       </c>
       <c r="K32" s="88">
         <f t="shared" si="3"/>
-        <v>37222.514999999999</v>
-      </c>
-      <c r="L32" s="247">
+        <v>43043.150250000006</v>
+      </c>
+      <c r="L32" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M32" s="6">
         <f t="shared" si="5"/>
-        <v>37222.514999999999</v>
+        <v>57321.681750000003</v>
       </c>
       <c r="N32" s="11">
         <f t="shared" si="1"/>
-        <v>39455.865899999997</v>
+        <v>60760.982655</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -5557,7 +5496,7 @@
       <c r="F33" s="88">
         <v>50457.187000000005</v>
       </c>
-      <c r="G33" s="196">
+      <c r="G33" s="241">
         <f t="shared" si="6"/>
         <v>50457.187000000005</v>
       </c>
@@ -5568,23 +5507,23 @@
       <c r="I33" s="106"/>
       <c r="J33" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>19355.342699999997</v>
       </c>
       <c r="K33" s="88">
         <f t="shared" si="3"/>
-        <v>50457.187000000005</v>
-      </c>
-      <c r="L33" s="247">
+        <v>58347.381449999993</v>
+      </c>
+      <c r="L33" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M33" s="6">
         <f t="shared" si="5"/>
-        <v>50457.187000000005</v>
+        <v>77702.724149999995</v>
       </c>
       <c r="N33" s="11">
         <f t="shared" si="1"/>
-        <v>53484.618220000004</v>
+        <v>82364.887598999994</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -5604,7 +5543,7 @@
       <c r="F34" s="88">
         <v>44667.018000000011</v>
       </c>
-      <c r="G34" s="196">
+      <c r="G34" s="241">
         <f t="shared" si="6"/>
         <v>44667.018000000011</v>
       </c>
@@ -5615,23 +5554,23 @@
       <c r="I34" s="106"/>
       <c r="J34" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>17134.237800000003</v>
       </c>
       <c r="K34" s="88">
         <f t="shared" si="3"/>
-        <v>44667.018000000011</v>
-      </c>
-      <c r="L34" s="247">
+        <v>51651.780300000006</v>
+      </c>
+      <c r="L34" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M34" s="6">
         <f t="shared" si="5"/>
-        <v>44667.018000000011</v>
+        <v>68786.018100000016</v>
       </c>
       <c r="N34" s="11">
         <f t="shared" si="1"/>
-        <v>47347.03908000001</v>
+        <v>72913.179186000023</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -5651,7 +5590,7 @@
       <c r="F35" s="11">
         <v>41358.35</v>
       </c>
-      <c r="G35" s="195">
+      <c r="G35" s="242">
         <f>F35</f>
         <v>41358.35</v>
       </c>
@@ -5662,23 +5601,23 @@
       <c r="I35" s="106"/>
       <c r="J35" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15865.035</v>
       </c>
       <c r="K35" s="88">
         <f t="shared" si="3"/>
-        <v>41358.35</v>
-      </c>
-      <c r="L35" s="247">
+        <v>47825.722500000003</v>
+      </c>
+      <c r="L35" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M35" s="6">
         <f t="shared" si="5"/>
-        <v>41358.35</v>
+        <v>63690.757500000007</v>
       </c>
       <c r="N35" s="11">
         <f t="shared" si="1"/>
-        <v>43839.850999999995</v>
+        <v>67512.202950000006</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -5698,7 +5637,7 @@
       <c r="F36" s="88">
         <v>41358.35</v>
       </c>
-      <c r="G36" s="196">
+      <c r="G36" s="241">
         <f t="shared" ref="G36:G41" si="7">F36</f>
         <v>41358.35</v>
       </c>
@@ -5709,23 +5648,23 @@
       <c r="I36" s="106"/>
       <c r="J36" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15865.035</v>
       </c>
       <c r="K36" s="88">
         <f t="shared" si="3"/>
-        <v>41358.35</v>
-      </c>
-      <c r="L36" s="247">
+        <v>47825.722500000003</v>
+      </c>
+      <c r="L36" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M36" s="6">
         <f t="shared" si="5"/>
-        <v>41358.35</v>
+        <v>63690.757500000007</v>
       </c>
       <c r="N36" s="11">
         <f t="shared" si="1"/>
-        <v>43839.850999999995</v>
+        <v>67512.202950000006</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -5745,7 +5684,7 @@
       <c r="F37" s="88">
         <v>40531.182999999997</v>
       </c>
-      <c r="G37" s="196">
+      <c r="G37" s="241">
         <f t="shared" si="7"/>
         <v>40531.182999999997</v>
       </c>
@@ -5756,23 +5695,23 @@
       <c r="I37" s="106"/>
       <c r="J37" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15547.7343</v>
       </c>
       <c r="K37" s="88">
         <f t="shared" si="3"/>
-        <v>40531.182999999997</v>
-      </c>
-      <c r="L37" s="247">
+        <v>46869.208049999994</v>
+      </c>
+      <c r="L37" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M37" s="6">
         <f t="shared" si="5"/>
-        <v>40531.182999999997</v>
+        <v>62416.942349999998</v>
       </c>
       <c r="N37" s="11">
         <f t="shared" si="1"/>
-        <v>42963.053979999997</v>
+        <v>66161.958891000002</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -5792,7 +5731,7 @@
       <c r="F38" s="88">
         <v>40531.182999999997</v>
       </c>
-      <c r="G38" s="196">
+      <c r="G38" s="241">
         <f t="shared" si="7"/>
         <v>40531.182999999997</v>
       </c>
@@ -5803,23 +5742,23 @@
       <c r="I38" s="106"/>
       <c r="J38" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15547.7343</v>
       </c>
       <c r="K38" s="88">
         <f t="shared" si="3"/>
-        <v>40531.182999999997</v>
-      </c>
-      <c r="L38" s="247">
+        <v>46869.208049999994</v>
+      </c>
+      <c r="L38" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M38" s="6">
         <f t="shared" si="5"/>
-        <v>40531.182999999997</v>
+        <v>62416.942349999998</v>
       </c>
       <c r="N38" s="11">
         <f t="shared" si="1"/>
-        <v>42963.053979999997</v>
+        <v>66161.958891000002</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -5839,7 +5778,7 @@
       <c r="F39" s="88">
         <v>48802.852999999996</v>
       </c>
-      <c r="G39" s="196">
+      <c r="G39" s="241">
         <f t="shared" si="7"/>
         <v>48802.852999999996</v>
       </c>
@@ -5850,23 +5789,23 @@
       <c r="I39" s="106"/>
       <c r="J39" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>18720.741299999998</v>
       </c>
       <c r="K39" s="88">
         <f t="shared" si="3"/>
-        <v>48802.852999999996</v>
-      </c>
-      <c r="L39" s="247">
+        <v>56434.352549999996</v>
+      </c>
+      <c r="L39" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M39" s="6">
         <f t="shared" si="5"/>
-        <v>48802.852999999996</v>
+        <v>75155.09384999999</v>
       </c>
       <c r="N39" s="11">
         <f t="shared" si="1"/>
-        <v>51731.024179999993</v>
+        <v>79664.399480999986</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -5886,7 +5825,7 @@
       <c r="F40" s="88">
         <v>47148.518999999993</v>
       </c>
-      <c r="G40" s="196">
+      <c r="G40" s="241">
         <f t="shared" si="7"/>
         <v>47148.518999999993</v>
       </c>
@@ -5897,23 +5836,23 @@
       <c r="I40" s="106"/>
       <c r="J40" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>18086.139899999998</v>
       </c>
       <c r="K40" s="88">
         <f t="shared" si="3"/>
-        <v>47148.518999999993</v>
-      </c>
-      <c r="L40" s="247">
+        <v>54521.323649999991</v>
+      </c>
+      <c r="L40" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M40" s="6">
         <f t="shared" si="5"/>
-        <v>47148.518999999993</v>
+        <v>72607.463549999986</v>
       </c>
       <c r="N40" s="11">
         <f t="shared" si="1"/>
-        <v>49977.430139999989</v>
+        <v>76963.911362999992</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -5933,7 +5872,7 @@
       <c r="F41" s="88">
         <v>44667.018000000011</v>
       </c>
-      <c r="G41" s="196">
+      <c r="G41" s="241">
         <f t="shared" si="7"/>
         <v>44667.018000000011</v>
       </c>
@@ -5944,23 +5883,23 @@
       <c r="I41" s="106"/>
       <c r="J41" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>17134.237800000003</v>
       </c>
       <c r="K41" s="88">
         <f t="shared" si="3"/>
-        <v>44667.018000000011</v>
-      </c>
-      <c r="L41" s="247">
+        <v>51651.780300000006</v>
+      </c>
+      <c r="L41" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="5"/>
-        <v>44667.018000000011</v>
+        <v>68786.018100000016</v>
       </c>
       <c r="N41" s="11">
         <f t="shared" si="1"/>
-        <v>47347.03908000001</v>
+        <v>72913.179186000023</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -5980,7 +5919,7 @@
       <c r="F42" s="88">
         <v>45494.184999999998</v>
       </c>
-      <c r="G42" s="196">
+      <c r="G42" s="241">
         <f>F42</f>
         <v>45494.184999999998</v>
       </c>
@@ -5991,23 +5930,23 @@
       <c r="I42" s="106"/>
       <c r="J42" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>17451.538500000002</v>
       </c>
       <c r="K42" s="88">
         <f t="shared" si="3"/>
-        <v>45494.184999999998</v>
-      </c>
-      <c r="L42" s="247">
+        <v>52608.294750000008</v>
+      </c>
+      <c r="L42" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M42" s="6">
         <f t="shared" si="5"/>
-        <v>45494.184999999998</v>
+        <v>70059.833250000011</v>
       </c>
       <c r="N42" s="11">
         <f t="shared" si="1"/>
-        <v>48223.8361</v>
+        <v>74263.423245000013</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -6027,7 +5966,7 @@
       <c r="F43" s="88">
         <v>37222.514999999999</v>
       </c>
-      <c r="G43" s="196">
+      <c r="G43" s="241">
         <f t="shared" ref="G43:G44" si="8">F43</f>
         <v>37222.514999999999</v>
       </c>
@@ -6038,27 +5977,27 @@
       <c r="I43" s="106"/>
       <c r="J43" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>14278.531500000001</v>
       </c>
       <c r="K43" s="88">
         <f t="shared" si="3"/>
-        <v>37222.514999999999</v>
-      </c>
-      <c r="L43" s="247">
+        <v>43043.150250000006</v>
+      </c>
+      <c r="L43" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="5"/>
-        <v>37222.514999999999</v>
+        <v>57321.681750000003</v>
       </c>
       <c r="N43" s="11">
         <f t="shared" si="1"/>
-        <v>39455.865899999997</v>
+        <v>60760.982655</v>
       </c>
       <c r="P43" s="108">
         <f>L1-K52</f>
-        <v>9488.005231000483</v>
+        <v>1.2049999088048935E-2</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -6078,7 +6017,7 @@
       <c r="F44" s="88">
         <v>50457.187000000005</v>
       </c>
-      <c r="G44" s="196">
+      <c r="G44" s="241">
         <f t="shared" si="8"/>
         <v>50457.187000000005</v>
       </c>
@@ -6089,11 +6028,11 @@
       <c r="I44" s="106"/>
       <c r="J44" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>19355.342699999997</v>
       </c>
       <c r="K44" s="88">
         <f t="shared" si="3"/>
-        <v>50457.187000000005</v>
+        <v>58347.381449999993</v>
       </c>
       <c r="L44" s="160">
         <f t="shared" si="4"/>
@@ -6101,11 +6040,11 @@
       </c>
       <c r="M44" s="6">
         <f t="shared" si="5"/>
-        <v>50457.187000000005</v>
+        <v>77702.724149999995</v>
       </c>
       <c r="N44" s="11">
         <f t="shared" si="1"/>
-        <v>53484.618220000004</v>
+        <v>82364.887598999994</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -6125,7 +6064,7 @@
       <c r="F45" s="88">
         <v>44667.018000000011</v>
       </c>
-      <c r="G45" s="196">
+      <c r="G45" s="241">
         <f t="shared" ref="G45:G51" si="9">F45</f>
         <v>44667.018000000011</v>
       </c>
@@ -6136,11 +6075,11 @@
       <c r="I45" s="106"/>
       <c r="J45" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>17134.237800000003</v>
       </c>
       <c r="K45" s="88">
         <f t="shared" si="3"/>
-        <v>44667.018000000011</v>
+        <v>51651.780300000006</v>
       </c>
       <c r="L45" s="160">
         <f t="shared" si="4"/>
@@ -6148,11 +6087,11 @@
       </c>
       <c r="M45" s="6">
         <f t="shared" si="5"/>
-        <v>44667.018000000011</v>
+        <v>68786.018100000016</v>
       </c>
       <c r="N45" s="11">
         <f t="shared" si="1"/>
-        <v>47347.03908000001</v>
+        <v>72913.179186000023</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -6172,7 +6111,7 @@
       <c r="F46" s="88">
         <v>43839.850999999995</v>
       </c>
-      <c r="G46" s="196">
+      <c r="G46" s="241">
         <f>F46</f>
         <v>43839.850999999995</v>
       </c>
@@ -6183,11 +6122,11 @@
       <c r="I46" s="106"/>
       <c r="J46" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15865.035</v>
       </c>
       <c r="K46" s="88">
         <f t="shared" si="3"/>
-        <v>41358.35</v>
+        <v>47825.722500000003</v>
       </c>
       <c r="L46" s="160">
         <f t="shared" si="4"/>
@@ -6195,11 +6134,11 @@
       </c>
       <c r="M46" s="6">
         <f t="shared" si="5"/>
-        <v>41358.35</v>
+        <v>63690.757500000007</v>
       </c>
       <c r="N46" s="11">
         <f t="shared" si="1"/>
-        <v>43839.850999999995</v>
+        <v>67512.202950000006</v>
       </c>
       <c r="Q46" t="s">
         <v>132</v>
@@ -6222,7 +6161,7 @@
       <c r="F47" s="88">
         <v>41358.35</v>
       </c>
-      <c r="G47" s="196">
+      <c r="G47" s="241">
         <f t="shared" si="9"/>
         <v>41358.35</v>
       </c>
@@ -6233,11 +6172,11 @@
       <c r="I47" s="106"/>
       <c r="J47" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15865.035</v>
       </c>
       <c r="K47" s="88">
         <f t="shared" si="3"/>
-        <v>41358.35</v>
+        <v>47825.722500000003</v>
       </c>
       <c r="L47" s="160">
         <f t="shared" si="4"/>
@@ -6245,16 +6184,16 @@
       </c>
       <c r="M47" s="6">
         <f t="shared" si="5"/>
-        <v>41358.35</v>
+        <v>63690.757500000007</v>
       </c>
       <c r="N47" s="11">
         <f t="shared" si="1"/>
-        <v>43839.850999999995</v>
+        <v>67512.202950000006</v>
       </c>
       <c r="O47" s="137"/>
       <c r="Q47" s="134">
         <f>M3-J52</f>
-        <v>0</v>
+        <v>-0.13370000058785081</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -6274,7 +6213,7 @@
       <c r="F48" s="88">
         <v>40531.182999999997</v>
       </c>
-      <c r="G48" s="196">
+      <c r="G48" s="241">
         <f t="shared" si="9"/>
         <v>40531.182999999997</v>
       </c>
@@ -6285,11 +6224,11 @@
       <c r="I48" s="106"/>
       <c r="J48" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15547.7343</v>
       </c>
       <c r="K48" s="88">
         <f t="shared" si="3"/>
-        <v>40531.182999999997</v>
+        <v>46869.208049999994</v>
       </c>
       <c r="L48" s="160">
         <f t="shared" si="4"/>
@@ -6297,11 +6236,11 @@
       </c>
       <c r="M48" s="6">
         <f t="shared" si="5"/>
-        <v>40531.182999999997</v>
+        <v>62416.942349999998</v>
       </c>
       <c r="N48" s="11">
         <f t="shared" si="1"/>
-        <v>42963.053979999997</v>
+        <v>66161.958891000002</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
@@ -6322,7 +6261,7 @@
       <c r="F49" s="88">
         <v>40531.182999999997</v>
       </c>
-      <c r="G49" s="196">
+      <c r="G49" s="241">
         <f>F49</f>
         <v>40531.182999999997</v>
       </c>
@@ -6333,11 +6272,11 @@
       <c r="I49" s="106"/>
       <c r="J49" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15547.7343</v>
       </c>
       <c r="K49" s="88">
         <f t="shared" si="3"/>
-        <v>40531.182999999997</v>
+        <v>46869.208049999994</v>
       </c>
       <c r="L49" s="160">
         <f t="shared" si="4"/>
@@ -6345,11 +6284,11 @@
       </c>
       <c r="M49" s="6">
         <f t="shared" si="5"/>
-        <v>40531.182999999997</v>
+        <v>62416.942349999998</v>
       </c>
       <c r="N49" s="11">
         <f t="shared" si="1"/>
-        <v>42963.053979999997</v>
+        <v>66161.958891000002</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
@@ -6369,7 +6308,7 @@
       <c r="F50" s="88">
         <v>48802.852999999996</v>
       </c>
-      <c r="G50" s="195">
+      <c r="G50" s="242">
         <f>F50</f>
         <v>48802.852999999996</v>
       </c>
@@ -6380,11 +6319,11 @@
       <c r="I50" s="106"/>
       <c r="J50" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>18720.741299999998</v>
       </c>
       <c r="K50" s="88">
         <f t="shared" si="3"/>
-        <v>48802.852999999996</v>
+        <v>56434.352549999996</v>
       </c>
       <c r="L50" s="160">
         <f t="shared" si="4"/>
@@ -6392,11 +6331,11 @@
       </c>
       <c r="M50" s="6">
         <f t="shared" si="5"/>
-        <v>48802.852999999996</v>
+        <v>75155.09384999999</v>
       </c>
       <c r="N50" s="11">
         <f t="shared" si="1"/>
-        <v>51731.024179999993</v>
+        <v>79664.399480999986</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
@@ -6416,7 +6355,7 @@
       <c r="F51" s="88">
         <v>47148.518999999993</v>
       </c>
-      <c r="G51" s="196">
+      <c r="G51" s="241">
         <f t="shared" si="9"/>
         <v>47148.518999999993</v>
       </c>
@@ -6427,11 +6366,11 @@
       <c r="I51" s="106"/>
       <c r="J51" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>18086.139899999998</v>
       </c>
       <c r="K51" s="88">
         <f t="shared" si="3"/>
-        <v>47148.518999999993</v>
+        <v>54521.323649999991</v>
       </c>
       <c r="L51" s="160">
         <f t="shared" ref="L51" si="10">J$3*E51%+J$4</f>
@@ -6439,11 +6378,11 @@
       </c>
       <c r="M51" s="6">
         <f t="shared" si="5"/>
-        <v>47148.518999999993</v>
+        <v>72607.463549999986</v>
       </c>
       <c r="N51" s="11">
         <f t="shared" si="1"/>
-        <v>49977.430139999989</v>
+        <v>76963.911362999992</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6467,59 +6406,59 @@
       <c r="I52" s="89"/>
       <c r="J52" s="126">
         <f>SUM(J8:J51)</f>
-        <v>0</v>
+        <v>2916310.7337000007</v>
       </c>
       <c r="K52" s="90">
         <f>SUM(K7:K51)</f>
-        <v>8217161.5547689991</v>
-      </c>
-      <c r="L52" s="169">
+        <v>9512419.9879500009</v>
+      </c>
+      <c r="L52" s="168">
         <f>SUM(L7:L51)</f>
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="M52" s="91">
         <f>SUM(M7:M51)</f>
-        <v>8281188.1846146872</v>
+        <v>12768686.879035691</v>
       </c>
       <c r="N52" s="90">
         <f>SUM(N7:N51)</f>
-        <v>8778059.4756915644</v>
+        <v>13534808.091777833</v>
       </c>
       <c r="P52" s="134"/>
     </row>
     <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K53" s="137">
         <f>K52-L1</f>
-        <v>-9488.005231000483</v>
+        <v>-1.2049999088048935E-2</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="224"/>
-      <c r="D54" s="224"/>
-      <c r="E54" s="224"/>
-      <c r="F54" s="224"/>
-      <c r="G54" s="224"/>
-      <c r="H54" s="224"/>
-      <c r="I54" s="224"/>
-      <c r="J54" s="224"/>
-      <c r="K54" s="224"/>
-      <c r="L54" s="224"/>
-      <c r="M54" s="224"/>
-      <c r="N54" s="224"/>
+      <c r="C54" s="216"/>
+      <c r="D54" s="216"/>
+      <c r="E54" s="216"/>
+      <c r="F54" s="216"/>
+      <c r="G54" s="216"/>
+      <c r="H54" s="216"/>
+      <c r="I54" s="216"/>
+      <c r="J54" s="216"/>
+      <c r="K54" s="216"/>
+      <c r="L54" s="216"/>
+      <c r="M54" s="216"/>
+      <c r="N54" s="216"/>
     </row>
     <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="224"/>
-      <c r="D55" s="224"/>
-      <c r="E55" s="224"/>
-      <c r="F55" s="224"/>
-      <c r="G55" s="224"/>
-      <c r="H55" s="224"/>
-      <c r="I55" s="224"/>
-      <c r="J55" s="224"/>
-      <c r="K55" s="224"/>
-      <c r="L55" s="224"/>
-      <c r="M55" s="224"/>
-      <c r="N55" s="224"/>
+      <c r="C55" s="216"/>
+      <c r="D55" s="216"/>
+      <c r="E55" s="216"/>
+      <c r="F55" s="216"/>
+      <c r="G55" s="216"/>
+      <c r="H55" s="216"/>
+      <c r="I55" s="216"/>
+      <c r="J55" s="216"/>
+      <c r="K55" s="216"/>
+      <c r="L55" s="216"/>
+      <c r="M55" s="216"/>
+      <c r="N55" s="216"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C56" s="163"/>
@@ -6536,112 +6475,107 @@
       <c r="N56" s="163"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C57" s="224" t="s">
+      <c r="C57" s="216" t="s">
         <v>129</v>
       </c>
-      <c r="D57" s="224"/>
-      <c r="E57" s="224"/>
-      <c r="F57" s="224"/>
-      <c r="G57" s="224"/>
-      <c r="H57" s="224"/>
-      <c r="I57" s="224"/>
-      <c r="J57" s="224"/>
-      <c r="K57" s="224"/>
-      <c r="L57" s="224"/>
-      <c r="M57" s="224"/>
-      <c r="N57" s="224"/>
+      <c r="D57" s="216"/>
+      <c r="E57" s="216"/>
+      <c r="F57" s="216"/>
+      <c r="G57" s="216"/>
+      <c r="H57" s="216"/>
+      <c r="I57" s="216"/>
+      <c r="J57" s="216"/>
+      <c r="K57" s="216"/>
+      <c r="L57" s="216"/>
+      <c r="M57" s="216"/>
+      <c r="N57" s="216"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C58" s="224"/>
-      <c r="D58" s="224"/>
-      <c r="E58" s="224"/>
-      <c r="F58" s="224"/>
-      <c r="G58" s="224"/>
-      <c r="H58" s="224"/>
-      <c r="I58" s="224"/>
-      <c r="J58" s="224"/>
-      <c r="K58" s="224"/>
-      <c r="L58" s="224"/>
-      <c r="M58" s="224"/>
-      <c r="N58" s="224"/>
+      <c r="C58" s="216"/>
+      <c r="D58" s="216"/>
+      <c r="E58" s="216"/>
+      <c r="F58" s="216"/>
+      <c r="G58" s="216"/>
+      <c r="H58" s="216"/>
+      <c r="I58" s="216"/>
+      <c r="J58" s="216"/>
+      <c r="K58" s="216"/>
+      <c r="L58" s="216"/>
+      <c r="M58" s="216"/>
+      <c r="N58" s="216"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C59" s="224"/>
-      <c r="D59" s="224"/>
-      <c r="E59" s="224"/>
-      <c r="F59" s="224"/>
-      <c r="G59" s="224"/>
-      <c r="H59" s="224"/>
-      <c r="I59" s="224"/>
-      <c r="J59" s="224"/>
-      <c r="K59" s="224"/>
-      <c r="L59" s="224"/>
-      <c r="M59" s="224"/>
-      <c r="N59" s="224"/>
+      <c r="C59" s="216"/>
+      <c r="D59" s="216"/>
+      <c r="E59" s="216"/>
+      <c r="F59" s="216"/>
+      <c r="G59" s="216"/>
+      <c r="H59" s="216"/>
+      <c r="I59" s="216"/>
+      <c r="J59" s="216"/>
+      <c r="K59" s="216"/>
+      <c r="L59" s="216"/>
+      <c r="M59" s="216"/>
+      <c r="N59" s="216"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C60" s="224"/>
-      <c r="D60" s="224"/>
-      <c r="E60" s="224"/>
-      <c r="F60" s="224"/>
-      <c r="G60" s="224"/>
-      <c r="H60" s="224"/>
-      <c r="I60" s="224"/>
-      <c r="J60" s="224"/>
-      <c r="K60" s="224"/>
-      <c r="L60" s="224"/>
-      <c r="M60" s="224"/>
-      <c r="N60" s="224"/>
+      <c r="C60" s="216"/>
+      <c r="D60" s="216"/>
+      <c r="E60" s="216"/>
+      <c r="F60" s="216"/>
+      <c r="G60" s="216"/>
+      <c r="H60" s="216"/>
+      <c r="I60" s="216"/>
+      <c r="J60" s="216"/>
+      <c r="K60" s="216"/>
+      <c r="L60" s="216"/>
+      <c r="M60" s="216"/>
+      <c r="N60" s="216"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C61" s="224"/>
-      <c r="D61" s="224"/>
-      <c r="E61" s="224"/>
-      <c r="F61" s="224"/>
-      <c r="G61" s="224"/>
-      <c r="H61" s="224"/>
-      <c r="I61" s="224"/>
-      <c r="J61" s="224"/>
-      <c r="K61" s="224"/>
-      <c r="L61" s="224"/>
-      <c r="M61" s="224"/>
-      <c r="N61" s="224"/>
+      <c r="C61" s="216"/>
+      <c r="D61" s="216"/>
+      <c r="E61" s="216"/>
+      <c r="F61" s="216"/>
+      <c r="G61" s="216"/>
+      <c r="H61" s="216"/>
+      <c r="I61" s="216"/>
+      <c r="J61" s="216"/>
+      <c r="K61" s="216"/>
+      <c r="L61" s="216"/>
+      <c r="M61" s="216"/>
+      <c r="N61" s="216"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C62" s="224"/>
-      <c r="D62" s="224"/>
-      <c r="E62" s="224"/>
-      <c r="F62" s="224"/>
-      <c r="G62" s="224"/>
-      <c r="H62" s="224"/>
-      <c r="I62" s="224"/>
-      <c r="J62" s="224"/>
-      <c r="K62" s="224"/>
-      <c r="L62" s="224"/>
-      <c r="M62" s="224"/>
-      <c r="N62" s="224"/>
+      <c r="C62" s="216"/>
+      <c r="D62" s="216"/>
+      <c r="E62" s="216"/>
+      <c r="F62" s="216"/>
+      <c r="G62" s="216"/>
+      <c r="H62" s="216"/>
+      <c r="I62" s="216"/>
+      <c r="J62" s="216"/>
+      <c r="K62" s="216"/>
+      <c r="L62" s="216"/>
+      <c r="M62" s="216"/>
+      <c r="N62" s="216"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C63" s="224"/>
-      <c r="D63" s="224"/>
-      <c r="E63" s="224"/>
-      <c r="F63" s="224"/>
-      <c r="G63" s="224"/>
-      <c r="H63" s="224"/>
-      <c r="I63" s="224"/>
-      <c r="J63" s="224"/>
-      <c r="K63" s="224"/>
-      <c r="L63" s="224"/>
-      <c r="M63" s="224"/>
-      <c r="N63" s="224"/>
+      <c r="C63" s="216"/>
+      <c r="D63" s="216"/>
+      <c r="E63" s="216"/>
+      <c r="F63" s="216"/>
+      <c r="G63" s="216"/>
+      <c r="H63" s="216"/>
+      <c r="I63" s="216"/>
+      <c r="J63" s="216"/>
+      <c r="K63" s="216"/>
+      <c r="L63" s="216"/>
+      <c r="M63" s="216"/>
+      <c r="N63" s="216"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
@@ -6654,9 +6588,14 @@
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="I5:I6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6677,7 +6616,7 @@
       <c r="C5" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="186">
+      <c r="D5" s="185">
         <v>-447223.45918396302</v>
       </c>
     </row>
@@ -6685,7 +6624,7 @@
       <c r="C6" t="s">
         <v>147</v>
       </c>
-      <c r="D6" s="186">
+      <c r="D6" s="185">
         <v>0</v>
       </c>
     </row>
@@ -6693,7 +6632,7 @@
       <c r="C7" t="s">
         <v>148</v>
       </c>
-      <c r="D7" s="186">
+      <c r="D7" s="185">
         <v>0</v>
       </c>
     </row>
@@ -6701,7 +6640,7 @@
       <c r="C8" t="s">
         <v>149</v>
       </c>
-      <c r="D8" s="186">
+      <c r="D8" s="185">
         <v>0</v>
       </c>
     </row>
@@ -6714,7 +6653,7 @@
       <c r="C11" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="186">
+      <c r="D11" s="185">
         <v>451182</v>
       </c>
     </row>
@@ -6722,7 +6661,7 @@
       <c r="C12" t="s">
         <v>147</v>
       </c>
-      <c r="D12" s="186">
+      <c r="D12" s="185">
         <v>40606.380000000005</v>
       </c>
     </row>
@@ -6730,7 +6669,7 @@
       <c r="C13" t="s">
         <v>148</v>
       </c>
-      <c r="D13" s="186">
+      <c r="D13" s="185">
         <v>41358.350000000006</v>
       </c>
     </row>
@@ -6738,7 +6677,7 @@
       <c r="C14" t="s">
         <v>149</v>
       </c>
-      <c r="D14" s="186">
+      <c r="D14" s="185">
         <v>37598.5</v>
       </c>
     </row>
@@ -6756,7 +6695,7 @@
       <c r="C17" t="s">
         <v>146</v>
       </c>
-      <c r="D17" s="186">
+      <c r="D17" s="185">
         <f>D11+D5</f>
         <v>3958.5408160369843</v>
       </c>
@@ -6765,7 +6704,7 @@
       <c r="C18" t="s">
         <v>147</v>
       </c>
-      <c r="D18" s="186">
+      <c r="D18" s="185">
         <v>40606.380000000005</v>
       </c>
     </row>
@@ -6773,7 +6712,7 @@
       <c r="C19" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="186">
+      <c r="D19" s="185">
         <v>41358.350000000006</v>
       </c>
     </row>
@@ -6781,7 +6720,7 @@
       <c r="C20" t="s">
         <v>149</v>
       </c>
-      <c r="D20" s="186">
+      <c r="D20" s="185">
         <v>37598.5</v>
       </c>
     </row>
@@ -6789,30 +6728,30 @@
       <c r="C21" t="s">
         <v>153</v>
       </c>
-      <c r="D21" s="186">
+      <c r="D21" s="185">
         <v>-25000</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="239" t="s">
+      <c r="C22" s="227" t="s">
         <v>152</v>
       </c>
-      <c r="D22" s="242">
+      <c r="D22" s="230">
         <f>SUM(D17:D21)</f>
         <v>98521.770816036995</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="240"/>
-      <c r="D23" s="243"/>
+      <c r="C23" s="228"/>
+      <c r="D23" s="231"/>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="240"/>
-      <c r="D24" s="243"/>
+      <c r="C24" s="228"/>
+      <c r="D24" s="231"/>
     </row>
     <row r="25" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="241"/>
-      <c r="D25" s="244"/>
+      <c r="C25" s="229"/>
+      <c r="D25" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6924,10 +6863,10 @@
       <c r="O4" s="49"/>
     </row>
     <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="245" t="s">
+      <c r="A5" s="233" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="245" t="s">
+      <c r="B5" s="233" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="55" t="s">
@@ -6939,7 +6878,7 @@
       <c r="E5" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="245" t="s">
+      <c r="F5" s="233" t="s">
         <v>75</v>
       </c>
       <c r="G5" s="37" t="s">
@@ -6961,16 +6900,16 @@
         <v>29</v>
       </c>
       <c r="M5" s="41"/>
-      <c r="N5" s="245" t="s">
+      <c r="N5" s="233" t="s">
         <v>78</v>
       </c>
-      <c r="O5" s="245" t="s">
+      <c r="O5" s="233" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="246"/>
-      <c r="B6" s="246"/>
+      <c r="A6" s="234"/>
+      <c r="B6" s="234"/>
       <c r="C6" s="56" t="s">
         <v>80</v>
       </c>
@@ -6980,7 +6919,7 @@
       <c r="E6" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="246"/>
+      <c r="F6" s="234"/>
       <c r="G6" s="44" t="s">
         <v>81</v>
       </c>
@@ -7000,8 +6939,8 @@
         <v>84</v>
       </c>
       <c r="M6" s="47"/>
-      <c r="N6" s="246"/>
-      <c r="O6" s="246"/>
+      <c r="N6" s="234"/>
+      <c r="O6" s="234"/>
     </row>
     <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
